--- a/output/slowfix_portfolio_daily.xlsx
+++ b/output/slowfix_portfolio_daily.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>303,541.24</t>
+          <t>305,657.44</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+203.54%</t>
+          <t>+205.66%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>312,885  (+212.88%)</t>
+          <t>315,134  (+215.13%)</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5,136  (9.3 pts of return)</t>
+          <t>5,197  (9.5 pts of return)</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11">
@@ -706,7 +706,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>27.6%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>3.9 bars</t>
+          <t>3.8 bars</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>+9.87R  (best +25.82R)</t>
+          <t>+9.44R  (best +25.82R)</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14,530  (+9.87%)</t>
+          <t>13,957  (+9.44%)</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-1,582  (-1.05%)</t>
+          <t>-1,589  (-1.05%)</t>
         </is>
       </c>
     </row>
@@ -3705,13 +3705,13 @@
         <v>46129</v>
       </c>
       <c r="B112" s="5" t="n">
-        <v>154965.97</v>
+        <v>156127.96</v>
       </c>
       <c r="C112" s="5" t="n">
         <v>2391.46</v>
       </c>
       <c r="D112" s="5" t="n">
-        <v>152574.51</v>
+        <v>153736.5</v>
       </c>
       <c r="E112" t="n">
         <v>2</v>
@@ -3728,7 +3728,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance stop (-1,254); Ethereum_Per_USD_Binance stop (-1,547); Live_Cattle_Futures_CME bearish_reversal (+31,630); USD_EUR_Cross_Rate open_at_end (open-&gt;closed 0)</t>
+          <t>Bitcoin_Per_USD_Binance stop (-1,254); Ethereum_Per_USD_Binance stop (-1,547); Live_Cattle_Futures_CME bearish_reversal (+31,630); USD_EUR_Cross_Rate data_end (+1,123)</t>
         </is>
       </c>
     </row>
@@ -3737,13 +3737,13 @@
         <v>46130</v>
       </c>
       <c r="B113" s="5" t="n">
-        <v>154965.97</v>
+        <v>156127.96</v>
       </c>
       <c r="C113" s="5" t="n">
         <v>2391.46</v>
       </c>
       <c r="D113" s="5" t="n">
-        <v>152574.51</v>
+        <v>153736.5</v>
       </c>
       <c r="E113" t="n">
         <v>2</v>
@@ -3761,13 +3761,13 @@
         <v>46132</v>
       </c>
       <c r="B114" s="5" t="n">
-        <v>154965.97</v>
+        <v>156127.96</v>
       </c>
       <c r="C114" s="5" t="n">
         <v>2391.46</v>
       </c>
       <c r="D114" s="5" t="n">
-        <v>152574.51</v>
+        <v>153736.5</v>
       </c>
       <c r="E114" t="n">
         <v>2</v>
@@ -3785,13 +3785,13 @@
         <v>46133</v>
       </c>
       <c r="B115" s="5" t="n">
-        <v>154965.97</v>
+        <v>156127.96</v>
       </c>
       <c r="C115" s="5" t="n">
         <v>2391.46</v>
       </c>
       <c r="D115" s="5" t="n">
-        <v>152574.51</v>
+        <v>153736.5</v>
       </c>
       <c r="E115" t="n">
         <v>2</v>
@@ -3809,13 +3809,13 @@
         <v>46134</v>
       </c>
       <c r="B116" s="5" t="n">
-        <v>153743.88</v>
+        <v>154905.87</v>
       </c>
       <c r="C116" s="5" t="n">
-        <v>2704.36</v>
+        <v>2715.98</v>
       </c>
       <c r="D116" s="5" t="n">
-        <v>151039.52</v>
+        <v>152189.89</v>
       </c>
       <c r="E116" t="n">
         <v>2</v>
@@ -3827,7 +3827,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini short (risk 1,526)</t>
+          <t>Dow_Futures_E_mini short (risk 1,537)</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -3841,13 +3841,13 @@
         <v>46135</v>
       </c>
       <c r="B117" s="5" t="n">
-        <v>153743.88</v>
+        <v>154905.87</v>
       </c>
       <c r="C117" s="5" t="n">
-        <v>2704.36</v>
+        <v>2715.98</v>
       </c>
       <c r="D117" s="5" t="n">
-        <v>151039.52</v>
+        <v>152189.89</v>
       </c>
       <c r="E117" t="n">
         <v>2</v>
@@ -3865,13 +3865,13 @@
         <v>46136</v>
       </c>
       <c r="B118" s="5" t="n">
-        <v>153743.88</v>
+        <v>154905.87</v>
       </c>
       <c r="C118" s="5" t="n">
-        <v>2704.36</v>
+        <v>2715.98</v>
       </c>
       <c r="D118" s="5" t="n">
-        <v>151039.52</v>
+        <v>152189.89</v>
       </c>
       <c r="E118" t="n">
         <v>2</v>
@@ -3889,13 +3889,13 @@
         <v>46139</v>
       </c>
       <c r="B119" s="5" t="n">
-        <v>153743.88</v>
+        <v>154905.87</v>
       </c>
       <c r="C119" s="5" t="n">
-        <v>4214.76</v>
+        <v>4237.88</v>
       </c>
       <c r="D119" s="5" t="n">
-        <v>149529.13</v>
+        <v>150667.99</v>
       </c>
       <c r="E119" t="n">
         <v>3</v>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_CME short (risk 1,510)</t>
+          <t>Bitcoin_Per_USD_CME short (risk 1,522)</t>
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
@@ -3917,13 +3917,13 @@
         <v>46140</v>
       </c>
       <c r="B120" s="5" t="n">
-        <v>153743.88</v>
+        <v>154905.87</v>
       </c>
       <c r="C120" s="5" t="n">
-        <v>5710.05</v>
+        <v>5744.56</v>
       </c>
       <c r="D120" s="5" t="n">
-        <v>148033.84</v>
+        <v>149161.31</v>
       </c>
       <c r="E120" t="n">
         <v>4</v>
@@ -3935,7 +3935,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>S_P_500_E_mini short (risk 1,495)</t>
+          <t>S_P_500_E_mini short (risk 1,507)</t>
         </is>
       </c>
       <c r="H120" t="inlineStr"/>
@@ -3945,13 +3945,13 @@
         <v>46141</v>
       </c>
       <c r="B121" s="5" t="n">
-        <v>153743.88</v>
+        <v>154905.87</v>
       </c>
       <c r="C121" s="5" t="n">
-        <v>7190.39</v>
+        <v>7236.17</v>
       </c>
       <c r="D121" s="5" t="n">
-        <v>146553.5</v>
+        <v>147669.7</v>
       </c>
       <c r="E121" t="n">
         <v>5</v>
@@ -3963,7 +3963,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 1,480)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 1,492)</t>
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
@@ -3973,13 +3973,13 @@
         <v>46142</v>
       </c>
       <c r="B122" s="5" t="n">
-        <v>150619.22</v>
+        <v>151757.41</v>
       </c>
       <c r="C122" s="5" t="n">
-        <v>5634.88</v>
+        <v>5668.82</v>
       </c>
       <c r="D122" s="5" t="n">
-        <v>144984.33</v>
+        <v>146088.58</v>
       </c>
       <c r="E122" t="n">
         <v>4</v>
@@ -3991,12 +3991,12 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures short (risk 1,466)</t>
+          <t>Corn_CBOT_Futures short (risk 1,477)</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini stop (-1,626); S_P_500_E_mini stop (-1,499)</t>
+          <t>Dow_Futures_E_mini stop (-1,638); S_P_500_E_mini stop (-1,510)</t>
         </is>
       </c>
     </row>
@@ -4005,13 +4005,13 @@
         <v>46143</v>
       </c>
       <c r="B123" s="5" t="n">
-        <v>148845.15</v>
+        <v>149969.83</v>
       </c>
       <c r="C123" s="5" t="n">
-        <v>8475.530000000001</v>
+        <v>8531.1</v>
       </c>
       <c r="D123" s="5" t="n">
-        <v>140369.62</v>
+        <v>141438.72</v>
       </c>
       <c r="E123" t="n">
         <v>6</v>
@@ -4023,12 +4023,12 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Japanese_Yen_Futures short (risk 1,450); Live_Cattle_Futures_CME short (risk 1,435); US_Dollar_Index_Futures long (risk 1,421)</t>
+          <t>Japanese_Yen_Futures short (risk 1,461); Live_Cattle_Futures_CME short (risk 1,446); US_Dollar_Index_Futures long (risk 1,432)</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures stop (-1,774)</t>
+          <t>Corn_CBOT_Futures stop (-1,788)</t>
         </is>
       </c>
     </row>
@@ -4037,13 +4037,13 @@
         <v>46146</v>
       </c>
       <c r="B124" s="5" t="n">
-        <v>147322.32</v>
+        <v>148435.4</v>
       </c>
       <c r="C124" s="5" t="n">
-        <v>8368.83</v>
+        <v>8423.59</v>
       </c>
       <c r="D124" s="5" t="n">
-        <v>138953.49</v>
+        <v>140011.81</v>
       </c>
       <c r="E124" t="n">
         <v>6</v>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Nasdaq_100_E_mini short (risk 1,404)</t>
+          <t>Nasdaq_100_E_mini short (risk 1,414)</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_CME stop (-1,523)</t>
+          <t>Bitcoin_Per_USD_CME stop (-1,534)</t>
         </is>
       </c>
     </row>
@@ -4069,13 +4069,13 @@
         <v>46147</v>
       </c>
       <c r="B125" s="5" t="n">
-        <v>145917.67</v>
+        <v>147020.05</v>
       </c>
       <c r="C125" s="5" t="n">
-        <v>8354.67</v>
+        <v>8409.32</v>
       </c>
       <c r="D125" s="5" t="n">
-        <v>137563</v>
+        <v>138610.73</v>
       </c>
       <c r="E125" t="n">
         <v>6</v>
@@ -4087,12 +4087,12 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures short (risk 1,390)</t>
+          <t>Corn_CBOT_Futures short (risk 1,400)</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Nasdaq_100_E_mini stop (-1,405)</t>
+          <t>Nasdaq_100_E_mini stop (-1,415)</t>
         </is>
       </c>
     </row>
@@ -4101,13 +4101,13 @@
         <v>46148</v>
       </c>
       <c r="B126" s="5" t="n">
-        <v>152081.6</v>
+        <v>153230.93</v>
       </c>
       <c r="C126" s="5" t="n">
-        <v>5379.13</v>
+        <v>5411.12</v>
       </c>
       <c r="D126" s="5" t="n">
-        <v>146702.48</v>
+        <v>147819.81</v>
       </c>
       <c r="E126" t="n">
         <v>4</v>
@@ -4119,12 +4119,12 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_CME short (risk 1,376)</t>
+          <t>Bitcoin_Per_USD_CME short (risk 1,386)</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT bearish_reversal (+9,215); Japanese_Yen_Futures stop (-1,607); US_Dollar_Index_Futures stop (-1,444)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT bearish_reversal (+9,285); Japanese_Yen_Futures stop (-1,619); US_Dollar_Index_Futures stop (-1,455)</t>
         </is>
       </c>
     </row>
@@ -4133,13 +4133,13 @@
         <v>46149</v>
       </c>
       <c r="B127" s="5" t="n">
-        <v>169384.34</v>
+        <v>170533.66</v>
       </c>
       <c r="C127" s="5" t="n">
-        <v>7119.89</v>
+        <v>7174.12</v>
       </c>
       <c r="D127" s="5" t="n">
-        <v>162264.45</v>
+        <v>163359.55</v>
       </c>
       <c r="E127" t="n">
         <v>5</v>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>EURO_Futures short (risk 1,467); NY_Platinum_Futures short (risk 1,452)</t>
+          <t>EURO_Futures short (risk 1,478); NY_Platinum_Futures short (risk 1,463)</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -4165,13 +4165,13 @@
         <v>46150</v>
       </c>
       <c r="B128" s="5" t="n">
-        <v>167879.7</v>
+        <v>169017.56</v>
       </c>
       <c r="C128" s="5" t="n">
-        <v>5652.86</v>
+        <v>5695.92</v>
       </c>
       <c r="D128" s="5" t="n">
-        <v>162226.83</v>
+        <v>163321.65</v>
       </c>
       <c r="E128" t="n">
         <v>4</v>
@@ -4184,7 +4184,7 @@
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr">
         <is>
-          <t>EURO_Futures stop (-1,505)</t>
+          <t>EURO_Futures stop (-1,516)</t>
         </is>
       </c>
     </row>
@@ -4193,13 +4193,13 @@
         <v>46153</v>
       </c>
       <c r="B129" s="5" t="n">
-        <v>176006.96</v>
+        <v>177206.73</v>
       </c>
       <c r="C129" s="5" t="n">
-        <v>4387.43</v>
+        <v>4419.44</v>
       </c>
       <c r="D129" s="5" t="n">
-        <v>171619.53</v>
+        <v>172787.29</v>
       </c>
       <c r="E129" t="n">
         <v>3</v>
@@ -4211,12 +4211,12 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX short (risk 1,622)</t>
+          <t>Gold_Futures_COMEX short (risk 1,633)</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Live_Cattle_Futures_CME bearish_reversal (+9,600); NY_Platinum_Futures stop (-1,472)</t>
+          <t>Live_Cattle_Futures_CME bearish_reversal (+9,673); NY_Platinum_Futures stop (-1,484)</t>
         </is>
       </c>
     </row>
@@ -4225,13 +4225,13 @@
         <v>46154</v>
       </c>
       <c r="B130" s="5" t="n">
-        <v>174332.78</v>
+        <v>175521.25</v>
       </c>
       <c r="C130" s="5" t="n">
-        <v>4481.36</v>
+        <v>4514.1</v>
       </c>
       <c r="D130" s="5" t="n">
-        <v>169851.42</v>
+        <v>171007.15</v>
       </c>
       <c r="E130" t="n">
         <v>3</v>
@@ -4243,12 +4243,12 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX short (risk 1,716)</t>
+          <t>Silver_Futures_COMEX short (risk 1,728)</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX stop (-1,674)</t>
+          <t>Gold_Futures_COMEX stop (-1,685)</t>
         </is>
       </c>
     </row>
@@ -4257,13 +4257,13 @@
         <v>46155</v>
       </c>
       <c r="B131" s="5" t="n">
-        <v>172613.01</v>
+        <v>173789.78</v>
       </c>
       <c r="C131" s="5" t="n">
-        <v>2765.16</v>
+        <v>2786.23</v>
       </c>
       <c r="D131" s="5" t="n">
-        <v>169847.85</v>
+        <v>171003.56</v>
       </c>
       <c r="E131" t="n">
         <v>2</v>
@@ -4276,7 +4276,7 @@
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX stop (-1,720)</t>
+          <t>Silver_Futures_COMEX stop (-1,731)</t>
         </is>
       </c>
     </row>
@@ -4285,13 +4285,13 @@
         <v>46156</v>
       </c>
       <c r="B132" s="5" t="n">
-        <v>172613.01</v>
+        <v>173789.78</v>
       </c>
       <c r="C132" s="5" t="n">
-        <v>4463.64</v>
+        <v>4496.26</v>
       </c>
       <c r="D132" s="5" t="n">
-        <v>168149.37</v>
+        <v>169293.52</v>
       </c>
       <c r="E132" t="n">
         <v>3</v>
@@ -4303,7 +4303,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 1,698)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 1,710)</t>
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
@@ -4313,13 +4313,13 @@
         <v>46157</v>
       </c>
       <c r="B133" s="5" t="n">
-        <v>203182.76</v>
+        <v>204592.35</v>
       </c>
       <c r="C133" s="5" t="n">
-        <v>3074.11</v>
+        <v>3096.14</v>
       </c>
       <c r="D133" s="5" t="n">
-        <v>200108.65</v>
+        <v>201496.21</v>
       </c>
       <c r="E133" t="n">
         <v>2</v>
@@ -4332,7 +4332,7 @@
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures bearish_reversal (+30,570)</t>
+          <t>Corn_CBOT_Futures bearish_reversal (+30,803)</t>
         </is>
       </c>
     </row>
@@ -4341,13 +4341,13 @@
         <v>46160</v>
       </c>
       <c r="B134" s="5" t="n">
-        <v>218550.19</v>
+        <v>220076.83</v>
       </c>
       <c r="C134" s="5" t="n">
-        <v>1698.48</v>
+        <v>1710.04</v>
       </c>
       <c r="D134" s="5" t="n">
-        <v>216851.71</v>
+        <v>218366.79</v>
       </c>
       <c r="E134" t="n">
         <v>1</v>
@@ -4360,7 +4360,7 @@
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_CME bearish_reversal (+15,367)</t>
+          <t>Bitcoin_Per_USD_CME bearish_reversal (+15,484)</t>
         </is>
       </c>
     </row>
@@ -4369,13 +4369,13 @@
         <v>46161</v>
       </c>
       <c r="B135" s="5" t="n">
-        <v>218550.19</v>
+        <v>220076.83</v>
       </c>
       <c r="C135" s="5" t="n">
-        <v>1698.48</v>
+        <v>1710.04</v>
       </c>
       <c r="D135" s="5" t="n">
-        <v>216851.71</v>
+        <v>218366.79</v>
       </c>
       <c r="E135" t="n">
         <v>1</v>
@@ -4393,13 +4393,13 @@
         <v>46162</v>
       </c>
       <c r="B136" s="5" t="n">
-        <v>218550.19</v>
+        <v>220076.83</v>
       </c>
       <c r="C136" s="5" t="n">
-        <v>3867</v>
+        <v>3893.7</v>
       </c>
       <c r="D136" s="5" t="n">
-        <v>214683.19</v>
+        <v>216183.13</v>
       </c>
       <c r="E136" t="n">
         <v>2</v>
@@ -4411,7 +4411,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures short (risk 2,169)</t>
+          <t>US_Dollar_Index_Futures short (risk 2,184)</t>
         </is>
       </c>
       <c r="H136" t="inlineStr"/>
@@ -4421,13 +4421,13 @@
         <v>46163</v>
       </c>
       <c r="B137" s="5" t="n">
-        <v>218550.19</v>
+        <v>220076.83</v>
       </c>
       <c r="C137" s="5" t="n">
-        <v>6013.83</v>
+        <v>6055.53</v>
       </c>
       <c r="D137" s="5" t="n">
-        <v>212536.36</v>
+        <v>214021.3</v>
       </c>
       <c r="E137" t="n">
         <v>3</v>
@@ -4439,7 +4439,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>NY_Palladium_Futures long (risk 2,147)</t>
+          <t>NY_Palladium_Futures long (risk 2,162)</t>
         </is>
       </c>
       <c r="H137" t="inlineStr"/>
@@ -4449,13 +4449,13 @@
         <v>46164</v>
       </c>
       <c r="B138" s="5" t="n">
-        <v>218550.19</v>
+        <v>220076.83</v>
       </c>
       <c r="C138" s="5" t="n">
-        <v>6013.83</v>
+        <v>6055.53</v>
       </c>
       <c r="D138" s="5" t="n">
-        <v>212536.36</v>
+        <v>214021.3</v>
       </c>
       <c r="E138" t="n">
         <v>3</v>
@@ -4473,13 +4473,13 @@
         <v>46167</v>
       </c>
       <c r="B139" s="5" t="n">
-        <v>218550.19</v>
+        <v>220076.83</v>
       </c>
       <c r="C139" s="5" t="n">
-        <v>6013.83</v>
+        <v>6055.53</v>
       </c>
       <c r="D139" s="5" t="n">
-        <v>212536.36</v>
+        <v>214021.3</v>
       </c>
       <c r="E139" t="n">
         <v>3</v>
@@ -4497,13 +4497,13 @@
         <v>46168</v>
       </c>
       <c r="B140" s="5" t="n">
-        <v>218550.19</v>
+        <v>220076.83</v>
       </c>
       <c r="C140" s="5" t="n">
-        <v>6013.83</v>
+        <v>6055.53</v>
       </c>
       <c r="D140" s="5" t="n">
-        <v>212536.36</v>
+        <v>214021.3</v>
       </c>
       <c r="E140" t="n">
         <v>3</v>
@@ -4521,13 +4521,13 @@
         <v>46169</v>
       </c>
       <c r="B141" s="5" t="n">
-        <v>218550.19</v>
+        <v>220076.83</v>
       </c>
       <c r="C141" s="5" t="n">
-        <v>6013.83</v>
+        <v>6055.53</v>
       </c>
       <c r="D141" s="5" t="n">
-        <v>212536.36</v>
+        <v>214021.3</v>
       </c>
       <c r="E141" t="n">
         <v>3</v>
@@ -4545,13 +4545,13 @@
         <v>46170</v>
       </c>
       <c r="B142" s="5" t="n">
-        <v>218550.19</v>
+        <v>220076.83</v>
       </c>
       <c r="C142" s="5" t="n">
-        <v>8139.19</v>
+        <v>8195.75</v>
       </c>
       <c r="D142" s="5" t="n">
-        <v>210411</v>
+        <v>211881.08</v>
       </c>
       <c r="E142" t="n">
         <v>4</v>
@@ -4563,7 +4563,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX long (risk 2,125)</t>
+          <t>Silver_Futures_COMEX long (risk 2,140)</t>
         </is>
       </c>
       <c r="H142" t="inlineStr"/>
@@ -4573,13 +4573,13 @@
         <v>46174</v>
       </c>
       <c r="B143" s="5" t="n">
-        <v>235721.13</v>
+        <v>237364.61</v>
       </c>
       <c r="C143" s="5" t="n">
-        <v>6440.71</v>
+        <v>6485.71</v>
       </c>
       <c r="D143" s="5" t="n">
-        <v>229280.42</v>
+        <v>230878.9</v>
       </c>
       <c r="E143" t="n">
         <v>3</v>
@@ -4592,7 +4592,7 @@
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT bearish_reversal (+17,171)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT bearish_reversal (+17,288)</t>
         </is>
       </c>
     </row>
@@ -4601,13 +4601,13 @@
         <v>46175</v>
       </c>
       <c r="B144" s="5" t="n">
-        <v>235721.13</v>
+        <v>237364.61</v>
       </c>
       <c r="C144" s="5" t="n">
-        <v>6440.71</v>
+        <v>6485.71</v>
       </c>
       <c r="D144" s="5" t="n">
-        <v>229280.42</v>
+        <v>230878.9</v>
       </c>
       <c r="E144" t="n">
         <v>3</v>
@@ -4625,13 +4625,13 @@
         <v>46176</v>
       </c>
       <c r="B145" s="5" t="n">
-        <v>233523.79</v>
+        <v>235151.91</v>
       </c>
       <c r="C145" s="5" t="n">
-        <v>4293.88</v>
+        <v>4323.88</v>
       </c>
       <c r="D145" s="5" t="n">
-        <v>229229.91</v>
+        <v>230828.03</v>
       </c>
       <c r="E145" t="n">
         <v>2</v>
@@ -4644,7 +4644,7 @@
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr">
         <is>
-          <t>NY_Palladium_Futures stop (-2,197)</t>
+          <t>NY_Palladium_Futures stop (-2,213)</t>
         </is>
       </c>
     </row>
@@ -4653,13 +4653,13 @@
         <v>46177</v>
       </c>
       <c r="B146" s="5" t="n">
-        <v>233523.79</v>
+        <v>235151.91</v>
       </c>
       <c r="C146" s="5" t="n">
-        <v>4293.88</v>
+        <v>4323.88</v>
       </c>
       <c r="D146" s="5" t="n">
-        <v>229229.91</v>
+        <v>230828.03</v>
       </c>
       <c r="E146" t="n">
         <v>2</v>
@@ -4677,13 +4677,13 @@
         <v>46178</v>
       </c>
       <c r="B147" s="5" t="n">
-        <v>229180.82</v>
+        <v>230778.6</v>
       </c>
       <c r="C147" s="5" t="n">
-        <v>2292.3</v>
+        <v>2308.28</v>
       </c>
       <c r="D147" s="5" t="n">
-        <v>226888.52</v>
+        <v>228470.32</v>
       </c>
       <c r="E147" t="n">
         <v>1</v>
@@ -4695,12 +4695,12 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini short (risk 2,292)</t>
+          <t>Dow_Futures_E_mini short (risk 2,308)</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX stop (-2,130); US_Dollar_Index_Futures stop (-2,213)</t>
+          <t>Silver_Futures_COMEX stop (-2,145); US_Dollar_Index_Futures stop (-2,228)</t>
         </is>
       </c>
     </row>
@@ -4709,13 +4709,13 @@
         <v>46181</v>
       </c>
       <c r="B148" s="5" t="n">
-        <v>229180.82</v>
+        <v>230778.6</v>
       </c>
       <c r="C148" s="5" t="n">
-        <v>6807.38</v>
+        <v>6854.84</v>
       </c>
       <c r="D148" s="5" t="n">
-        <v>222373.44</v>
+        <v>223923.76</v>
       </c>
       <c r="E148" t="n">
         <v>3</v>
@@ -4727,7 +4727,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX long (risk 2,269); US_Dollar_Index_Futures short (risk 2,246)</t>
+          <t>Gold_Futures_COMEX long (risk 2,285); US_Dollar_Index_Futures short (risk 2,262)</t>
         </is>
       </c>
       <c r="H148" t="inlineStr"/>
@@ -4737,13 +4737,13 @@
         <v>46182</v>
       </c>
       <c r="B149" s="5" t="n">
-        <v>226895.16</v>
+        <v>228477</v>
       </c>
       <c r="C149" s="5" t="n">
-        <v>4538.5</v>
+        <v>4570.14</v>
       </c>
       <c r="D149" s="5" t="n">
-        <v>222356.66</v>
+        <v>223906.87</v>
       </c>
       <c r="E149" t="n">
         <v>2</v>
@@ -4756,7 +4756,7 @@
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX stop (-2,286)</t>
+          <t>Gold_Futures_COMEX stop (-2,302)</t>
         </is>
       </c>
     </row>
@@ -4765,13 +4765,13 @@
         <v>46183</v>
       </c>
       <c r="B150" s="5" t="n">
-        <v>226895.16</v>
+        <v>228477</v>
       </c>
       <c r="C150" s="5" t="n">
-        <v>4538.5</v>
+        <v>4570.14</v>
       </c>
       <c r="D150" s="5" t="n">
-        <v>222356.66</v>
+        <v>223906.87</v>
       </c>
       <c r="E150" t="n">
         <v>2</v>
@@ -4789,13 +4789,13 @@
         <v>46184</v>
       </c>
       <c r="B151" s="5" t="n">
-        <v>224582.41</v>
+        <v>226148.13</v>
       </c>
       <c r="C151" s="5" t="n">
-        <v>4515.87</v>
+        <v>4547.35</v>
       </c>
       <c r="D151" s="5" t="n">
-        <v>220066.54</v>
+        <v>221600.78</v>
       </c>
       <c r="E151" t="n">
         <v>2</v>
@@ -4807,12 +4807,12 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX long (risk 2,224)</t>
+          <t>Gold_Futures_COMEX long (risk 2,239)</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures stop (-2,313)</t>
+          <t>US_Dollar_Index_Futures stop (-2,329)</t>
         </is>
       </c>
     </row>
@@ -4821,13 +4821,13 @@
         <v>46185</v>
       </c>
       <c r="B152" s="5" t="n">
-        <v>224582.41</v>
+        <v>226148.13</v>
       </c>
       <c r="C152" s="5" t="n">
-        <v>6716.53</v>
+        <v>6763.36</v>
       </c>
       <c r="D152" s="5" t="n">
-        <v>217865.87</v>
+        <v>219384.77</v>
       </c>
       <c r="E152" t="n">
         <v>3</v>
@@ -4839,7 +4839,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures long (risk 2,201)</t>
+          <t>Corn_CBOT_Futures long (risk 2,216)</t>
         </is>
       </c>
       <c r="H152" t="inlineStr"/>
@@ -4849,13 +4849,13 @@
         <v>46188</v>
       </c>
       <c r="B153" s="5" t="n">
-        <v>219676.91</v>
+        <v>221208.44</v>
       </c>
       <c r="C153" s="5" t="n">
-        <v>4402.23</v>
+        <v>4432.92</v>
       </c>
       <c r="D153" s="5" t="n">
-        <v>215274.69</v>
+        <v>216775.52</v>
       </c>
       <c r="E153" t="n">
         <v>2</v>
@@ -4867,12 +4867,12 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT long (risk 2,179)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT long (risk 2,194)</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures stop (-2,527); Dow_Futures_E_mini stop (-2,379)</t>
+          <t>Corn_CBOT_Futures stop (-2,544); Dow_Futures_E_mini stop (-2,395)</t>
         </is>
       </c>
     </row>
@@ -4881,13 +4881,13 @@
         <v>46189</v>
       </c>
       <c r="B154" s="5" t="n">
-        <v>219676.91</v>
+        <v>221208.44</v>
       </c>
       <c r="C154" s="5" t="n">
-        <v>4402.23</v>
+        <v>4432.92</v>
       </c>
       <c r="D154" s="5" t="n">
-        <v>215274.69</v>
+        <v>216775.52</v>
       </c>
       <c r="E154" t="n">
         <v>2</v>
@@ -4905,13 +4905,13 @@
         <v>46190</v>
       </c>
       <c r="B155" s="5" t="n">
-        <v>230339.05</v>
+        <v>231944.9</v>
       </c>
       <c r="C155" s="5" t="n">
-        <v>4376.31</v>
+        <v>4406.82</v>
       </c>
       <c r="D155" s="5" t="n">
-        <v>225962.73</v>
+        <v>227538.08</v>
       </c>
       <c r="E155" t="n">
         <v>2</v>
@@ -4923,12 +4923,12 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures short (risk 2,153)</t>
+          <t>US_Dollar_Index_Futures short (risk 2,168)</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT bullish_reversal (+10,662)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT bullish_reversal (+10,736)</t>
         </is>
       </c>
     </row>
@@ -4937,13 +4937,13 @@
         <v>46191</v>
       </c>
       <c r="B156" s="5" t="n">
-        <v>228157.11</v>
+        <v>229747.75</v>
       </c>
       <c r="C156" s="5" t="n">
-        <v>2223.57</v>
+        <v>2239.07</v>
       </c>
       <c r="D156" s="5" t="n">
-        <v>225933.54</v>
+        <v>227508.69</v>
       </c>
       <c r="E156" t="n">
         <v>1</v>
@@ -4956,7 +4956,7 @@
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures stop (-2,182)</t>
+          <t>US_Dollar_Index_Futures stop (-2,197)</t>
         </is>
       </c>
     </row>
@@ -4965,13 +4965,13 @@
         <v>46192</v>
       </c>
       <c r="B157" s="5" t="n">
-        <v>228157.11</v>
+        <v>229747.75</v>
       </c>
       <c r="C157" s="5" t="n">
-        <v>4482.9</v>
+        <v>4514.16</v>
       </c>
       <c r="D157" s="5" t="n">
-        <v>223674.21</v>
+        <v>225233.6</v>
       </c>
       <c r="E157" t="n">
         <v>2</v>
@@ -4983,7 +4983,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures short (risk 2,259)</t>
+          <t>US_Dollar_Index_Futures short (risk 2,275)</t>
         </is>
       </c>
       <c r="H157" t="inlineStr"/>
@@ -4993,13 +4993,13 @@
         <v>46195</v>
       </c>
       <c r="B158" s="5" t="n">
-        <v>228157.11</v>
+        <v>229747.75</v>
       </c>
       <c r="C158" s="5" t="n">
-        <v>4482.9</v>
+        <v>4514.16</v>
       </c>
       <c r="D158" s="5" t="n">
-        <v>223674.21</v>
+        <v>225233.6</v>
       </c>
       <c r="E158" t="n">
         <v>2</v>
@@ -5017,13 +5017,13 @@
         <v>46196</v>
       </c>
       <c r="B159" s="5" t="n">
-        <v>225866.61</v>
+        <v>227441.29</v>
       </c>
       <c r="C159" s="5" t="n">
-        <v>4460.31</v>
+        <v>4491.4</v>
       </c>
       <c r="D159" s="5" t="n">
-        <v>221406.3</v>
+        <v>222949.88</v>
       </c>
       <c r="E159" t="n">
         <v>2</v>
@@ -5035,12 +5035,12 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures long (risk 2,237)</t>
+          <t>NY_Platinum_Futures long (risk 2,252)</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures stop (-2,290)</t>
+          <t>US_Dollar_Index_Futures stop (-2,306)</t>
         </is>
       </c>
     </row>
@@ -5049,13 +5049,13 @@
         <v>46197</v>
       </c>
       <c r="B160" s="5" t="n">
-        <v>221347.03</v>
+        <v>222890.19</v>
       </c>
       <c r="C160" s="5" t="n">
-        <v>2214.06</v>
+        <v>2229.5</v>
       </c>
       <c r="D160" s="5" t="n">
-        <v>219132.96</v>
+        <v>220660.7</v>
       </c>
       <c r="E160" t="n">
         <v>1</v>
@@ -5067,12 +5067,12 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>EURO_Futures long (risk 2,214)</t>
+          <t>EURO_Futures long (risk 2,229)</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX stop (-2,239); NY_Platinum_Futures stop (-2,280)</t>
+          <t>Gold_Futures_COMEX stop (-2,255); NY_Platinum_Futures stop (-2,296)</t>
         </is>
       </c>
     </row>
@@ -5081,13 +5081,13 @@
         <v>46198</v>
       </c>
       <c r="B161" s="5" t="n">
-        <v>221347.03</v>
+        <v>222890.19</v>
       </c>
       <c r="C161" s="5" t="n">
-        <v>10848.78</v>
+        <v>10924.41</v>
       </c>
       <c r="D161" s="5" t="n">
-        <v>210498.25</v>
+        <v>211965.78</v>
       </c>
       <c r="E161" t="n">
         <v>5</v>
@@ -5099,7 +5099,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures short (risk 2,191); NY_Palladium_Futures long (risk 2,169); NY_Platinum_Futures long (risk 2,148); US_Dollar_Index_Futures short (risk 2,126)</t>
+          <t>NY_Natural_Gas_Futures short (risk 2,207); NY_Palladium_Futures long (risk 2,185); NY_Platinum_Futures long (risk 2,163); US_Dollar_Index_Futures short (risk 2,141)</t>
         </is>
       </c>
       <c r="H161" t="inlineStr"/>
@@ -5109,13 +5109,13 @@
         <v>46199</v>
       </c>
       <c r="B162" s="5" t="n">
-        <v>218976.81</v>
+        <v>220503.46</v>
       </c>
       <c r="C162" s="5" t="n">
-        <v>8657.450000000001</v>
+        <v>8717.799999999999</v>
       </c>
       <c r="D162" s="5" t="n">
-        <v>210319.37</v>
+        <v>211785.65</v>
       </c>
       <c r="E162" t="n">
         <v>4</v>
@@ -5128,7 +5128,7 @@
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures stop (-2,370)</t>
+          <t>NY_Natural_Gas_Futures stop (-2,387)</t>
         </is>
       </c>
     </row>
@@ -5137,13 +5137,13 @@
         <v>46202</v>
       </c>
       <c r="B163" s="5" t="n">
-        <v>218976.81</v>
+        <v>220503.46</v>
       </c>
       <c r="C163" s="5" t="n">
-        <v>8657.450000000001</v>
+        <v>8717.799999999999</v>
       </c>
       <c r="D163" s="5" t="n">
-        <v>210319.37</v>
+        <v>211785.65</v>
       </c>
       <c r="E163" t="n">
         <v>4</v>
@@ -5161,13 +5161,13 @@
         <v>46203</v>
       </c>
       <c r="B164" s="5" t="n">
-        <v>218976.81</v>
+        <v>220503.46</v>
       </c>
       <c r="C164" s="5" t="n">
-        <v>14904.14</v>
+        <v>15008.05</v>
       </c>
       <c r="D164" s="5" t="n">
-        <v>204072.67</v>
+        <v>205495.41</v>
       </c>
       <c r="E164" t="n">
         <v>7</v>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT long (risk 2,103); German_Long_Bund short (risk 2,082); Gold_Futures_COMEX long (risk 2,061)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT long (risk 2,118); German_Long_Bund short (risk 2,097); Gold_Futures_COMEX long (risk 2,076)</t>
         </is>
       </c>
       <c r="H164" t="inlineStr"/>
@@ -5189,13 +5189,13 @@
         <v>46204</v>
       </c>
       <c r="B165" s="5" t="n">
-        <v>216803.75</v>
+        <v>218315.24</v>
       </c>
       <c r="C165" s="5" t="n">
-        <v>16817.47</v>
+        <v>16934.71</v>
       </c>
       <c r="D165" s="5" t="n">
-        <v>199986.28</v>
+        <v>201380.53</v>
       </c>
       <c r="E165" t="n">
         <v>8</v>
@@ -5207,12 +5207,12 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini short (risk 2,041); Sugar_World_CSCE_Futures short (risk 2,020)</t>
+          <t>Dow_Futures_E_mini short (risk 2,055); Sugar_World_CSCE_Futures short (risk 2,034)</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures stop (-2,173)</t>
+          <t>NY_Platinum_Futures stop (-2,188)</t>
         </is>
       </c>
     </row>
@@ -5221,13 +5221,13 @@
         <v>46205</v>
       </c>
       <c r="B166" s="5" t="n">
-        <v>231751.06</v>
+        <v>233366.76</v>
       </c>
       <c r="C166" s="5" t="n">
-        <v>12650.49</v>
+        <v>12738.69</v>
       </c>
       <c r="D166" s="5" t="n">
-        <v>219100.56</v>
+        <v>220628.07</v>
       </c>
       <c r="E166" t="n">
         <v>6</v>
@@ -5240,7 +5240,7 @@
       <c r="G166" t="inlineStr"/>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini stop (-2,063); US_Dollar_Index_Futures bearish_reversal (+17,010)</t>
+          <t>Dow_Futures_E_mini stop (-2,077); US_Dollar_Index_Futures bearish_reversal (+17,129)</t>
         </is>
       </c>
     </row>
@@ -5249,13 +5249,13 @@
         <v>46206</v>
       </c>
       <c r="B167" s="5" t="n">
-        <v>231751.06</v>
+        <v>233366.76</v>
       </c>
       <c r="C167" s="5" t="n">
-        <v>12650.49</v>
+        <v>12738.69</v>
       </c>
       <c r="D167" s="5" t="n">
-        <v>219100.56</v>
+        <v>220628.07</v>
       </c>
       <c r="E167" t="n">
         <v>6</v>
@@ -5273,13 +5273,13 @@
         <v>46210</v>
       </c>
       <c r="B168" s="5" t="n">
-        <v>229419.92</v>
+        <v>231019.37</v>
       </c>
       <c r="C168" s="5" t="n">
-        <v>10630.17</v>
+        <v>10704.29</v>
       </c>
       <c r="D168" s="5" t="n">
-        <v>218789.74</v>
+        <v>220315.08</v>
       </c>
       <c r="E168" t="n">
         <v>5</v>
@@ -5292,7 +5292,7 @@
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Sugar_World_CSCE_Futures stop (-2,331)</t>
+          <t>Sugar_World_CSCE_Futures stop (-2,347)</t>
         </is>
       </c>
     </row>
@@ -5301,13 +5301,13 @@
         <v>46211</v>
       </c>
       <c r="B169" s="5" t="n">
-        <v>263898.32</v>
+        <v>265738.14</v>
       </c>
       <c r="C169" s="5" t="n">
-        <v>10798.74</v>
+        <v>10874.02</v>
       </c>
       <c r="D169" s="5" t="n">
-        <v>253099.58</v>
+        <v>254864.12</v>
       </c>
       <c r="E169" t="n">
         <v>5</v>
@@ -5319,12 +5319,12 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Live_Cattle_Futures_CME long (risk 2,188); NY_Natural_Gas_Futures short (risk 2,166)</t>
+          <t>Live_Cattle_Futures_CME long (risk 2,203); NY_Natural_Gas_Futures short (risk 2,181)</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT bullish_reversal (+21,442); German_Long_Bund bearish_reversal (+13,036)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT bullish_reversal (+21,592); German_Long_Bund bearish_reversal (+13,127)</t>
         </is>
       </c>
     </row>
@@ -5333,13 +5333,13 @@
         <v>46212</v>
       </c>
       <c r="B170" s="5" t="n">
-        <v>271670.61</v>
+        <v>273564.62</v>
       </c>
       <c r="C170" s="5" t="n">
-        <v>8632.719999999999</v>
+        <v>8692.9</v>
       </c>
       <c r="D170" s="5" t="n">
-        <v>263037.89</v>
+        <v>264871.72</v>
       </c>
       <c r="E170" t="n">
         <v>4</v>
@@ -5352,7 +5352,7 @@
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures bearish_reversal (+7,772)</t>
+          <t>NY_Natural_Gas_Futures bearish_reversal (+7,826)</t>
         </is>
       </c>
     </row>
@@ -5361,13 +5361,13 @@
         <v>46213</v>
       </c>
       <c r="B171" s="5" t="n">
-        <v>269378.53</v>
+        <v>271256.55</v>
       </c>
       <c r="C171" s="5" t="n">
-        <v>6444.82</v>
+        <v>6489.75</v>
       </c>
       <c r="D171" s="5" t="n">
-        <v>262933.71</v>
+        <v>264766.8</v>
       </c>
       <c r="E171" t="n">
         <v>3</v>
@@ -5380,7 +5380,7 @@
       <c r="G171" t="inlineStr"/>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Live_Cattle_Futures_CME stop (-2,292)</t>
+          <t>Live_Cattle_Futures_CME stop (-2,308)</t>
         </is>
       </c>
     </row>
@@ -5389,13 +5389,13 @@
         <v>46216</v>
       </c>
       <c r="B172" s="5" t="n">
-        <v>269378.53</v>
+        <v>271256.55</v>
       </c>
       <c r="C172" s="5" t="n">
-        <v>9074.16</v>
+        <v>9137.42</v>
       </c>
       <c r="D172" s="5" t="n">
-        <v>260304.37</v>
+        <v>262119.14</v>
       </c>
       <c r="E172" t="n">
         <v>4</v>
@@ -5407,7 +5407,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 2,629)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 2,648)</t>
         </is>
       </c>
       <c r="H172" t="inlineStr"/>
@@ -5417,13 +5417,13 @@
         <v>46217</v>
       </c>
       <c r="B173" s="5" t="n">
-        <v>306315.62</v>
+        <v>308451.17</v>
       </c>
       <c r="C173" s="5" t="n">
-        <v>6904.74</v>
+        <v>6952.88</v>
       </c>
       <c r="D173" s="5" t="n">
-        <v>299410.88</v>
+        <v>301498.29</v>
       </c>
       <c r="E173" t="n">
         <v>3</v>
@@ -5436,7 +5436,7 @@
       <c r="G173" t="inlineStr"/>
       <c r="H173" t="inlineStr">
         <is>
-          <t>NY_Palladium_Futures bullish_reversal (+36,937)</t>
+          <t>NY_Palladium_Futures bullish_reversal (+37,195)</t>
         </is>
       </c>
     </row>
@@ -5445,13 +5445,13 @@
         <v>46218</v>
       </c>
       <c r="B174" s="5" t="n">
-        <v>303556.44</v>
+        <v>305672.75</v>
       </c>
       <c r="C174" s="5" t="n">
-        <v>4275.4</v>
+        <v>4305.21</v>
       </c>
       <c r="D174" s="5" t="n">
-        <v>299281.04</v>
+        <v>301367.54</v>
       </c>
       <c r="E174" t="n">
         <v>2</v>
@@ -5464,7 +5464,7 @@
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT stop (-2,759)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT stop (-2,778)</t>
         </is>
       </c>
     </row>
@@ -5473,13 +5473,13 @@
         <v>46219</v>
       </c>
       <c r="B175" s="5" t="n">
-        <v>303556.44</v>
+        <v>305672.75</v>
       </c>
       <c r="C175" s="5" t="n">
-        <v>4275.4</v>
+        <v>4305.21</v>
       </c>
       <c r="D175" s="5" t="n">
-        <v>299281.04</v>
+        <v>301367.54</v>
       </c>
       <c r="E175" t="n">
         <v>2</v>
@@ -5497,13 +5497,13 @@
         <v>46220</v>
       </c>
       <c r="B176" s="5" t="n">
-        <v>303556.44</v>
+        <v>305672.75</v>
       </c>
       <c r="C176" s="5" t="n">
-        <v>4275.4</v>
+        <v>4305.21</v>
       </c>
       <c r="D176" s="5" t="n">
-        <v>299281.04</v>
+        <v>301367.54</v>
       </c>
       <c r="E176" t="n">
         <v>2</v>
@@ -5521,13 +5521,13 @@
         <v>46223</v>
       </c>
       <c r="B177" s="5" t="n">
-        <v>303556.44</v>
+        <v>305672.75</v>
       </c>
       <c r="C177" s="5" t="n">
-        <v>4275.4</v>
+        <v>4305.21</v>
       </c>
       <c r="D177" s="5" t="n">
-        <v>299281.04</v>
+        <v>301367.54</v>
       </c>
       <c r="E177" t="n">
         <v>2</v>
@@ -5545,13 +5545,13 @@
         <v>46224</v>
       </c>
       <c r="B178" s="5" t="n">
-        <v>303556.44</v>
+        <v>305672.75</v>
       </c>
       <c r="C178" s="5" t="n">
-        <v>4275.4</v>
+        <v>4305.21</v>
       </c>
       <c r="D178" s="5" t="n">
-        <v>299281.04</v>
+        <v>301367.54</v>
       </c>
       <c r="E178" t="n">
         <v>2</v>
@@ -5569,13 +5569,13 @@
         <v>46225</v>
       </c>
       <c r="B179" s="5" t="n">
-        <v>303556.44</v>
+        <v>305672.75</v>
       </c>
       <c r="C179" s="5" t="n">
-        <v>4275.4</v>
+        <v>4305.21</v>
       </c>
       <c r="D179" s="5" t="n">
-        <v>299281.04</v>
+        <v>301367.54</v>
       </c>
       <c r="E179" t="n">
         <v>2</v>
@@ -5593,13 +5593,13 @@
         <v>46226</v>
       </c>
       <c r="B180" s="5" t="n">
-        <v>303541.24</v>
+        <v>305657.44</v>
       </c>
       <c r="C180" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D180" s="5" t="n">
-        <v>303541.24</v>
+        <v>305657.44</v>
       </c>
       <c r="E180" t="n">
         <v>0</v>
@@ -7282,7 +7282,7 @@
         <v>17302.74</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>169384.34</v>
+        <v>170533.66</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         <v>-1222.09</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>153743.88</v>
+        <v>154905.87</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -7561,14 +7561,22 @@
           <t>2026-04-17</t>
         </is>
       </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>0.032</v>
+        <v>0.065</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.032</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="I38" s="5" t="n">
         <v>120072.03</v>
@@ -7576,15 +7584,15 @@
       <c r="J38" s="5" t="n">
         <v>1200.72</v>
       </c>
-      <c r="K38" s="7" t="n">
-        <v>-38.73</v>
+      <c r="K38" s="6" t="n">
+        <v>1123.25</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>154965.97</v>
+        <v>156127.96</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>open_at_end</t>
+          <t>data_end</t>
         </is>
       </c>
     </row>
@@ -7622,16 +7630,16 @@
         <v>-1.066</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>152574.51</v>
+        <v>153736.5</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>1525.75</v>
+        <v>1537.36</v>
       </c>
       <c r="K39" s="7" t="n">
-        <v>-1625.79</v>
+        <v>-1638.18</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>152118.09</v>
+        <v>153267.7</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
@@ -7673,16 +7681,16 @@
         <v>-1.008</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>151039.52</v>
+        <v>152189.89</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>1510.4</v>
+        <v>1521.9</v>
       </c>
       <c r="K40" s="7" t="n">
-        <v>-1522.83</v>
+        <v>-1534.42</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>147322.32</v>
+        <v>148435.4</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
@@ -7724,16 +7732,16 @@
         <v>-1.002</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>149529.13</v>
+        <v>150667.99</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>1495.29</v>
+        <v>1506.68</v>
       </c>
       <c r="K41" s="7" t="n">
-        <v>-1498.87</v>
+        <v>-1510.29</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>150619.22</v>
+        <v>151757.41</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -7775,16 +7783,16 @@
         <v>6.225</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>148033.84</v>
+        <v>149161.31</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>1480.34</v>
+        <v>1491.61</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>9214.700000000001</v>
+        <v>9284.889999999999</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>155132.38</v>
+        <v>156304.94</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -7826,16 +7834,16 @@
         <v>-1.211</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>146553.5</v>
+        <v>147669.7</v>
       </c>
       <c r="J43" s="5" t="n">
-        <v>1465.53</v>
+        <v>1476.7</v>
       </c>
       <c r="K43" s="7" t="n">
-        <v>-1774.07</v>
+        <v>-1787.58</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>148845.15</v>
+        <v>149969.83</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -7877,16 +7885,16 @@
         <v>-1.108</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>144984.33</v>
+        <v>146088.58</v>
       </c>
       <c r="J44" s="5" t="n">
-        <v>1449.84</v>
+        <v>1460.89</v>
       </c>
       <c r="K44" s="7" t="n">
-        <v>-1606.58</v>
+        <v>-1618.82</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>153525.79</v>
+        <v>154686.12</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
@@ -7928,16 +7936,16 @@
         <v>6.688</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>143534.49</v>
+        <v>144627.7</v>
       </c>
       <c r="J45" s="5" t="n">
-        <v>1435.34</v>
+        <v>1446.28</v>
       </c>
       <c r="K45" s="6" t="n">
-        <v>9599.59</v>
+        <v>9672.700000000001</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>177479.28</v>
+        <v>178690.26</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
@@ -7979,16 +7987,16 @@
         <v>-1.016</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>142099.15</v>
+        <v>143181.42</v>
       </c>
       <c r="J46" s="5" t="n">
-        <v>1420.99</v>
+        <v>1431.81</v>
       </c>
       <c r="K46" s="7" t="n">
-        <v>-1444.19</v>
+        <v>-1455.19</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>152081.6</v>
+        <v>153230.93</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
@@ -8030,16 +8038,16 @@
         <v>-1.001</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>140369.62</v>
+        <v>141438.72</v>
       </c>
       <c r="J47" s="5" t="n">
-        <v>1403.7</v>
+        <v>1414.39</v>
       </c>
       <c r="K47" s="7" t="n">
-        <v>-1404.65</v>
+        <v>-1415.35</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>145917.67</v>
+        <v>147020.05</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
@@ -8081,16 +8089,16 @@
         <v>22</v>
       </c>
       <c r="I48" s="5" t="n">
-        <v>138953.49</v>
+        <v>140011.81</v>
       </c>
       <c r="J48" s="5" t="n">
-        <v>1389.53</v>
+        <v>1400.12</v>
       </c>
       <c r="K48" s="6" t="n">
-        <v>30569.74</v>
+        <v>30802.57</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>203182.76</v>
+        <v>204592.35</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
@@ -8132,16 +8140,16 @@
         <v>11.171</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>137563</v>
+        <v>138610.73</v>
       </c>
       <c r="J49" s="5" t="n">
-        <v>1375.63</v>
+        <v>1386.11</v>
       </c>
       <c r="K49" s="6" t="n">
-        <v>15367.43</v>
+        <v>15484.48</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>218550.19</v>
+        <v>220076.83</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
@@ -8183,16 +8191,16 @@
         <v>-1.026</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>146702.48</v>
+        <v>147819.81</v>
       </c>
       <c r="J50" s="5" t="n">
-        <v>1467.02</v>
+        <v>1478.2</v>
       </c>
       <c r="K50" s="7" t="n">
-        <v>-1504.64</v>
+        <v>-1516.1</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>167879.7</v>
+        <v>169017.56</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
@@ -8234,16 +8242,16 @@
         <v>-1.014</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>145235.45</v>
+        <v>146341.61</v>
       </c>
       <c r="J51" s="5" t="n">
-        <v>1452.35</v>
+        <v>1463.42</v>
       </c>
       <c r="K51" s="7" t="n">
-        <v>-1472.32</v>
+        <v>-1483.53</v>
       </c>
       <c r="L51" s="5" t="n">
-        <v>176006.96</v>
+        <v>177206.73</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -8285,16 +8293,16 @@
         <v>-1.032</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>162226.83</v>
+        <v>163321.65</v>
       </c>
       <c r="J52" s="5" t="n">
-        <v>1622.27</v>
+        <v>1633.22</v>
       </c>
       <c r="K52" s="7" t="n">
-        <v>-1674.18</v>
+        <v>-1685.48</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>174332.78</v>
+        <v>175521.25</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
@@ -8336,16 +8344,16 @@
         <v>-1.002</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>171619.53</v>
+        <v>172787.29</v>
       </c>
       <c r="J53" s="5" t="n">
-        <v>1716.2</v>
+        <v>1727.87</v>
       </c>
       <c r="K53" s="7" t="n">
-        <v>-1719.77</v>
+        <v>-1731.47</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>172613.01</v>
+        <v>173789.78</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
@@ -8387,16 +8395,16 @@
         <v>10.11</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>169847.85</v>
+        <v>171003.56</v>
       </c>
       <c r="J54" s="5" t="n">
-        <v>1698.48</v>
+        <v>1710.04</v>
       </c>
       <c r="K54" s="6" t="n">
-        <v>17170.94</v>
+        <v>17287.78</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>235721.13</v>
+        <v>237364.61</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
@@ -8438,16 +8446,16 @@
         <v>-1.021</v>
       </c>
       <c r="I55" s="5" t="n">
-        <v>216851.71</v>
+        <v>218366.79</v>
       </c>
       <c r="J55" s="5" t="n">
-        <v>2168.52</v>
+        <v>2183.67</v>
       </c>
       <c r="K55" s="7" t="n">
-        <v>-2213</v>
+        <v>-2228.46</v>
       </c>
       <c r="L55" s="5" t="n">
-        <v>229180.82</v>
+        <v>230778.6</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
@@ -8489,16 +8497,16 @@
         <v>-1.024</v>
       </c>
       <c r="I56" s="5" t="n">
-        <v>214683.19</v>
+        <v>216183.13</v>
       </c>
       <c r="J56" s="5" t="n">
-        <v>2146.83</v>
+        <v>2161.83</v>
       </c>
       <c r="K56" s="7" t="n">
-        <v>-2197.35</v>
+        <v>-2212.7</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>233523.79</v>
+        <v>235151.91</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
@@ -8540,16 +8548,16 @@
         <v>-1.002</v>
       </c>
       <c r="I57" s="5" t="n">
-        <v>212536.36</v>
+        <v>214021.3</v>
       </c>
       <c r="J57" s="5" t="n">
-        <v>2125.36</v>
+        <v>2140.21</v>
       </c>
       <c r="K57" s="7" t="n">
-        <v>-2129.97</v>
+        <v>-2144.85</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>231393.82</v>
+        <v>233007.06</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
@@ -8591,16 +8599,16 @@
         <v>-1.038</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>229229.91</v>
+        <v>230828.03</v>
       </c>
       <c r="J58" s="5" t="n">
-        <v>2292.3</v>
+        <v>2308.28</v>
       </c>
       <c r="K58" s="7" t="n">
-        <v>-2378.8</v>
+        <v>-2395.39</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>219676.91</v>
+        <v>221208.44</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
@@ -8642,16 +8650,16 @@
         <v>-1.007</v>
       </c>
       <c r="I59" s="5" t="n">
-        <v>226888.52</v>
+        <v>228470.32</v>
       </c>
       <c r="J59" s="5" t="n">
-        <v>2268.89</v>
+        <v>2284.7</v>
       </c>
       <c r="K59" s="7" t="n">
-        <v>-2285.66</v>
+        <v>-2301.6</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>226895.16</v>
+        <v>228477</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
@@ -8693,16 +8701,16 @@
         <v>-1.03</v>
       </c>
       <c r="I60" s="5" t="n">
-        <v>224619.63</v>
+        <v>226185.61</v>
       </c>
       <c r="J60" s="5" t="n">
-        <v>2246.2</v>
+        <v>2261.86</v>
       </c>
       <c r="K60" s="7" t="n">
-        <v>-2312.75</v>
+        <v>-2328.87</v>
       </c>
       <c r="L60" s="5" t="n">
-        <v>224582.41</v>
+        <v>226148.13</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
@@ -8744,16 +8752,16 @@
         <v>-1.007</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>222356.66</v>
+        <v>223906.87</v>
       </c>
       <c r="J61" s="5" t="n">
-        <v>2223.57</v>
+        <v>2239.07</v>
       </c>
       <c r="K61" s="7" t="n">
-        <v>-2239.2</v>
+        <v>-2254.81</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>223627.41</v>
+        <v>225186.48</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
@@ -8795,16 +8803,16 @@
         <v>-1.148</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>220066.54</v>
+        <v>221600.78</v>
       </c>
       <c r="J62" s="5" t="n">
-        <v>2200.67</v>
+        <v>2216.01</v>
       </c>
       <c r="K62" s="7" t="n">
-        <v>-2526.69</v>
+        <v>-2544.31</v>
       </c>
       <c r="L62" s="5" t="n">
-        <v>222055.72</v>
+        <v>223603.82</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
@@ -8846,16 +8854,16 @@
         <v>4.894</v>
       </c>
       <c r="I63" s="5" t="n">
-        <v>217865.87</v>
+        <v>219384.77</v>
       </c>
       <c r="J63" s="5" t="n">
-        <v>2178.66</v>
+        <v>2193.85</v>
       </c>
       <c r="K63" s="6" t="n">
-        <v>10662.13</v>
+        <v>10736.46</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>230339.05</v>
+        <v>231944.9</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
@@ -8897,16 +8905,16 @@
         <v>-1.014</v>
       </c>
       <c r="I64" s="5" t="n">
-        <v>215274.69</v>
+        <v>216775.52</v>
       </c>
       <c r="J64" s="5" t="n">
-        <v>2152.75</v>
+        <v>2167.76</v>
       </c>
       <c r="K64" s="7" t="n">
-        <v>-2181.94</v>
+        <v>-2197.15</v>
       </c>
       <c r="L64" s="5" t="n">
-        <v>228157.11</v>
+        <v>229747.75</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
@@ -8948,16 +8956,16 @@
         <v>-1.014</v>
       </c>
       <c r="I65" s="5" t="n">
-        <v>225933.54</v>
+        <v>227508.69</v>
       </c>
       <c r="J65" s="5" t="n">
-        <v>2259.34</v>
+        <v>2275.09</v>
       </c>
       <c r="K65" s="7" t="n">
-        <v>-2290.5</v>
+        <v>-2306.47</v>
       </c>
       <c r="L65" s="5" t="n">
-        <v>225866.61</v>
+        <v>227441.29</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
@@ -8999,16 +9007,16 @@
         <v>-1.02</v>
       </c>
       <c r="I66" s="5" t="n">
-        <v>223674.21</v>
+        <v>225233.6</v>
       </c>
       <c r="J66" s="5" t="n">
-        <v>2236.74</v>
+        <v>2252.34</v>
       </c>
       <c r="K66" s="7" t="n">
-        <v>-2280.39</v>
+        <v>-2296.28</v>
       </c>
       <c r="L66" s="5" t="n">
-        <v>221347.03</v>
+        <v>222890.19</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
@@ -9042,16 +9050,16 @@
         <v>-0.004</v>
       </c>
       <c r="I67" s="5" t="n">
-        <v>221406.3</v>
+        <v>222949.88</v>
       </c>
       <c r="J67" s="5" t="n">
-        <v>2214.06</v>
+        <v>2229.5</v>
       </c>
       <c r="K67" s="7" t="n">
-        <v>-8.02</v>
+        <v>-8.08</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>303548.42</v>
+        <v>305664.67</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
@@ -9093,16 +9101,16 @@
         <v>-1.082</v>
       </c>
       <c r="I68" s="5" t="n">
-        <v>219132.96</v>
+        <v>220660.7</v>
       </c>
       <c r="J68" s="5" t="n">
-        <v>2191.33</v>
+        <v>2206.61</v>
       </c>
       <c r="K68" s="7" t="n">
-        <v>-2370.21</v>
+        <v>-2386.74</v>
       </c>
       <c r="L68" s="5" t="n">
-        <v>218976.81</v>
+        <v>220503.46</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
@@ -9144,16 +9152,16 @@
         <v>17.026</v>
       </c>
       <c r="I69" s="5" t="n">
-        <v>216941.63</v>
+        <v>218454.09</v>
       </c>
       <c r="J69" s="5" t="n">
-        <v>2169.42</v>
+        <v>2184.54</v>
       </c>
       <c r="K69" s="6" t="n">
-        <v>36937.1</v>
+        <v>37194.61</v>
       </c>
       <c r="L69" s="5" t="n">
-        <v>306315.62</v>
+        <v>308451.17</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
@@ -9195,16 +9203,16 @@
         <v>-1.012</v>
       </c>
       <c r="I70" s="5" t="n">
-        <v>214772.22</v>
+        <v>216269.55</v>
       </c>
       <c r="J70" s="5" t="n">
-        <v>2147.72</v>
+        <v>2162.7</v>
       </c>
       <c r="K70" s="7" t="n">
-        <v>-2173.06</v>
+        <v>-2188.21</v>
       </c>
       <c r="L70" s="5" t="n">
-        <v>216803.75</v>
+        <v>218315.24</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
@@ -9246,16 +9254,16 @@
         <v>8</v>
       </c>
       <c r="I71" s="5" t="n">
-        <v>212624.5</v>
+        <v>214106.85</v>
       </c>
       <c r="J71" s="5" t="n">
-        <v>2126.24</v>
+        <v>2141.07</v>
       </c>
       <c r="K71" s="6" t="n">
-        <v>17009.98</v>
+        <v>17128.57</v>
       </c>
       <c r="L71" s="5" t="n">
-        <v>231751.06</v>
+        <v>233366.76</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
@@ -9297,16 +9305,16 @@
         <v>10.195</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>210319.37</v>
+        <v>211785.65</v>
       </c>
       <c r="J72" s="5" t="n">
-        <v>2103.19</v>
+        <v>2117.86</v>
       </c>
       <c r="K72" s="6" t="n">
-        <v>21442.31</v>
+        <v>21591.8</v>
       </c>
       <c r="L72" s="5" t="n">
-        <v>250862.23</v>
+        <v>252611.17</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
@@ -9348,16 +9356,16 @@
         <v>6.261</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>208216.17</v>
+        <v>209667.8</v>
       </c>
       <c r="J73" s="5" t="n">
-        <v>2082.16</v>
+        <v>2096.68</v>
       </c>
       <c r="K73" s="6" t="n">
-        <v>13036.09</v>
+        <v>13126.97</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>263898.32</v>
+        <v>265738.14</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
@@ -9391,16 +9399,16 @@
         <v>-0.003</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>206134.01</v>
+        <v>207571.12</v>
       </c>
       <c r="J74" s="5" t="n">
-        <v>2061.34</v>
+        <v>2075.71</v>
       </c>
       <c r="K74" s="7" t="n">
-        <v>-7.18</v>
+        <v>-7.23</v>
       </c>
       <c r="L74" s="5" t="n">
-        <v>303541.24</v>
+        <v>305657.44</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
@@ -9442,16 +9450,16 @@
         <v>-1.011</v>
       </c>
       <c r="I75" s="5" t="n">
-        <v>204072.67</v>
+        <v>205495.41</v>
       </c>
       <c r="J75" s="5" t="n">
-        <v>2040.73</v>
+        <v>2054.95</v>
       </c>
       <c r="K75" s="7" t="n">
-        <v>-2062.67</v>
+        <v>-2077.05</v>
       </c>
       <c r="L75" s="5" t="n">
-        <v>214741.08</v>
+        <v>216238.19</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
@@ -9493,16 +9501,16 @@
         <v>-1.154</v>
       </c>
       <c r="I76" s="5" t="n">
-        <v>202031.94</v>
+        <v>203440.45</v>
       </c>
       <c r="J76" s="5" t="n">
-        <v>2020.32</v>
+        <v>2034.4</v>
       </c>
       <c r="K76" s="7" t="n">
-        <v>-2331.14</v>
+        <v>-2347.39</v>
       </c>
       <c r="L76" s="5" t="n">
-        <v>229419.92</v>
+        <v>231019.37</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
@@ -9544,16 +9552,16 @@
         <v>-1.048</v>
       </c>
       <c r="I77" s="5" t="n">
-        <v>218789.74</v>
+        <v>220315.08</v>
       </c>
       <c r="J77" s="5" t="n">
-        <v>2187.9</v>
+        <v>2203.15</v>
       </c>
       <c r="K77" s="7" t="n">
-        <v>-2292.08</v>
+        <v>-2308.06</v>
       </c>
       <c r="L77" s="5" t="n">
-        <v>269378.53</v>
+        <v>271256.55</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
@@ -9595,16 +9603,16 @@
         <v>3.588</v>
       </c>
       <c r="I78" s="5" t="n">
-        <v>216601.85</v>
+        <v>218111.93</v>
       </c>
       <c r="J78" s="5" t="n">
-        <v>2166.02</v>
+        <v>2181.12</v>
       </c>
       <c r="K78" s="6" t="n">
-        <v>7772.29</v>
+        <v>7826.48</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>271670.61</v>
+        <v>273564.62</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
@@ -9646,16 +9654,16 @@
         <v>-1.049</v>
       </c>
       <c r="I79" s="5" t="n">
-        <v>262933.71</v>
+        <v>264766.8</v>
       </c>
       <c r="J79" s="5" t="n">
-        <v>2629.34</v>
+        <v>2647.67</v>
       </c>
       <c r="K79" s="7" t="n">
-        <v>-2759.18</v>
+        <v>-2778.42</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>303556.44</v>
+        <v>305672.75</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>

--- a/output/slowfix_portfolio_daily.xlsx
+++ b/output/slowfix_portfolio_daily.xlsx
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -691,168 +691,180 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>closed trades</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>76</v>
+          <t>return / drawdown</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>16.2x</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>win rate</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>27.6%</t>
-        </is>
+          <t>closed trades</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>76</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>average hold</t>
+          <t>win rate</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>3.8 bars</t>
+          <t>27.6%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>average winner</t>
+          <t>average hold</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>+9.44R  (best +25.82R)</t>
+          <t>3.8 bars</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>longest win streak</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>3</v>
+          <t>average winner</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>+9.44R  (best +25.82R)</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>longest loss streak</t>
+          <t>longest win streak</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>average win</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>13,957  (+9.44%)</t>
-        </is>
+          <t>longest loss streak</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>average loss</t>
+          <t>average win</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-1,589  (-1.05%)</t>
+          <t>13,957  (+9.44%)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>markets with trades</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>28</v>
+          <t>average loss</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>-1,589  (-1.05%)</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>max concurrent positions</t>
+          <t>markets with trades</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>time in market</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>87% of trading days</t>
-        </is>
+          <t>max concurrent positions</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>peak risk committed</t>
+          <t>time in market</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>7.8% of live balance</t>
+          <t>87% of trading days</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>window</t>
+          <t>peak risk committed</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-07-23</t>
+          <t>7.8% of live balance</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>risk per trade</t>
+          <t>window</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1.0% of liquid capital</t>
+          <t>2025-12-18 -&gt; 2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>risk per trade</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1.0% of liquid capital</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
           <t>slippage model</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>entry 1t, target 1t, stop 3t</t>
         </is>

--- a/output/slowfix_portfolio_daily.xlsx
+++ b/output/slowfix_portfolio_daily.xlsx
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -793,78 +793,88 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>markets with trades</t>
+          <t>markets tested</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>max concurrent positions</t>
+          <t>markets with trades</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>time in market</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>87% of trading days</t>
-        </is>
+          <t>max concurrent positions</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>peak risk committed</t>
+          <t>time in market</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>7.8% of live balance</t>
+          <t>87% of trading days</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>window</t>
+          <t>peak risk committed</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-07-23</t>
+          <t>7.8% of live balance</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>risk per trade</t>
+          <t>window</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1.0% of liquid capital</t>
+          <t>2025-12-18 -&gt; 2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>risk per trade</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1.0% of liquid capital</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
           <t>slippage model</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>entry 1t, target 1t, stop 3t</t>
         </is>

--- a/output/slowfix_portfolio_daily.xlsx
+++ b/output/slowfix_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$180</f>
+              <f>'equity_curve'!$A$2:$A$181</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$180</f>
+              <f>'equity_curve'!$B$2:$B$181</f>
             </numRef>
           </val>
         </ser>
@@ -612,7 +612,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>target = the first opposite reversal beyond entry, no 5R cap</t>
+          <t>target = the first opposite reversal beyond entry, no cap</t>
         </is>
       </c>
     </row>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>305,657.44</t>
+          <t>305,525.99</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+205.66%</t>
+          <t>+205.53%</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5,197  (9.5 pts of return)</t>
+          <t>5,328  (9.6 pts of return)</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-07-23</t>
+          <t>2025-12-18 -&gt; 2026-07-24</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H180"/>
+  <dimension ref="A1:H181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5615,22 +5615,50 @@
         <v>46226</v>
       </c>
       <c r="B180" s="5" t="n">
-        <v>305657.44</v>
+        <v>305672.75</v>
       </c>
       <c r="C180" s="5" t="n">
+        <v>4305.21</v>
+      </c>
+      <c r="D180" s="5" t="n">
+        <v>301367.54</v>
+      </c>
+      <c r="E180" t="n">
+        <v>2</v>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>EURO_Futures, Gold_Futures_COMEX</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="4" t="n">
+        <v>46227</v>
+      </c>
+      <c r="B181" s="5" t="n">
+        <v>305525.99</v>
+      </c>
+      <c r="C181" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D180" s="5" t="n">
-        <v>305657.44</v>
-      </c>
-      <c r="E180" t="n">
+      <c r="D181" s="5" t="n">
+        <v>305525.99</v>
+      </c>
+      <c r="E181" t="n">
         <v>0</v>
       </c>
-      <c r="F180" t="inlineStr"/>
-      <c r="G180" t="inlineStr"/>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>EURO_Futures open_at_end (open-&gt;closed 0); Gold_Futures_COMEX open_at_end (open-&gt;closed 0)</t>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 3,014); Corn_CBOT_Futures short (risk 2,984)</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT open_at_end (open-&gt;closed 0); Corn_CBOT_Futures open_at_end (open-&gt;closed 0); EURO_Futures open_at_end (open-&gt;closed 0); Gold_Futures_COMEX open_at_end (open-&gt;closed 0)</t>
         </is>
       </c>
     </row>
@@ -5646,7 +5674,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M79"/>
+  <dimension ref="A1:M81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -9081,7 +9109,7 @@
         <v>-8.08</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>305664.67</v>
+        <v>305533.22</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
@@ -9430,7 +9458,7 @@
         <v>-7.23</v>
       </c>
       <c r="L74" s="5" t="n">
-        <v>305657.44</v>
+        <v>305525.99</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
@@ -9690,6 +9718,92 @@
       <c r="M79" t="inlineStr">
         <is>
           <t>stop</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="H80" t="n">
+        <v>-0.019</v>
+      </c>
+      <c r="I80" s="5" t="n">
+        <v>301367.54</v>
+      </c>
+      <c r="J80" s="5" t="n">
+        <v>3013.68</v>
+      </c>
+      <c r="K80" s="7" t="n">
+        <v>-56.86</v>
+      </c>
+      <c r="L80" s="5" t="n">
+        <v>305615.89</v>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Corn_CBOT_Futures</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="H81" t="n">
+        <v>-0.025</v>
+      </c>
+      <c r="I81" s="5" t="n">
+        <v>298353.87</v>
+      </c>
+      <c r="J81" s="5" t="n">
+        <v>2983.54</v>
+      </c>
+      <c r="K81" s="7" t="n">
+        <v>-74.59</v>
+      </c>
+      <c r="L81" s="5" t="n">
+        <v>305541.3</v>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
         </is>
       </c>
     </row>

--- a/output/slowfix_portfolio_daily.xlsx
+++ b/output/slowfix_portfolio_daily.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>305,525.99</t>
+          <t>488,249.74</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+205.53%</t>
+          <t>+388.25%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>315,134  (+215.13%)</t>
+          <t>511,213  (+411.21%)</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5,328  (9.6 pts of return)</t>
+          <t>10,198  (23.0 pts of return)</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12.66%</t>
+          <t>19.18%</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>16.2x</t>
+          <t>20.2x</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>13,957  (+9.44%)</t>
+          <t>26,586  (+14.85%)</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-1,589  (-1.05%)</t>
+          <t>-3,086  (-1.65%)</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>7.8% of live balance</t>
+          <t>12.0% of live balance</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.0% of liquid capital</t>
+          <t>1.573% of liquid capital</t>
         </is>
       </c>
     </row>
@@ -954,10 +954,10 @@
         <v>100000</v>
       </c>
       <c r="C2" s="5" t="n">
-        <v>1000</v>
+        <v>1573</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX short (risk 1,000)</t>
+          <t>Gold_Futures_COMEX short (risk 1,573)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -979,13 +979,13 @@
         <v>46010</v>
       </c>
       <c r="B3" s="5" t="n">
-        <v>111493.95</v>
+        <v>118079.99</v>
       </c>
       <c r="C3" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>111493.95</v>
+        <v>118079.99</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -994,7 +994,7 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX bearish_reversal (+11,494)</t>
+          <t>Gold_Futures_COMEX bearish_reversal (+18,080)</t>
         </is>
       </c>
     </row>
@@ -1003,13 +1003,13 @@
         <v>46011</v>
       </c>
       <c r="B4" s="5" t="n">
-        <v>111493.95</v>
+        <v>118079.99</v>
       </c>
       <c r="C4" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>111493.95</v>
+        <v>118079.99</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -1023,13 +1023,13 @@
         <v>46021</v>
       </c>
       <c r="B5" s="5" t="n">
-        <v>111493.95</v>
+        <v>118079.99</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1114.94</v>
+        <v>1857.4</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>110379.01</v>
+        <v>116222.59</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX short (risk 1,115)</t>
+          <t>Gold_Futures_COMEX short (risk 1,857)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -1051,13 +1051,13 @@
         <v>46023</v>
       </c>
       <c r="B6" s="5" t="n">
-        <v>111493.95</v>
+        <v>118079.99</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>1114.94</v>
+        <v>1857.4</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>110379.01</v>
+        <v>116222.59</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -1075,13 +1075,13 @@
         <v>46024</v>
       </c>
       <c r="B7" s="5" t="n">
-        <v>111493.95</v>
+        <v>118079.99</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1114.94</v>
+        <v>1857.4</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>110379.01</v>
+        <v>116222.59</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -1099,13 +1099,13 @@
         <v>46025</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>111493.95</v>
+        <v>118079.99</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>1114.94</v>
+        <v>1857.4</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>110379.01</v>
+        <v>116222.59</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
@@ -1123,13 +1123,13 @@
         <v>46026</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>111493.95</v>
+        <v>118079.99</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1114.94</v>
+        <v>1857.4</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>110379.01</v>
+        <v>116222.59</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -1147,13 +1147,13 @@
         <v>46027</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>110362.85</v>
+        <v>116195.67</v>
       </c>
       <c r="C10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>110362.85</v>
+        <v>116195.67</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -1162,7 +1162,7 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX stop (-1,131)</t>
+          <t>Gold_Futures_COMEX stop (-1,884)</t>
         </is>
       </c>
     </row>
@@ -1171,13 +1171,13 @@
         <v>46028</v>
       </c>
       <c r="B11" s="5" t="n">
-        <v>110362.85</v>
+        <v>116195.67</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>110362.85</v>
+        <v>116195.67</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -1191,13 +1191,13 @@
         <v>46029</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>110362.85</v>
+        <v>116195.67</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>2196.22</v>
+        <v>3626.77</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>108166.63</v>
+        <v>112568.9</v>
       </c>
       <c r="E12" t="n">
         <v>2</v>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Coffee_NYCSCE_Futures short (risk 1,104); S_P_500_Index short (risk 1,093)</t>
+          <t>Coffee_NYCSCE_Futures short (risk 1,828); S_P_500_Index short (risk 1,799)</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -1219,13 +1219,13 @@
         <v>46030</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>109250.5</v>
+        <v>114353.46</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1092.59</v>
+        <v>1799.01</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>108157.91</v>
+        <v>112554.46</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -1238,7 +1238,7 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Coffee_NYCSCE_Futures stop (-1,112)</t>
+          <t>Coffee_NYCSCE_Futures stop (-1,842)</t>
         </is>
       </c>
     </row>
@@ -1247,13 +1247,13 @@
         <v>46031</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>108152.62</v>
+        <v>112545.75</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>108152.62</v>
+        <v>112545.75</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -1262,7 +1262,7 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>S_P_500_Index stop (-1,098)</t>
+          <t>S_P_500_Index stop (-1,808)</t>
         </is>
       </c>
     </row>
@@ -1271,13 +1271,13 @@
         <v>46032</v>
       </c>
       <c r="B15" s="5" t="n">
-        <v>108152.62</v>
+        <v>112545.75</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>108152.62</v>
+        <v>112545.75</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -1291,13 +1291,13 @@
         <v>46033</v>
       </c>
       <c r="B16" s="5" t="n">
-        <v>108152.62</v>
+        <v>112545.75</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>108152.62</v>
+        <v>112545.75</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -1311,13 +1311,13 @@
         <v>46034</v>
       </c>
       <c r="B17" s="5" t="n">
-        <v>108152.62</v>
+        <v>112545.75</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>108152.62</v>
+        <v>112545.75</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -1331,13 +1331,13 @@
         <v>46035</v>
       </c>
       <c r="B18" s="5" t="n">
-        <v>108152.62</v>
+        <v>112545.75</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>1081.53</v>
+        <v>1770.34</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>107071.1</v>
+        <v>110775.41</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cocoa_NYCSCE_Futures long (risk 1,082)</t>
+          <t>Cocoa_NYCSCE_Futures long (risk 1,770)</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -1359,13 +1359,13 @@
         <v>46036</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>106979.05</v>
+        <v>110624.74</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>106979.05</v>
+        <v>110624.74</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -1374,7 +1374,7 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Cocoa_NYCSCE_Futures stop (-1,174)</t>
+          <t>Cocoa_NYCSCE_Futures stop (-1,921)</t>
         </is>
       </c>
     </row>
@@ -1383,13 +1383,13 @@
         <v>46037</v>
       </c>
       <c r="B20" s="5" t="n">
-        <v>106979.05</v>
+        <v>110624.74</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>106979.05</v>
+        <v>110624.74</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -1403,13 +1403,13 @@
         <v>46038</v>
       </c>
       <c r="B21" s="5" t="n">
-        <v>106979.05</v>
+        <v>110624.74</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>106979.05</v>
+        <v>110624.74</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>46039</v>
       </c>
       <c r="B22" s="5" t="n">
-        <v>106979.05</v>
+        <v>110624.74</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>106979.05</v>
+        <v>110624.74</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -1443,13 +1443,13 @@
         <v>46040</v>
       </c>
       <c r="B23" s="5" t="n">
-        <v>106979.05</v>
+        <v>110624.74</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>106979.05</v>
+        <v>110624.74</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -1463,13 +1463,13 @@
         <v>46041</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>106979.05</v>
+        <v>110624.74</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>106979.05</v>
+        <v>110624.74</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -1483,13 +1483,13 @@
         <v>46042</v>
       </c>
       <c r="B25" s="5" t="n">
-        <v>106979.05</v>
+        <v>110624.74</v>
       </c>
       <c r="C25" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>106979.05</v>
+        <v>110624.74</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -1503,13 +1503,13 @@
         <v>46043</v>
       </c>
       <c r="B26" s="5" t="n">
-        <v>106979.05</v>
+        <v>110624.74</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>1069.79</v>
+        <v>1740.13</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>105909.26</v>
+        <v>108884.61</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Coffee_NYCSCE_Futures long (risk 1,070)</t>
+          <t>Coffee_NYCSCE_Futures long (risk 1,740)</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
@@ -1531,13 +1531,13 @@
         <v>46044</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>106979.05</v>
+        <v>110624.74</v>
       </c>
       <c r="C27" s="5" t="n">
-        <v>1069.79</v>
+        <v>1740.13</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>105909.26</v>
+        <v>108884.61</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -1555,13 +1555,13 @@
         <v>46045</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>106979.05</v>
+        <v>110624.74</v>
       </c>
       <c r="C28" s="5" t="n">
-        <v>1069.79</v>
+        <v>1740.13</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>105909.26</v>
+        <v>108884.61</v>
       </c>
       <c r="E28" t="n">
         <v>1</v>
@@ -1579,13 +1579,13 @@
         <v>46046</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>106979.05</v>
+        <v>110624.74</v>
       </c>
       <c r="C29" s="5" t="n">
-        <v>1069.79</v>
+        <v>1740.13</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>105909.26</v>
+        <v>108884.61</v>
       </c>
       <c r="E29" t="n">
         <v>1</v>
@@ -1603,13 +1603,13 @@
         <v>46047</v>
       </c>
       <c r="B30" s="5" t="n">
-        <v>106979.05</v>
+        <v>110624.74</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>1069.79</v>
+        <v>1740.13</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>105909.26</v>
+        <v>108884.61</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
@@ -1627,13 +1627,13 @@
         <v>46048</v>
       </c>
       <c r="B31" s="5" t="n">
-        <v>106979.05</v>
+        <v>110624.74</v>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1069.79</v>
+        <v>1740.13</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>105909.26</v>
+        <v>108884.61</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
@@ -1651,13 +1651,13 @@
         <v>46049</v>
       </c>
       <c r="B32" s="5" t="n">
-        <v>111594.3</v>
+        <v>118131.92</v>
       </c>
       <c r="C32" s="5" t="n">
-        <v>1059.09</v>
+        <v>1712.75</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>110535.21</v>
+        <v>116419.17</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
@@ -1669,12 +1669,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>S_P_500_Index short (risk 1,059)</t>
+          <t>S_P_500_Index short (risk 1,713)</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Coffee_NYCSCE_Futures bullish_reversal (+4,615)</t>
+          <t>Coffee_NYCSCE_Futures bullish_reversal (+7,507)</t>
         </is>
       </c>
     </row>
@@ -1683,13 +1683,13 @@
         <v>46050</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>110528.62</v>
+        <v>116408.52</v>
       </c>
       <c r="C33" s="5" t="n">
-        <v>1105.35</v>
+        <v>1831.27</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>109423.26</v>
+        <v>114577.24</v>
       </c>
       <c r="E33" t="n">
         <v>1</v>
@@ -1701,12 +1701,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Teucrium_Wheat_Fund short (risk 1,105)</t>
+          <t>Teucrium_Wheat_Fund short (risk 1,831)</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>S_P_500_Index stop (-1,066)</t>
+          <t>S_P_500_Index stop (-1,723)</t>
         </is>
       </c>
     </row>
@@ -1715,13 +1715,13 @@
         <v>46051</v>
       </c>
       <c r="B34" s="5" t="n">
-        <v>109177.63</v>
+        <v>114170.29</v>
       </c>
       <c r="C34" s="5" t="n">
-        <v>3249.98</v>
+        <v>5322.3</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>105927.65</v>
+        <v>108848</v>
       </c>
       <c r="E34" t="n">
         <v>3</v>
@@ -1733,12 +1733,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ethereum_Per_USD_Binance long (risk 1,094); Live_Cattle_Futures_CME short (risk 1,083); S_P_500_Index short (risk 1,072)</t>
+          <t>Ethereum_Per_USD_Binance long (risk 1,802); Live_Cattle_Futures_CME short (risk 1,774); S_P_500_Index short (risk 1,746)</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Teucrium_Wheat_Fund stop (-1,351)</t>
+          <t>Teucrium_Wheat_Fund stop (-2,238)</t>
         </is>
       </c>
     </row>
@@ -1747,13 +1747,13 @@
         <v>46052</v>
       </c>
       <c r="B35" s="5" t="n">
-        <v>106859.97</v>
+        <v>110363.84</v>
       </c>
       <c r="C35" s="5" t="n">
-        <v>2131.73</v>
+        <v>3458.22</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>104728.24</v>
+        <v>106905.61</v>
       </c>
       <c r="E35" t="n">
         <v>2</v>
@@ -1765,12 +1765,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cocoa_NYCSCE_Futures long (risk 1,059)</t>
+          <t>Cocoa_NYCSCE_Futures long (risk 1,712)</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Ethereum_Per_USD_Binance stop (-1,170); Live_Cattle_Futures_CME stop (-1,148)</t>
+          <t>Ethereum_Per_USD_Binance stop (-1,927); Live_Cattle_Futures_CME stop (-1,880)</t>
         </is>
       </c>
     </row>
@@ -1779,13 +1779,13 @@
         <v>46053</v>
       </c>
       <c r="B36" s="5" t="n">
-        <v>106859.97</v>
+        <v>110363.84</v>
       </c>
       <c r="C36" s="5" t="n">
-        <v>2131.73</v>
+        <v>3458.22</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>104728.24</v>
+        <v>106905.61</v>
       </c>
       <c r="E36" t="n">
         <v>2</v>
@@ -1803,13 +1803,13 @@
         <v>46054</v>
       </c>
       <c r="B37" s="5" t="n">
-        <v>106859.97</v>
+        <v>110363.84</v>
       </c>
       <c r="C37" s="5" t="n">
-        <v>2131.73</v>
+        <v>3458.22</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>104728.24</v>
+        <v>106905.61</v>
       </c>
       <c r="E37" t="n">
         <v>2</v>
@@ -1827,13 +1827,13 @@
         <v>46055</v>
       </c>
       <c r="B38" s="5" t="n">
-        <v>106859.97</v>
+        <v>110363.84</v>
       </c>
       <c r="C38" s="5" t="n">
-        <v>3179.02</v>
+        <v>5139.85</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>103680.95</v>
+        <v>105223.99</v>
       </c>
       <c r="E38" t="n">
         <v>3</v>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance long (risk 1,047)</t>
+          <t>Bitcoin_Per_USD_Binance long (risk 1,682)</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
@@ -1855,13 +1855,13 @@
         <v>46056</v>
       </c>
       <c r="B39" s="5" t="n">
-        <v>104733.91</v>
+        <v>106925.92</v>
       </c>
       <c r="C39" s="5" t="n">
-        <v>2096.09</v>
+        <v>3367.35</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>102637.82</v>
+        <v>103558.57</v>
       </c>
       <c r="E39" t="n">
         <v>2</v>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>EURO_STOXX_50_Index short (risk 1,037)</t>
+          <t>EURO_STOXX_50_Index short (risk 1,655)</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance stop (-1,049); S_P_500_Index stop (-1,077)</t>
+          <t>Bitcoin_Per_USD_Binance stop (-1,685); S_P_500_Index stop (-1,753)</t>
         </is>
       </c>
     </row>
@@ -1887,13 +1887,13 @@
         <v>46057</v>
       </c>
       <c r="B40" s="5" t="n">
-        <v>104733.91</v>
+        <v>106925.92</v>
       </c>
       <c r="C40" s="5" t="n">
-        <v>2096.09</v>
+        <v>3367.35</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>102637.82</v>
+        <v>103558.57</v>
       </c>
       <c r="E40" t="n">
         <v>2</v>
@@ -1911,13 +1911,13 @@
         <v>46058</v>
       </c>
       <c r="B41" s="5" t="n">
-        <v>104733.91</v>
+        <v>106925.92</v>
       </c>
       <c r="C41" s="5" t="n">
-        <v>3122.46</v>
+        <v>4996.33</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>101611.44</v>
+        <v>101929.6</v>
       </c>
       <c r="E41" t="n">
         <v>3</v>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures long (risk 1,026)</t>
+          <t>NY_Copper_Futures long (risk 1,629)</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
@@ -1939,13 +1939,13 @@
         <v>46059</v>
       </c>
       <c r="B42" s="5" t="n">
-        <v>103702.78</v>
+        <v>105289.42</v>
       </c>
       <c r="C42" s="5" t="n">
-        <v>3112.2</v>
+        <v>4970.7</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>100590.58</v>
+        <v>100318.71</v>
       </c>
       <c r="E42" t="n">
         <v>3</v>
@@ -1957,12 +1957,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance long (risk 1,016)</t>
+          <t>Bitcoin_Per_USD_Binance long (risk 1,603)</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures stop (-1,031)</t>
+          <t>NY_Copper_Futures stop (-1,637)</t>
         </is>
       </c>
     </row>
@@ -1971,13 +1971,13 @@
         <v>46060</v>
       </c>
       <c r="B43" s="5" t="n">
-        <v>103702.78</v>
+        <v>105289.42</v>
       </c>
       <c r="C43" s="5" t="n">
-        <v>3112.2</v>
+        <v>4970.7</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>100590.58</v>
+        <v>100318.71</v>
       </c>
       <c r="E43" t="n">
         <v>3</v>
@@ -1995,13 +1995,13 @@
         <v>46061</v>
       </c>
       <c r="B44" s="5" t="n">
-        <v>103702.78</v>
+        <v>105289.42</v>
       </c>
       <c r="C44" s="5" t="n">
-        <v>3112.2</v>
+        <v>4970.7</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>100590.58</v>
+        <v>100318.71</v>
       </c>
       <c r="E44" t="n">
         <v>3</v>
@@ -2019,13 +2019,13 @@
         <v>46062</v>
       </c>
       <c r="B45" s="5" t="n">
-        <v>103702.78</v>
+        <v>105289.42</v>
       </c>
       <c r="C45" s="5" t="n">
-        <v>3112.2</v>
+        <v>4970.7</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>100590.58</v>
+        <v>100318.71</v>
       </c>
       <c r="E45" t="n">
         <v>3</v>
@@ -2043,13 +2043,13 @@
         <v>46063</v>
       </c>
       <c r="B46" s="5" t="n">
-        <v>101577.44</v>
+        <v>101874.8</v>
       </c>
       <c r="C46" s="5" t="n">
-        <v>2022.02</v>
+        <v>3181.37</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>99555.42</v>
+        <v>98693.42999999999</v>
       </c>
       <c r="E46" t="n">
         <v>2</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>S_P_500_Index short (risk 1,006)</t>
+          <t>S_P_500_Index short (risk 1,578)</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Cocoa_NYCSCE_Futures stop (-1,087); EURO_STOXX_50_Index stop (-1,038)</t>
+          <t>Cocoa_NYCSCE_Futures stop (-1,757); EURO_STOXX_50_Index stop (-1,657)</t>
         </is>
       </c>
     </row>
@@ -2075,13 +2075,13 @@
         <v>46064</v>
       </c>
       <c r="B47" s="5" t="n">
-        <v>100562.47</v>
+        <v>100282.57</v>
       </c>
       <c r="C47" s="5" t="n">
-        <v>2011.67</v>
+        <v>3155.8</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>98550.8</v>
+        <v>97126.77</v>
       </c>
       <c r="E47" t="n">
         <v>2</v>
@@ -2093,12 +2093,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT short (risk 996)</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT short (risk 1,552)</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>S_P_500_Index stop (-1,015)</t>
+          <t>S_P_500_Index stop (-1,592)</t>
         </is>
       </c>
     </row>
@@ -2107,13 +2107,13 @@
         <v>46065</v>
       </c>
       <c r="B48" s="5" t="n">
-        <v>99429.60000000001</v>
+        <v>98515.99000000001</v>
       </c>
       <c r="C48" s="5" t="n">
-        <v>2001.62</v>
+        <v>3131.16</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>97427.98</v>
+        <v>95384.83</v>
       </c>
       <c r="E48" t="n">
         <v>2</v>
@@ -2125,12 +2125,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>EURO_STOXX_50_Index short (risk 986)</t>
+          <t>EURO_STOXX_50_Index short (risk 1,528)</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT stop (-1,133)</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT stop (-1,767)</t>
         </is>
       </c>
     </row>
@@ -2139,13 +2139,13 @@
         <v>46066</v>
       </c>
       <c r="B49" s="5" t="n">
-        <v>99429.60000000001</v>
+        <v>98515.99000000001</v>
       </c>
       <c r="C49" s="5" t="n">
-        <v>2975.9</v>
+        <v>4631.56</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>96453.7</v>
+        <v>93884.42999999999</v>
       </c>
       <c r="E49" t="n">
         <v>3</v>
@@ -2157,7 +2157,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures long (risk 974)</t>
+          <t>NY_Copper_Futures long (risk 1,500)</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
@@ -2167,13 +2167,13 @@
         <v>46067</v>
       </c>
       <c r="B50" s="5" t="n">
-        <v>99429.60000000001</v>
+        <v>98515.99000000001</v>
       </c>
       <c r="C50" s="5" t="n">
-        <v>2975.9</v>
+        <v>4631.56</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>96453.7</v>
+        <v>93884.42999999999</v>
       </c>
       <c r="E50" t="n">
         <v>3</v>
@@ -2191,13 +2191,13 @@
         <v>46068</v>
       </c>
       <c r="B51" s="5" t="n">
-        <v>99429.60000000001</v>
+        <v>98515.99000000001</v>
       </c>
       <c r="C51" s="5" t="n">
-        <v>2975.9</v>
+        <v>4631.56</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>96453.7</v>
+        <v>93884.42999999999</v>
       </c>
       <c r="E51" t="n">
         <v>3</v>
@@ -2215,13 +2215,13 @@
         <v>46069</v>
       </c>
       <c r="B52" s="5" t="n">
-        <v>99429.60000000001</v>
+        <v>98515.99000000001</v>
       </c>
       <c r="C52" s="5" t="n">
-        <v>2975.9</v>
+        <v>4631.56</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>96453.7</v>
+        <v>93884.42999999999</v>
       </c>
       <c r="E52" t="n">
         <v>3</v>
@@ -2239,13 +2239,13 @@
         <v>46070</v>
       </c>
       <c r="B53" s="5" t="n">
-        <v>98451.17</v>
+        <v>97009.2</v>
       </c>
       <c r="C53" s="5" t="n">
-        <v>2001.62</v>
+        <v>3131.16</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>96449.55</v>
+        <v>93878.03999999999</v>
       </c>
       <c r="E53" t="n">
         <v>2</v>
@@ -2258,7 +2258,7 @@
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures stop (-978)</t>
+          <t>NY_Copper_Futures stop (-1,507)</t>
         </is>
       </c>
     </row>
@@ -2267,13 +2267,13 @@
         <v>46071</v>
       </c>
       <c r="B54" s="5" t="n">
-        <v>97464.64999999999</v>
+        <v>95479.82000000001</v>
       </c>
       <c r="C54" s="5" t="n">
-        <v>1016.11</v>
+        <v>1603.35</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>96448.53</v>
+        <v>93876.47</v>
       </c>
       <c r="E54" t="n">
         <v>1</v>
@@ -2286,7 +2286,7 @@
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>EURO_STOXX_50_Index stop (-987)</t>
+          <t>EURO_STOXX_50_Index stop (-1,529)</t>
         </is>
       </c>
     </row>
@@ -2295,13 +2295,13 @@
         <v>46072</v>
       </c>
       <c r="B55" s="5" t="n">
-        <v>97464.64999999999</v>
+        <v>95479.82000000001</v>
       </c>
       <c r="C55" s="5" t="n">
-        <v>1016.11</v>
+        <v>1603.35</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>96448.53</v>
+        <v>93876.47</v>
       </c>
       <c r="E55" t="n">
         <v>1</v>
@@ -2319,13 +2319,13 @@
         <v>46073</v>
       </c>
       <c r="B56" s="5" t="n">
-        <v>97464.64999999999</v>
+        <v>95479.82000000001</v>
       </c>
       <c r="C56" s="5" t="n">
-        <v>1016.11</v>
+        <v>1603.35</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>96448.53</v>
+        <v>93876.47</v>
       </c>
       <c r="E56" t="n">
         <v>1</v>
@@ -2343,13 +2343,13 @@
         <v>46074</v>
       </c>
       <c r="B57" s="5" t="n">
-        <v>97464.64999999999</v>
+        <v>95479.82000000001</v>
       </c>
       <c r="C57" s="5" t="n">
-        <v>1016.11</v>
+        <v>1603.35</v>
       </c>
       <c r="D57" s="5" t="n">
-        <v>96448.53</v>
+        <v>93876.47</v>
       </c>
       <c r="E57" t="n">
         <v>1</v>
@@ -2367,13 +2367,13 @@
         <v>46075</v>
       </c>
       <c r="B58" s="5" t="n">
-        <v>97464.64999999999</v>
+        <v>95479.82000000001</v>
       </c>
       <c r="C58" s="5" t="n">
-        <v>1016.11</v>
+        <v>1603.35</v>
       </c>
       <c r="D58" s="5" t="n">
-        <v>96448.53</v>
+        <v>93876.47</v>
       </c>
       <c r="E58" t="n">
         <v>1</v>
@@ -2391,13 +2391,13 @@
         <v>46076</v>
       </c>
       <c r="B59" s="5" t="n">
-        <v>97464.64999999999</v>
+        <v>95479.82000000001</v>
       </c>
       <c r="C59" s="5" t="n">
-        <v>1980.6</v>
+        <v>3080.03</v>
       </c>
       <c r="D59" s="5" t="n">
-        <v>95484.05</v>
+        <v>92399.78999999999</v>
       </c>
       <c r="E59" t="n">
         <v>2</v>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT short (risk 964)</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT short (risk 1,477)</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
@@ -2419,13 +2419,13 @@
         <v>46077</v>
       </c>
       <c r="B60" s="5" t="n">
-        <v>97464.64999999999</v>
+        <v>95479.82000000001</v>
       </c>
       <c r="C60" s="5" t="n">
-        <v>3880.73</v>
+        <v>5964.06</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>93583.92</v>
+        <v>89515.75999999999</v>
       </c>
       <c r="E60" t="n">
         <v>4</v>
@@ -2437,7 +2437,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cocoa_NYCSCE_Futures long (risk 955); Ethereum_Per_USD_Binance long (risk 945)</t>
+          <t>Cocoa_NYCSCE_Futures long (risk 1,453); Ethereum_Per_USD_Binance long (risk 1,431)</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
@@ -2447,13 +2447,13 @@
         <v>46078</v>
       </c>
       <c r="B61" s="5" t="n">
-        <v>107514.56</v>
+        <v>110689.15</v>
       </c>
       <c r="C61" s="5" t="n">
-        <v>2935.44</v>
+        <v>4533.48</v>
       </c>
       <c r="D61" s="5" t="n">
-        <v>104579.12</v>
+        <v>106155.67</v>
       </c>
       <c r="E61" t="n">
         <v>3</v>
@@ -2466,7 +2466,7 @@
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Ethereum_Per_USD_Binance bullish_reversal (+10,050)</t>
+          <t>Ethereum_Per_USD_Binance bullish_reversal (+15,209)</t>
         </is>
       </c>
     </row>
@@ -2475,13 +2475,13 @@
         <v>46079</v>
       </c>
       <c r="B62" s="5" t="n">
-        <v>106274.5</v>
+        <v>108790.57</v>
       </c>
       <c r="C62" s="5" t="n">
-        <v>1970.95</v>
+        <v>3056.8</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>104303.55</v>
+        <v>105733.76</v>
       </c>
       <c r="E62" t="n">
         <v>2</v>
@@ -2494,7 +2494,7 @@
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT stop (-1,240)</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT stop (-1,899)</t>
         </is>
       </c>
     </row>
@@ -2503,13 +2503,13 @@
         <v>46080</v>
       </c>
       <c r="B63" s="5" t="n">
-        <v>105221.73</v>
+        <v>107188.04</v>
       </c>
       <c r="C63" s="5" t="n">
-        <v>1016.11</v>
+        <v>1603.35</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>104205.62</v>
+        <v>105584.69</v>
       </c>
       <c r="E63" t="n">
         <v>1</v>
@@ -2522,7 +2522,7 @@
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Cocoa_NYCSCE_Futures stop (-1,053)</t>
+          <t>Cocoa_NYCSCE_Futures stop (-1,603)</t>
         </is>
       </c>
     </row>
@@ -2531,13 +2531,13 @@
         <v>46081</v>
       </c>
       <c r="B64" s="5" t="n">
-        <v>105221.73</v>
+        <v>107188.04</v>
       </c>
       <c r="C64" s="5" t="n">
-        <v>1016.11</v>
+        <v>1603.35</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>104205.62</v>
+        <v>105584.69</v>
       </c>
       <c r="E64" t="n">
         <v>1</v>
@@ -2555,13 +2555,13 @@
         <v>46082</v>
       </c>
       <c r="B65" s="5" t="n">
-        <v>105221.73</v>
+        <v>107188.04</v>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1016.11</v>
+        <v>1603.35</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>104205.62</v>
+        <v>105584.69</v>
       </c>
       <c r="E65" t="n">
         <v>1</v>
@@ -2579,13 +2579,13 @@
         <v>46083</v>
       </c>
       <c r="B66" s="5" t="n">
-        <v>107632.38</v>
+        <v>110991.87</v>
       </c>
       <c r="C66" s="5" t="n">
-        <v>1042.06</v>
+        <v>1660.85</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>106590.32</v>
+        <v>109331.02</v>
       </c>
       <c r="E66" t="n">
         <v>1</v>
@@ -2597,12 +2597,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX short (risk 1,042)</t>
+          <t>Gold_Futures_COMEX short (risk 1,661)</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance bullish_reversal (+2,411)</t>
+          <t>Bitcoin_Per_USD_Binance bullish_reversal (+3,804)</t>
         </is>
       </c>
     </row>
@@ -2611,13 +2611,13 @@
         <v>46084</v>
       </c>
       <c r="B67" s="5" t="n">
-        <v>107632.38</v>
+        <v>110991.87</v>
       </c>
       <c r="C67" s="5" t="n">
-        <v>1042.06</v>
+        <v>1660.85</v>
       </c>
       <c r="D67" s="5" t="n">
-        <v>106590.32</v>
+        <v>109331.02</v>
       </c>
       <c r="E67" t="n">
         <v>1</v>
@@ -2635,13 +2635,13 @@
         <v>46085</v>
       </c>
       <c r="B68" s="5" t="n">
-        <v>107632.38</v>
+        <v>110991.87</v>
       </c>
       <c r="C68" s="5" t="n">
-        <v>2107.96</v>
+        <v>3380.62</v>
       </c>
       <c r="D68" s="5" t="n">
-        <v>105524.42</v>
+        <v>107611.24</v>
       </c>
       <c r="E68" t="n">
         <v>2</v>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate short (risk 1,066)</t>
+          <t>USD_EUR_Cross_Rate short (risk 1,720)</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
@@ -2663,13 +2663,13 @@
         <v>46086</v>
       </c>
       <c r="B69" s="5" t="n">
-        <v>106381.1</v>
+        <v>108973</v>
       </c>
       <c r="C69" s="5" t="n">
-        <v>2097.3</v>
+        <v>3353.57</v>
       </c>
       <c r="D69" s="5" t="n">
-        <v>104283.8</v>
+        <v>105619.43</v>
       </c>
       <c r="E69" t="n">
         <v>2</v>
@@ -2681,12 +2681,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>S_P_500_Index long (risk 1,055)</t>
+          <t>S_P_500_Index long (risk 1,693)</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate stop (-1,251)</t>
+          <t>USD_EUR_Cross_Rate stop (-2,019)</t>
         </is>
       </c>
     </row>
@@ -2695,13 +2695,13 @@
         <v>46087</v>
       </c>
       <c r="B70" s="5" t="n">
-        <v>105324.07</v>
+        <v>107277.41</v>
       </c>
       <c r="C70" s="5" t="n">
-        <v>2084.89</v>
+        <v>3322.24</v>
       </c>
       <c r="D70" s="5" t="n">
-        <v>103239.18</v>
+        <v>103955.17</v>
       </c>
       <c r="E70" t="n">
         <v>2</v>
@@ -2713,12 +2713,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate short (risk 1,043)</t>
+          <t>USD_EUR_Cross_Rate short (risk 1,661)</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>S_P_500_Index stop (-1,057)</t>
+          <t>S_P_500_Index stop (-1,696)</t>
         </is>
       </c>
     </row>
@@ -2727,13 +2727,13 @@
         <v>46088</v>
       </c>
       <c r="B71" s="5" t="n">
-        <v>105324.07</v>
+        <v>107277.41</v>
       </c>
       <c r="C71" s="5" t="n">
-        <v>2084.89</v>
+        <v>3322.24</v>
       </c>
       <c r="D71" s="5" t="n">
-        <v>103239.18</v>
+        <v>103955.17</v>
       </c>
       <c r="E71" t="n">
         <v>2</v>
@@ -2751,13 +2751,13 @@
         <v>46089</v>
       </c>
       <c r="B72" s="5" t="n">
-        <v>105324.07</v>
+        <v>107277.41</v>
       </c>
       <c r="C72" s="5" t="n">
-        <v>2084.89</v>
+        <v>3322.24</v>
       </c>
       <c r="D72" s="5" t="n">
-        <v>103239.18</v>
+        <v>103955.17</v>
       </c>
       <c r="E72" t="n">
         <v>2</v>
@@ -2775,13 +2775,13 @@
         <v>46090</v>
       </c>
       <c r="B73" s="5" t="n">
-        <v>108607.95</v>
+        <v>112512.07</v>
       </c>
       <c r="C73" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D73" s="5" t="n">
-        <v>108607.95</v>
+        <v>112512.07</v>
       </c>
       <c r="E73" t="n">
         <v>0</v>
@@ -2790,7 +2790,7 @@
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX bearish_reversal (+4,422); USD_EUR_Cross_Rate stop (-1,138)</t>
+          <t>Gold_Futures_COMEX bearish_reversal (+7,047); USD_EUR_Cross_Rate stop (-1,812)</t>
         </is>
       </c>
     </row>
@@ -2799,13 +2799,13 @@
         <v>46091</v>
       </c>
       <c r="B74" s="5" t="n">
-        <v>108607.95</v>
+        <v>112512.07</v>
       </c>
       <c r="C74" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>108607.95</v>
+        <v>112512.07</v>
       </c>
       <c r="E74" t="n">
         <v>0</v>
@@ -2819,13 +2819,13 @@
         <v>46092</v>
       </c>
       <c r="B75" s="5" t="n">
-        <v>108607.95</v>
+        <v>112512.07</v>
       </c>
       <c r="C75" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>108607.95</v>
+        <v>112512.07</v>
       </c>
       <c r="E75" t="n">
         <v>0</v>
@@ -2839,13 +2839,13 @@
         <v>46093</v>
       </c>
       <c r="B76" s="5" t="n">
-        <v>108607.95</v>
+        <v>112512.07</v>
       </c>
       <c r="C76" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>108607.95</v>
+        <v>112512.07</v>
       </c>
       <c r="E76" t="n">
         <v>0</v>
@@ -2859,13 +2859,13 @@
         <v>46094</v>
       </c>
       <c r="B77" s="5" t="n">
-        <v>108607.95</v>
+        <v>112512.07</v>
       </c>
       <c r="C77" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D77" s="5" t="n">
-        <v>108607.95</v>
+        <v>112512.07</v>
       </c>
       <c r="E77" t="n">
         <v>0</v>
@@ -2879,13 +2879,13 @@
         <v>46095</v>
       </c>
       <c r="B78" s="5" t="n">
-        <v>108607.95</v>
+        <v>112512.07</v>
       </c>
       <c r="C78" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D78" s="5" t="n">
-        <v>108607.95</v>
+        <v>112512.07</v>
       </c>
       <c r="E78" t="n">
         <v>0</v>
@@ -2899,13 +2899,13 @@
         <v>46096</v>
       </c>
       <c r="B79" s="5" t="n">
-        <v>108607.95</v>
+        <v>112512.07</v>
       </c>
       <c r="C79" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D79" s="5" t="n">
-        <v>108607.95</v>
+        <v>112512.07</v>
       </c>
       <c r="E79" t="n">
         <v>0</v>
@@ -2919,13 +2919,13 @@
         <v>46097</v>
       </c>
       <c r="B80" s="5" t="n">
-        <v>108607.95</v>
+        <v>112512.07</v>
       </c>
       <c r="C80" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D80" s="5" t="n">
-        <v>108607.95</v>
+        <v>112512.07</v>
       </c>
       <c r="E80" t="n">
         <v>0</v>
@@ -2939,13 +2939,13 @@
         <v>46098</v>
       </c>
       <c r="B81" s="5" t="n">
-        <v>108607.95</v>
+        <v>112512.07</v>
       </c>
       <c r="C81" s="5" t="n">
-        <v>1086.08</v>
+        <v>1769.81</v>
       </c>
       <c r="D81" s="5" t="n">
-        <v>107521.87</v>
+        <v>110742.26</v>
       </c>
       <c r="E81" t="n">
         <v>1</v>
@@ -2957,7 +2957,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance short (risk 1,086)</t>
+          <t>Bitcoin_Per_USD_Binance short (risk 1,770)</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
@@ -2967,13 +2967,13 @@
         <v>46099</v>
       </c>
       <c r="B82" s="5" t="n">
-        <v>108607.95</v>
+        <v>112512.07</v>
       </c>
       <c r="C82" s="5" t="n">
-        <v>1086.08</v>
+        <v>1769.81</v>
       </c>
       <c r="D82" s="5" t="n">
-        <v>107521.87</v>
+        <v>110742.26</v>
       </c>
       <c r="E82" t="n">
         <v>1</v>
@@ -2991,13 +2991,13 @@
         <v>46100</v>
       </c>
       <c r="B83" s="5" t="n">
-        <v>108607.95</v>
+        <v>112512.07</v>
       </c>
       <c r="C83" s="5" t="n">
-        <v>1086.08</v>
+        <v>1769.81</v>
       </c>
       <c r="D83" s="5" t="n">
-        <v>107521.87</v>
+        <v>110742.26</v>
       </c>
       <c r="E83" t="n">
         <v>1</v>
@@ -3015,13 +3015,13 @@
         <v>46101</v>
       </c>
       <c r="B84" s="5" t="n">
-        <v>108607.95</v>
+        <v>112512.07</v>
       </c>
       <c r="C84" s="5" t="n">
-        <v>2161.3</v>
+        <v>3511.79</v>
       </c>
       <c r="D84" s="5" t="n">
-        <v>106446.65</v>
+        <v>109000.28</v>
       </c>
       <c r="E84" t="n">
         <v>2</v>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP short (risk 1,075)</t>
+          <t>United_States_Oil_Fund_LP short (risk 1,742)</t>
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
@@ -3043,13 +3043,13 @@
         <v>46102</v>
       </c>
       <c r="B85" s="5" t="n">
-        <v>108607.95</v>
+        <v>112512.07</v>
       </c>
       <c r="C85" s="5" t="n">
-        <v>2161.3</v>
+        <v>3511.79</v>
       </c>
       <c r="D85" s="5" t="n">
-        <v>106446.65</v>
+        <v>109000.28</v>
       </c>
       <c r="E85" t="n">
         <v>2</v>
@@ -3067,13 +3067,13 @@
         <v>46103</v>
       </c>
       <c r="B86" s="5" t="n">
-        <v>120127.32</v>
+        <v>131283.41</v>
       </c>
       <c r="C86" s="5" t="n">
-        <v>1075.22</v>
+        <v>1741.98</v>
       </c>
       <c r="D86" s="5" t="n">
-        <v>119052.11</v>
+        <v>129541.43</v>
       </c>
       <c r="E86" t="n">
         <v>1</v>
@@ -3086,7 +3086,7 @@
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance bearish_reversal (+11,519)</t>
+          <t>Bitcoin_Per_USD_Binance bearish_reversal (+18,771)</t>
         </is>
       </c>
     </row>
@@ -3095,13 +3095,13 @@
         <v>46104</v>
       </c>
       <c r="B87" s="5" t="n">
-        <v>120127.32</v>
+        <v>131283.41</v>
       </c>
       <c r="C87" s="5" t="n">
-        <v>2265.74</v>
+        <v>3779.66</v>
       </c>
       <c r="D87" s="5" t="n">
-        <v>117861.58</v>
+        <v>127503.75</v>
       </c>
       <c r="E87" t="n">
         <v>2</v>
@@ -3113,7 +3113,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures long (risk 1,191)</t>
+          <t>NY_Copper_Futures long (risk 2,038)</t>
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
@@ -3123,13 +3123,13 @@
         <v>46105</v>
       </c>
       <c r="B88" s="5" t="n">
-        <v>120127.32</v>
+        <v>131283.41</v>
       </c>
       <c r="C88" s="5" t="n">
-        <v>3444.36</v>
+        <v>5785.3</v>
       </c>
       <c r="D88" s="5" t="n">
-        <v>116682.97</v>
+        <v>125498.11</v>
       </c>
       <c r="E88" t="n">
         <v>3</v>
@@ -3141,7 +3141,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX long (risk 1,179)</t>
+          <t>Gold_Futures_COMEX long (risk 2,006)</t>
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
@@ -3151,13 +3151,13 @@
         <v>46106</v>
       </c>
       <c r="B89" s="5" t="n">
-        <v>120127.32</v>
+        <v>131283.41</v>
       </c>
       <c r="C89" s="5" t="n">
-        <v>3444.36</v>
+        <v>5785.3</v>
       </c>
       <c r="D89" s="5" t="n">
-        <v>116682.97</v>
+        <v>125498.11</v>
       </c>
       <c r="E89" t="n">
         <v>3</v>
@@ -3175,13 +3175,13 @@
         <v>46107</v>
       </c>
       <c r="B90" s="5" t="n">
-        <v>120127.32</v>
+        <v>131283.41</v>
       </c>
       <c r="C90" s="5" t="n">
-        <v>3444.36</v>
+        <v>5785.3</v>
       </c>
       <c r="D90" s="5" t="n">
-        <v>116682.97</v>
+        <v>125498.11</v>
       </c>
       <c r="E90" t="n">
         <v>3</v>
@@ -3199,13 +3199,13 @@
         <v>46108</v>
       </c>
       <c r="B91" s="5" t="n">
-        <v>119019.27</v>
+        <v>129488.24</v>
       </c>
       <c r="C91" s="5" t="n">
-        <v>2369.14</v>
+        <v>4043.32</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>116650.14</v>
+        <v>125444.92</v>
       </c>
       <c r="E91" t="n">
         <v>2</v>
@@ -3218,7 +3218,7 @@
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP stop (-1,108)</t>
+          <t>United_States_Oil_Fund_LP stop (-1,795)</t>
         </is>
       </c>
     </row>
@@ -3227,13 +3227,13 @@
         <v>46109</v>
       </c>
       <c r="B92" s="5" t="n">
-        <v>119019.27</v>
+        <v>129488.24</v>
       </c>
       <c r="C92" s="5" t="n">
-        <v>2369.14</v>
+        <v>4043.32</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>116650.14</v>
+        <v>125444.92</v>
       </c>
       <c r="E92" t="n">
         <v>2</v>
@@ -3251,13 +3251,13 @@
         <v>46110</v>
       </c>
       <c r="B93" s="5" t="n">
-        <v>119019.27</v>
+        <v>129488.24</v>
       </c>
       <c r="C93" s="5" t="n">
-        <v>2369.14</v>
+        <v>4043.32</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>116650.14</v>
+        <v>125444.92</v>
       </c>
       <c r="E93" t="n">
         <v>2</v>
@@ -3275,13 +3275,13 @@
         <v>46111</v>
       </c>
       <c r="B94" s="5" t="n">
-        <v>119019.27</v>
+        <v>129488.24</v>
       </c>
       <c r="C94" s="5" t="n">
-        <v>2369.14</v>
+        <v>4043.32</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>116650.14</v>
+        <v>125444.92</v>
       </c>
       <c r="E94" t="n">
         <v>2</v>
@@ -3299,13 +3299,13 @@
         <v>46112</v>
       </c>
       <c r="B95" s="5" t="n">
-        <v>119019.27</v>
+        <v>129488.24</v>
       </c>
       <c r="C95" s="5" t="n">
-        <v>3535.64</v>
+        <v>6016.57</v>
       </c>
       <c r="D95" s="5" t="n">
-        <v>115483.64</v>
+        <v>123471.67</v>
       </c>
       <c r="E95" t="n">
         <v>3</v>
@@ -3317,7 +3317,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP short (risk 1,167)</t>
+          <t>United_States_Oil_Fund_LP short (risk 1,973)</t>
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
@@ -3327,13 +3327,13 @@
         <v>46113</v>
       </c>
       <c r="B96" s="5" t="n">
-        <v>119019.27</v>
+        <v>129488.24</v>
       </c>
       <c r="C96" s="5" t="n">
-        <v>3535.64</v>
+        <v>6016.57</v>
       </c>
       <c r="D96" s="5" t="n">
-        <v>115483.64</v>
+        <v>123471.67</v>
       </c>
       <c r="E96" t="n">
         <v>3</v>
@@ -3351,13 +3351,13 @@
         <v>46114</v>
       </c>
       <c r="B97" s="5" t="n">
-        <v>117792.95</v>
+        <v>127413.8</v>
       </c>
       <c r="C97" s="5" t="n">
-        <v>2369.14</v>
+        <v>4043.32</v>
       </c>
       <c r="D97" s="5" t="n">
-        <v>115423.82</v>
+        <v>123370.48</v>
       </c>
       <c r="E97" t="n">
         <v>2</v>
@@ -3370,7 +3370,7 @@
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP stop (-1,226)</t>
+          <t>United_States_Oil_Fund_LP stop (-2,074)</t>
         </is>
       </c>
     </row>
@@ -3379,13 +3379,13 @@
         <v>46115</v>
       </c>
       <c r="B98" s="5" t="n">
-        <v>117792.95</v>
+        <v>127413.8</v>
       </c>
       <c r="C98" s="5" t="n">
-        <v>2369.14</v>
+        <v>4043.32</v>
       </c>
       <c r="D98" s="5" t="n">
-        <v>115423.82</v>
+        <v>123370.48</v>
       </c>
       <c r="E98" t="n">
         <v>2</v>
@@ -3403,13 +3403,13 @@
         <v>46116</v>
       </c>
       <c r="B99" s="5" t="n">
-        <v>117792.95</v>
+        <v>127413.8</v>
       </c>
       <c r="C99" s="5" t="n">
-        <v>2369.14</v>
+        <v>4043.32</v>
       </c>
       <c r="D99" s="5" t="n">
-        <v>115423.82</v>
+        <v>123370.48</v>
       </c>
       <c r="E99" t="n">
         <v>2</v>
@@ -3427,13 +3427,13 @@
         <v>46117</v>
       </c>
       <c r="B100" s="5" t="n">
-        <v>117792.95</v>
+        <v>127413.8</v>
       </c>
       <c r="C100" s="5" t="n">
-        <v>2369.14</v>
+        <v>4043.32</v>
       </c>
       <c r="D100" s="5" t="n">
-        <v>115423.82</v>
+        <v>123370.48</v>
       </c>
       <c r="E100" t="n">
         <v>2</v>
@@ -3451,13 +3451,13 @@
         <v>46118</v>
       </c>
       <c r="B101" s="5" t="n">
-        <v>117792.95</v>
+        <v>127413.8</v>
       </c>
       <c r="C101" s="5" t="n">
-        <v>2369.14</v>
+        <v>4043.32</v>
       </c>
       <c r="D101" s="5" t="n">
-        <v>115423.82</v>
+        <v>123370.48</v>
       </c>
       <c r="E101" t="n">
         <v>2</v>
@@ -3475,13 +3475,13 @@
         <v>46119</v>
       </c>
       <c r="B102" s="5" t="n">
-        <v>117792.95</v>
+        <v>127413.8</v>
       </c>
       <c r="C102" s="5" t="n">
-        <v>2369.14</v>
+        <v>4043.32</v>
       </c>
       <c r="D102" s="5" t="n">
-        <v>115423.82</v>
+        <v>123370.48</v>
       </c>
       <c r="E102" t="n">
         <v>2</v>
@@ -3499,13 +3499,13 @@
         <v>46120</v>
       </c>
       <c r="B103" s="5" t="n">
-        <v>117792.95</v>
+        <v>127413.8</v>
       </c>
       <c r="C103" s="5" t="n">
-        <v>2369.14</v>
+        <v>4043.32</v>
       </c>
       <c r="D103" s="5" t="n">
-        <v>115423.82</v>
+        <v>123370.48</v>
       </c>
       <c r="E103" t="n">
         <v>2</v>
@@ -3523,13 +3523,13 @@
         <v>46121</v>
       </c>
       <c r="B104" s="5" t="n">
-        <v>117792.95</v>
+        <v>127413.8</v>
       </c>
       <c r="C104" s="5" t="n">
-        <v>2369.14</v>
+        <v>4043.32</v>
       </c>
       <c r="D104" s="5" t="n">
-        <v>115423.82</v>
+        <v>123370.48</v>
       </c>
       <c r="E104" t="n">
         <v>2</v>
@@ -3547,13 +3547,13 @@
         <v>46122</v>
       </c>
       <c r="B105" s="5" t="n">
-        <v>126176.05</v>
+        <v>141762.24</v>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1178.62</v>
+        <v>2005.63</v>
       </c>
       <c r="D105" s="5" t="n">
-        <v>124997.43</v>
+        <v>139756.6</v>
       </c>
       <c r="E105" t="n">
         <v>1</v>
@@ -3566,7 +3566,7 @@
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures bullish_reversal (+8,383)</t>
+          <t>NY_Copper_Futures bullish_reversal (+14,348)</t>
         </is>
       </c>
     </row>
@@ -3575,13 +3575,13 @@
         <v>46123</v>
       </c>
       <c r="B106" s="5" t="n">
-        <v>126176.05</v>
+        <v>141762.24</v>
       </c>
       <c r="C106" s="5" t="n">
-        <v>1178.62</v>
+        <v>2005.63</v>
       </c>
       <c r="D106" s="5" t="n">
-        <v>124997.43</v>
+        <v>139756.6</v>
       </c>
       <c r="E106" t="n">
         <v>1</v>
@@ -3599,13 +3599,13 @@
         <v>46124</v>
       </c>
       <c r="B107" s="5" t="n">
-        <v>126176.05</v>
+        <v>141762.24</v>
       </c>
       <c r="C107" s="5" t="n">
-        <v>1178.62</v>
+        <v>2005.63</v>
       </c>
       <c r="D107" s="5" t="n">
-        <v>124997.43</v>
+        <v>139756.6</v>
       </c>
       <c r="E107" t="n">
         <v>1</v>
@@ -3623,13 +3623,13 @@
         <v>46125</v>
       </c>
       <c r="B108" s="5" t="n">
-        <v>126176.05</v>
+        <v>141762.24</v>
       </c>
       <c r="C108" s="5" t="n">
-        <v>1178.62</v>
+        <v>2005.63</v>
       </c>
       <c r="D108" s="5" t="n">
-        <v>124997.43</v>
+        <v>139756.6</v>
       </c>
       <c r="E108" t="n">
         <v>1</v>
@@ -3647,13 +3647,13 @@
         <v>46126</v>
       </c>
       <c r="B109" s="5" t="n">
-        <v>126176.05</v>
+        <v>141762.24</v>
       </c>
       <c r="C109" s="5" t="n">
-        <v>2428.59</v>
+        <v>4204.01</v>
       </c>
       <c r="D109" s="5" t="n">
-        <v>123747.46</v>
+        <v>137558.23</v>
       </c>
       <c r="E109" t="n">
         <v>2</v>
@@ -3665,7 +3665,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance short (risk 1,250)</t>
+          <t>Bitcoin_Per_USD_Binance short (risk 2,198)</t>
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
@@ -3675,13 +3675,13 @@
         <v>46127</v>
       </c>
       <c r="B110" s="5" t="n">
-        <v>126176.05</v>
+        <v>141762.24</v>
       </c>
       <c r="C110" s="5" t="n">
-        <v>6104.01</v>
+        <v>10593.8</v>
       </c>
       <c r="D110" s="5" t="n">
-        <v>120072.03</v>
+        <v>131168.43</v>
       </c>
       <c r="E110" t="n">
         <v>5</v>
@@ -3693,7 +3693,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Ethereum_Per_USD_Binance short (risk 1,237); Live_Cattle_Futures_CME short (risk 1,225); NY_Copper_Futures short (risk 1,213)</t>
+          <t>Ethereum_Per_USD_Binance short (risk 2,164); Live_Cattle_Futures_CME short (risk 2,130); NY_Copper_Futures short (risk 2,096)</t>
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
@@ -3703,13 +3703,13 @@
         <v>46128</v>
       </c>
       <c r="B111" s="5" t="n">
-        <v>126176.05</v>
+        <v>141762.24</v>
       </c>
       <c r="C111" s="5" t="n">
-        <v>6104.01</v>
+        <v>10593.8</v>
       </c>
       <c r="D111" s="5" t="n">
-        <v>120072.03</v>
+        <v>131168.43</v>
       </c>
       <c r="E111" t="n">
         <v>5</v>
@@ -3727,13 +3727,13 @@
         <v>46129</v>
       </c>
       <c r="B112" s="5" t="n">
-        <v>156127.96</v>
+        <v>193768</v>
       </c>
       <c r="C112" s="5" t="n">
-        <v>2391.46</v>
+        <v>4101.89</v>
       </c>
       <c r="D112" s="5" t="n">
-        <v>153736.5</v>
+        <v>189666.11</v>
       </c>
       <c r="E112" t="n">
         <v>2</v>
@@ -3745,12 +3745,12 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate long (risk 1,201)</t>
+          <t>USD_EUR_Cross_Rate long (risk 2,063)</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance stop (-1,254); Ethereum_Per_USD_Binance stop (-1,547); Live_Cattle_Futures_CME bearish_reversal (+31,630); USD_EUR_Cross_Rate data_end (+1,123)</t>
+          <t>Bitcoin_Per_USD_Binance stop (-2,206); Ethereum_Per_USD_Binance stop (-2,705); Live_Cattle_Futures_CME bearish_reversal (+54,986); USD_EUR_Cross_Rate data_end (+1,930)</t>
         </is>
       </c>
     </row>
@@ -3759,13 +3759,13 @@
         <v>46130</v>
       </c>
       <c r="B113" s="5" t="n">
-        <v>156127.96</v>
+        <v>193768</v>
       </c>
       <c r="C113" s="5" t="n">
-        <v>2391.46</v>
+        <v>4101.89</v>
       </c>
       <c r="D113" s="5" t="n">
-        <v>153736.5</v>
+        <v>189666.11</v>
       </c>
       <c r="E113" t="n">
         <v>2</v>
@@ -3783,13 +3783,13 @@
         <v>46132</v>
       </c>
       <c r="B114" s="5" t="n">
-        <v>156127.96</v>
+        <v>193768</v>
       </c>
       <c r="C114" s="5" t="n">
-        <v>2391.46</v>
+        <v>4101.89</v>
       </c>
       <c r="D114" s="5" t="n">
-        <v>153736.5</v>
+        <v>189666.11</v>
       </c>
       <c r="E114" t="n">
         <v>2</v>
@@ -3807,13 +3807,13 @@
         <v>46133</v>
       </c>
       <c r="B115" s="5" t="n">
-        <v>156127.96</v>
+        <v>193768</v>
       </c>
       <c r="C115" s="5" t="n">
-        <v>2391.46</v>
+        <v>4101.89</v>
       </c>
       <c r="D115" s="5" t="n">
-        <v>153736.5</v>
+        <v>189666.11</v>
       </c>
       <c r="E115" t="n">
         <v>2</v>
@@ -3831,13 +3831,13 @@
         <v>46134</v>
       </c>
       <c r="B116" s="5" t="n">
-        <v>154905.87</v>
+        <v>191655.77</v>
       </c>
       <c r="C116" s="5" t="n">
-        <v>2715.98</v>
+        <v>4989.08</v>
       </c>
       <c r="D116" s="5" t="n">
-        <v>152189.89</v>
+        <v>186666.69</v>
       </c>
       <c r="E116" t="n">
         <v>2</v>
@@ -3849,12 +3849,12 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini short (risk 1,537)</t>
+          <t>Dow_Futures_E_mini short (risk 2,983)</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures stop (-1,222)</t>
+          <t>NY_Copper_Futures stop (-2,112)</t>
         </is>
       </c>
     </row>
@@ -3863,13 +3863,13 @@
         <v>46135</v>
       </c>
       <c r="B117" s="5" t="n">
-        <v>154905.87</v>
+        <v>191655.77</v>
       </c>
       <c r="C117" s="5" t="n">
-        <v>2715.98</v>
+        <v>4989.08</v>
       </c>
       <c r="D117" s="5" t="n">
-        <v>152189.89</v>
+        <v>186666.69</v>
       </c>
       <c r="E117" t="n">
         <v>2</v>
@@ -3887,13 +3887,13 @@
         <v>46136</v>
       </c>
       <c r="B118" s="5" t="n">
-        <v>154905.87</v>
+        <v>191655.77</v>
       </c>
       <c r="C118" s="5" t="n">
-        <v>2715.98</v>
+        <v>4989.08</v>
       </c>
       <c r="D118" s="5" t="n">
-        <v>152189.89</v>
+        <v>186666.69</v>
       </c>
       <c r="E118" t="n">
         <v>2</v>
@@ -3911,13 +3911,13 @@
         <v>46139</v>
       </c>
       <c r="B119" s="5" t="n">
-        <v>154905.87</v>
+        <v>191655.77</v>
       </c>
       <c r="C119" s="5" t="n">
-        <v>4237.88</v>
+        <v>7925.35</v>
       </c>
       <c r="D119" s="5" t="n">
-        <v>150667.99</v>
+        <v>183730.42</v>
       </c>
       <c r="E119" t="n">
         <v>3</v>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_CME short (risk 1,522)</t>
+          <t>Bitcoin_Per_USD_CME short (risk 2,936)</t>
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
@@ -3939,13 +3939,13 @@
         <v>46140</v>
       </c>
       <c r="B120" s="5" t="n">
-        <v>154905.87</v>
+        <v>191655.77</v>
       </c>
       <c r="C120" s="5" t="n">
-        <v>5744.56</v>
+        <v>10815.43</v>
       </c>
       <c r="D120" s="5" t="n">
-        <v>149161.31</v>
+        <v>180840.34</v>
       </c>
       <c r="E120" t="n">
         <v>4</v>
@@ -3957,7 +3957,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>S_P_500_E_mini short (risk 1,507)</t>
+          <t>S_P_500_E_mini short (risk 2,890)</t>
         </is>
       </c>
       <c r="H120" t="inlineStr"/>
@@ -3967,13 +3967,13 @@
         <v>46141</v>
       </c>
       <c r="B121" s="5" t="n">
-        <v>154905.87</v>
+        <v>191655.77</v>
       </c>
       <c r="C121" s="5" t="n">
-        <v>7236.17</v>
+        <v>13660.05</v>
       </c>
       <c r="D121" s="5" t="n">
-        <v>147669.7</v>
+        <v>177995.72</v>
       </c>
       <c r="E121" t="n">
         <v>5</v>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 1,492)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 2,845)</t>
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
@@ -3995,13 +3995,13 @@
         <v>46142</v>
       </c>
       <c r="B122" s="5" t="n">
-        <v>151757.41</v>
+        <v>185579.69</v>
       </c>
       <c r="C122" s="5" t="n">
-        <v>5668.82</v>
+        <v>10586.39</v>
       </c>
       <c r="D122" s="5" t="n">
-        <v>146088.58</v>
+        <v>174993.3</v>
       </c>
       <c r="E122" t="n">
         <v>4</v>
@@ -4013,12 +4013,12 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures short (risk 1,477)</t>
+          <t>Corn_CBOT_Futures short (risk 2,800)</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini stop (-1,638); S_P_500_E_mini stop (-1,510)</t>
+          <t>Dow_Futures_E_mini stop (-3,179); S_P_500_E_mini stop (-2,897)</t>
         </is>
       </c>
     </row>
@@ -4027,13 +4027,13 @@
         <v>46143</v>
       </c>
       <c r="B123" s="5" t="n">
-        <v>149969.83</v>
+        <v>182190.37</v>
       </c>
       <c r="C123" s="5" t="n">
-        <v>8531.1</v>
+        <v>15915.24</v>
       </c>
       <c r="D123" s="5" t="n">
-        <v>141438.72</v>
+        <v>166275.13</v>
       </c>
       <c r="E123" t="n">
         <v>6</v>
@@ -4045,12 +4045,12 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Japanese_Yen_Futures short (risk 1,461); Live_Cattle_Futures_CME short (risk 1,446); US_Dollar_Index_Futures long (risk 1,432)</t>
+          <t>Japanese_Yen_Futures short (risk 2,753); Live_Cattle_Futures_CME short (risk 2,709); US_Dollar_Index_Futures long (risk 2,667)</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures stop (-1,788)</t>
+          <t>Corn_CBOT_Futures stop (-3,389)</t>
         </is>
       </c>
     </row>
@@ -4059,13 +4059,13 @@
         <v>46146</v>
       </c>
       <c r="B124" s="5" t="n">
-        <v>148435.4</v>
+        <v>179229.94</v>
       </c>
       <c r="C124" s="5" t="n">
-        <v>8423.59</v>
+        <v>15594.48</v>
       </c>
       <c r="D124" s="5" t="n">
-        <v>140011.81</v>
+        <v>163635.46</v>
       </c>
       <c r="E124" t="n">
         <v>6</v>
@@ -4077,12 +4077,12 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Nasdaq_100_E_mini short (risk 1,414)</t>
+          <t>Nasdaq_100_E_mini short (risk 2,616)</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_CME stop (-1,534)</t>
+          <t>Bitcoin_Per_USD_CME stop (-2,960)</t>
         </is>
       </c>
     </row>
@@ -4091,13 +4091,13 @@
         <v>46147</v>
       </c>
       <c r="B125" s="5" t="n">
-        <v>147020.05</v>
+        <v>176612.65</v>
       </c>
       <c r="C125" s="5" t="n">
-        <v>8409.32</v>
+        <v>15552.96</v>
       </c>
       <c r="D125" s="5" t="n">
-        <v>138610.73</v>
+        <v>161059.69</v>
       </c>
       <c r="E125" t="n">
         <v>6</v>
@@ -4109,12 +4109,12 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures short (risk 1,400)</t>
+          <t>Corn_CBOT_Futures short (risk 2,574)</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Nasdaq_100_E_mini stop (-1,415)</t>
+          <t>Nasdaq_100_E_mini stop (-2,617)</t>
         </is>
       </c>
     </row>
@@ -4123,13 +4123,13 @@
         <v>46148</v>
       </c>
       <c r="B126" s="5" t="n">
-        <v>153230.93</v>
+        <v>188559.13</v>
       </c>
       <c r="C126" s="5" t="n">
-        <v>5411.12</v>
+        <v>9822.43</v>
       </c>
       <c r="D126" s="5" t="n">
-        <v>147819.81</v>
+        <v>178736.7</v>
       </c>
       <c r="E126" t="n">
         <v>4</v>
@@ -4141,12 +4141,12 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_CME short (risk 1,386)</t>
+          <t>Bitcoin_Per_USD_CME short (risk 2,533)</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT bearish_reversal (+9,285); Japanese_Yen_Futures stop (-1,619); US_Dollar_Index_Futures stop (-1,455)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT bearish_reversal (+17,707); Japanese_Yen_Futures stop (-3,050); US_Dollar_Index_Futures stop (-2,710)</t>
         </is>
       </c>
     </row>
@@ -4155,13 +4155,13 @@
         <v>46149</v>
       </c>
       <c r="B127" s="5" t="n">
-        <v>170533.66</v>
+        <v>218002.95</v>
       </c>
       <c r="C127" s="5" t="n">
-        <v>7174.12</v>
+        <v>13395.63</v>
       </c>
       <c r="D127" s="5" t="n">
-        <v>163359.55</v>
+        <v>204607.32</v>
       </c>
       <c r="E127" t="n">
         <v>5</v>
@@ -4173,12 +4173,12 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>EURO_Futures short (risk 1,478); NY_Platinum_Futures short (risk 1,463)</t>
+          <t>EURO_Futures short (risk 2,812); NY_Platinum_Futures short (risk 2,767)</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX bullish_reversal (+17,303)</t>
+          <t>Gold_Futures_COMEX bullish_reversal (+29,444)</t>
         </is>
       </c>
     </row>
@@ -4187,13 +4187,13 @@
         <v>46150</v>
       </c>
       <c r="B128" s="5" t="n">
-        <v>169017.56</v>
+        <v>215119.33</v>
       </c>
       <c r="C128" s="5" t="n">
-        <v>5695.92</v>
+        <v>10584.1</v>
       </c>
       <c r="D128" s="5" t="n">
-        <v>163321.65</v>
+        <v>204535.23</v>
       </c>
       <c r="E128" t="n">
         <v>4</v>
@@ -4206,7 +4206,7 @@
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr">
         <is>
-          <t>EURO_Futures stop (-1,516)</t>
+          <t>EURO_Futures stop (-2,884)</t>
         </is>
       </c>
     </row>
@@ -4215,13 +4215,13 @@
         <v>46153</v>
       </c>
       <c r="B129" s="5" t="n">
-        <v>177206.73</v>
+        <v>230434.09</v>
       </c>
       <c r="C129" s="5" t="n">
-        <v>4419.44</v>
+        <v>8324.790000000001</v>
       </c>
       <c r="D129" s="5" t="n">
-        <v>172787.29</v>
+        <v>222109.3</v>
       </c>
       <c r="E129" t="n">
         <v>3</v>
@@ -4233,12 +4233,12 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX short (risk 1,633)</t>
+          <t>Gold_Futures_COMEX short (risk 3,217)</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Live_Cattle_Futures_CME bearish_reversal (+9,673); NY_Platinum_Futures stop (-1,484)</t>
+          <t>Live_Cattle_Futures_CME bearish_reversal (+18,120); NY_Platinum_Futures stop (-2,805)</t>
         </is>
       </c>
     </row>
@@ -4247,13 +4247,13 @@
         <v>46154</v>
       </c>
       <c r="B130" s="5" t="n">
-        <v>175521.25</v>
+        <v>227113.8</v>
       </c>
       <c r="C130" s="5" t="n">
-        <v>4514.1</v>
+        <v>8601.23</v>
       </c>
       <c r="D130" s="5" t="n">
-        <v>171007.15</v>
+        <v>218512.57</v>
       </c>
       <c r="E130" t="n">
         <v>3</v>
@@ -4265,12 +4265,12 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX short (risk 1,728)</t>
+          <t>Silver_Futures_COMEX short (risk 3,494)</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX stop (-1,685)</t>
+          <t>Gold_Futures_COMEX stop (-3,320)</t>
         </is>
       </c>
     </row>
@@ -4279,13 +4279,13 @@
         <v>46155</v>
       </c>
       <c r="B131" s="5" t="n">
-        <v>173789.78</v>
+        <v>223612.74</v>
       </c>
       <c r="C131" s="5" t="n">
-        <v>2786.23</v>
+        <v>5107.45</v>
       </c>
       <c r="D131" s="5" t="n">
-        <v>171003.56</v>
+        <v>218505.29</v>
       </c>
       <c r="E131" t="n">
         <v>2</v>
@@ -4298,7 +4298,7 @@
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX stop (-1,731)</t>
+          <t>Silver_Futures_COMEX stop (-3,501)</t>
         </is>
       </c>
     </row>
@@ -4307,13 +4307,13 @@
         <v>46156</v>
       </c>
       <c r="B132" s="5" t="n">
-        <v>173789.78</v>
+        <v>223612.74</v>
       </c>
       <c r="C132" s="5" t="n">
-        <v>4496.26</v>
+        <v>8544.540000000001</v>
       </c>
       <c r="D132" s="5" t="n">
-        <v>169293.52</v>
+        <v>215068.2</v>
       </c>
       <c r="E132" t="n">
         <v>3</v>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 1,710)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 3,437)</t>
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
@@ -4335,13 +4335,13 @@
         <v>46157</v>
       </c>
       <c r="B133" s="5" t="n">
-        <v>204592.35</v>
+        <v>280240.38</v>
       </c>
       <c r="C133" s="5" t="n">
-        <v>3096.14</v>
+        <v>5970.56</v>
       </c>
       <c r="D133" s="5" t="n">
-        <v>201496.21</v>
+        <v>274269.83</v>
       </c>
       <c r="E133" t="n">
         <v>2</v>
@@ -4354,7 +4354,7 @@
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures bearish_reversal (+30,803)</t>
+          <t>Corn_CBOT_Futures bearish_reversal (+56,628)</t>
         </is>
       </c>
     </row>
@@ -4363,13 +4363,13 @@
         <v>46160</v>
       </c>
       <c r="B134" s="5" t="n">
-        <v>220076.83</v>
+        <v>308542.26</v>
       </c>
       <c r="C134" s="5" t="n">
-        <v>1710.04</v>
+        <v>3437.09</v>
       </c>
       <c r="D134" s="5" t="n">
-        <v>218366.79</v>
+        <v>305105.17</v>
       </c>
       <c r="E134" t="n">
         <v>1</v>
@@ -4382,7 +4382,7 @@
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_CME bearish_reversal (+15,484)</t>
+          <t>Bitcoin_Per_USD_CME bearish_reversal (+28,302)</t>
         </is>
       </c>
     </row>
@@ -4391,13 +4391,13 @@
         <v>46161</v>
       </c>
       <c r="B135" s="5" t="n">
-        <v>220076.83</v>
+        <v>308542.26</v>
       </c>
       <c r="C135" s="5" t="n">
-        <v>1710.04</v>
+        <v>3437.09</v>
       </c>
       <c r="D135" s="5" t="n">
-        <v>218366.79</v>
+        <v>305105.17</v>
       </c>
       <c r="E135" t="n">
         <v>1</v>
@@ -4415,13 +4415,13 @@
         <v>46162</v>
       </c>
       <c r="B136" s="5" t="n">
-        <v>220076.83</v>
+        <v>308542.26</v>
       </c>
       <c r="C136" s="5" t="n">
-        <v>3893.7</v>
+        <v>8236.389999999999</v>
       </c>
       <c r="D136" s="5" t="n">
-        <v>216183.13</v>
+        <v>300305.87</v>
       </c>
       <c r="E136" t="n">
         <v>2</v>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures short (risk 2,184)</t>
+          <t>US_Dollar_Index_Futures short (risk 4,799)</t>
         </is>
       </c>
       <c r="H136" t="inlineStr"/>
@@ -4443,13 +4443,13 @@
         <v>46163</v>
       </c>
       <c r="B137" s="5" t="n">
-        <v>220076.83</v>
+        <v>308542.26</v>
       </c>
       <c r="C137" s="5" t="n">
-        <v>6055.53</v>
+        <v>12960.2</v>
       </c>
       <c r="D137" s="5" t="n">
-        <v>214021.3</v>
+        <v>295582.06</v>
       </c>
       <c r="E137" t="n">
         <v>3</v>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>NY_Palladium_Futures long (risk 2,162)</t>
+          <t>NY_Palladium_Futures long (risk 4,724)</t>
         </is>
       </c>
       <c r="H137" t="inlineStr"/>
@@ -4471,13 +4471,13 @@
         <v>46164</v>
       </c>
       <c r="B138" s="5" t="n">
-        <v>220076.83</v>
+        <v>308542.26</v>
       </c>
       <c r="C138" s="5" t="n">
-        <v>6055.53</v>
+        <v>12960.2</v>
       </c>
       <c r="D138" s="5" t="n">
-        <v>214021.3</v>
+        <v>295582.06</v>
       </c>
       <c r="E138" t="n">
         <v>3</v>
@@ -4495,13 +4495,13 @@
         <v>46167</v>
       </c>
       <c r="B139" s="5" t="n">
-        <v>220076.83</v>
+        <v>308542.26</v>
       </c>
       <c r="C139" s="5" t="n">
-        <v>6055.53</v>
+        <v>12960.2</v>
       </c>
       <c r="D139" s="5" t="n">
-        <v>214021.3</v>
+        <v>295582.06</v>
       </c>
       <c r="E139" t="n">
         <v>3</v>
@@ -4519,13 +4519,13 @@
         <v>46168</v>
       </c>
       <c r="B140" s="5" t="n">
-        <v>220076.83</v>
+        <v>308542.26</v>
       </c>
       <c r="C140" s="5" t="n">
-        <v>6055.53</v>
+        <v>12960.2</v>
       </c>
       <c r="D140" s="5" t="n">
-        <v>214021.3</v>
+        <v>295582.06</v>
       </c>
       <c r="E140" t="n">
         <v>3</v>
@@ -4543,13 +4543,13 @@
         <v>46169</v>
       </c>
       <c r="B141" s="5" t="n">
-        <v>220076.83</v>
+        <v>308542.26</v>
       </c>
       <c r="C141" s="5" t="n">
-        <v>6055.53</v>
+        <v>12960.2</v>
       </c>
       <c r="D141" s="5" t="n">
-        <v>214021.3</v>
+        <v>295582.06</v>
       </c>
       <c r="E141" t="n">
         <v>3</v>
@@ -4567,13 +4567,13 @@
         <v>46170</v>
       </c>
       <c r="B142" s="5" t="n">
-        <v>220076.83</v>
+        <v>308542.26</v>
       </c>
       <c r="C142" s="5" t="n">
-        <v>8195.75</v>
+        <v>17609.71</v>
       </c>
       <c r="D142" s="5" t="n">
-        <v>211881.08</v>
+        <v>290932.55</v>
       </c>
       <c r="E142" t="n">
         <v>4</v>
@@ -4585,7 +4585,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX long (risk 2,140)</t>
+          <t>Silver_Futures_COMEX long (risk 4,650)</t>
         </is>
       </c>
       <c r="H142" t="inlineStr"/>
@@ -4595,13 +4595,13 @@
         <v>46174</v>
       </c>
       <c r="B143" s="5" t="n">
-        <v>237364.61</v>
+        <v>343289.86</v>
       </c>
       <c r="C143" s="5" t="n">
-        <v>6485.71</v>
+        <v>14172.62</v>
       </c>
       <c r="D143" s="5" t="n">
-        <v>230878.9</v>
+        <v>329117.24</v>
       </c>
       <c r="E143" t="n">
         <v>3</v>
@@ -4614,7 +4614,7 @@
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT bearish_reversal (+17,288)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT bearish_reversal (+34,748)</t>
         </is>
       </c>
     </row>
@@ -4623,13 +4623,13 @@
         <v>46175</v>
       </c>
       <c r="B144" s="5" t="n">
-        <v>237364.61</v>
+        <v>343289.86</v>
       </c>
       <c r="C144" s="5" t="n">
-        <v>6485.71</v>
+        <v>14172.62</v>
       </c>
       <c r="D144" s="5" t="n">
-        <v>230878.9</v>
+        <v>329117.24</v>
       </c>
       <c r="E144" t="n">
         <v>3</v>
@@ -4647,13 +4647,13 @@
         <v>46176</v>
       </c>
       <c r="B145" s="5" t="n">
-        <v>235151.91</v>
+        <v>338454.9</v>
       </c>
       <c r="C145" s="5" t="n">
-        <v>4323.88</v>
+        <v>9448.809999999999</v>
       </c>
       <c r="D145" s="5" t="n">
-        <v>230828.03</v>
+        <v>329006.09</v>
       </c>
       <c r="E145" t="n">
         <v>2</v>
@@ -4666,7 +4666,7 @@
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr">
         <is>
-          <t>NY_Palladium_Futures stop (-2,213)</t>
+          <t>NY_Palladium_Futures stop (-4,835)</t>
         </is>
       </c>
     </row>
@@ -4675,13 +4675,13 @@
         <v>46177</v>
       </c>
       <c r="B146" s="5" t="n">
-        <v>235151.91</v>
+        <v>338454.9</v>
       </c>
       <c r="C146" s="5" t="n">
-        <v>4323.88</v>
+        <v>9448.809999999999</v>
       </c>
       <c r="D146" s="5" t="n">
-        <v>230828.03</v>
+        <v>329006.09</v>
       </c>
       <c r="E146" t="n">
         <v>2</v>
@@ -4699,13 +4699,13 @@
         <v>46178</v>
       </c>
       <c r="B147" s="5" t="n">
-        <v>230778.6</v>
+        <v>328897.56</v>
       </c>
       <c r="C147" s="5" t="n">
-        <v>2308.28</v>
+        <v>5175.27</v>
       </c>
       <c r="D147" s="5" t="n">
-        <v>228470.32</v>
+        <v>323722.29</v>
       </c>
       <c r="E147" t="n">
         <v>1</v>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini short (risk 2,308)</t>
+          <t>Dow_Futures_E_mini short (risk 5,175)</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX stop (-2,145); US_Dollar_Index_Futures stop (-2,228)</t>
+          <t>Silver_Futures_COMEX stop (-4,660); US_Dollar_Index_Futures stop (-4,898)</t>
         </is>
       </c>
     </row>
@@ -4731,13 +4731,13 @@
         <v>46181</v>
       </c>
       <c r="B148" s="5" t="n">
-        <v>230778.6</v>
+        <v>328897.56</v>
       </c>
       <c r="C148" s="5" t="n">
-        <v>6854.84</v>
+        <v>15279.47</v>
       </c>
       <c r="D148" s="5" t="n">
-        <v>223923.76</v>
+        <v>313618.09</v>
       </c>
       <c r="E148" t="n">
         <v>3</v>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX long (risk 2,285); US_Dollar_Index_Futures short (risk 2,262)</t>
+          <t>Gold_Futures_COMEX long (risk 5,092); US_Dollar_Index_Futures short (risk 5,012)</t>
         </is>
       </c>
       <c r="H148" t="inlineStr"/>
@@ -4759,13 +4759,13 @@
         <v>46182</v>
       </c>
       <c r="B149" s="5" t="n">
-        <v>228477</v>
+        <v>323767.76</v>
       </c>
       <c r="C149" s="5" t="n">
-        <v>4570.14</v>
+        <v>10187.32</v>
       </c>
       <c r="D149" s="5" t="n">
-        <v>223906.87</v>
+        <v>313580.44</v>
       </c>
       <c r="E149" t="n">
         <v>2</v>
@@ -4778,7 +4778,7 @@
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX stop (-2,302)</t>
+          <t>Gold_Futures_COMEX stop (-5,130)</t>
         </is>
       </c>
     </row>
@@ -4787,13 +4787,13 @@
         <v>46183</v>
       </c>
       <c r="B150" s="5" t="n">
-        <v>228477</v>
+        <v>323767.76</v>
       </c>
       <c r="C150" s="5" t="n">
-        <v>4570.14</v>
+        <v>10187.32</v>
       </c>
       <c r="D150" s="5" t="n">
-        <v>223906.87</v>
+        <v>313580.44</v>
       </c>
       <c r="E150" t="n">
         <v>2</v>
@@ -4811,13 +4811,13 @@
         <v>46184</v>
       </c>
       <c r="B151" s="5" t="n">
-        <v>226148.13</v>
+        <v>318607.2</v>
       </c>
       <c r="C151" s="5" t="n">
-        <v>4547.35</v>
+        <v>10107.89</v>
       </c>
       <c r="D151" s="5" t="n">
-        <v>221600.78</v>
+        <v>308499.31</v>
       </c>
       <c r="E151" t="n">
         <v>2</v>
@@ -4829,12 +4829,12 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX long (risk 2,239)</t>
+          <t>Gold_Futures_COMEX long (risk 4,933)</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures stop (-2,329)</t>
+          <t>US_Dollar_Index_Futures stop (-5,161)</t>
         </is>
       </c>
     </row>
@@ -4843,13 +4843,13 @@
         <v>46185</v>
       </c>
       <c r="B152" s="5" t="n">
-        <v>226148.13</v>
+        <v>318607.2</v>
       </c>
       <c r="C152" s="5" t="n">
-        <v>6763.36</v>
+        <v>14960.58</v>
       </c>
       <c r="D152" s="5" t="n">
-        <v>219384.77</v>
+        <v>303646.62</v>
       </c>
       <c r="E152" t="n">
         <v>3</v>
@@ -4861,7 +4861,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures long (risk 2,216)</t>
+          <t>Corn_CBOT_Futures long (risk 4,853)</t>
         </is>
       </c>
       <c r="H152" t="inlineStr"/>
@@ -4871,13 +4871,13 @@
         <v>46188</v>
       </c>
       <c r="B153" s="5" t="n">
-        <v>221208.44</v>
+        <v>307665.03</v>
       </c>
       <c r="C153" s="5" t="n">
-        <v>4432.92</v>
+        <v>9708.98</v>
       </c>
       <c r="D153" s="5" t="n">
-        <v>216775.52</v>
+        <v>297956.05</v>
       </c>
       <c r="E153" t="n">
         <v>2</v>
@@ -4889,12 +4889,12 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT long (risk 2,194)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT long (risk 4,776)</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures stop (-2,544); Dow_Futures_E_mini stop (-2,395)</t>
+          <t>Corn_CBOT_Futures stop (-5,572); Dow_Futures_E_mini stop (-5,371)</t>
         </is>
       </c>
     </row>
@@ -4903,13 +4903,13 @@
         <v>46189</v>
       </c>
       <c r="B154" s="5" t="n">
-        <v>221208.44</v>
+        <v>307665.03</v>
       </c>
       <c r="C154" s="5" t="n">
-        <v>4432.92</v>
+        <v>9708.98</v>
       </c>
       <c r="D154" s="5" t="n">
-        <v>216775.52</v>
+        <v>297956.05</v>
       </c>
       <c r="E154" t="n">
         <v>2</v>
@@ -4927,13 +4927,13 @@
         <v>46190</v>
       </c>
       <c r="B155" s="5" t="n">
-        <v>231944.9</v>
+        <v>331040.05</v>
       </c>
       <c r="C155" s="5" t="n">
-        <v>4406.82</v>
+        <v>9619.469999999999</v>
       </c>
       <c r="D155" s="5" t="n">
-        <v>227538.08</v>
+        <v>321420.58</v>
       </c>
       <c r="E155" t="n">
         <v>2</v>
@@ -4945,12 +4945,12 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures short (risk 2,168)</t>
+          <t>US_Dollar_Index_Futures short (risk 4,687)</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT bullish_reversal (+10,736)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT bullish_reversal (+23,375)</t>
         </is>
       </c>
     </row>
@@ -4959,13 +4959,13 @@
         <v>46191</v>
       </c>
       <c r="B156" s="5" t="n">
-        <v>229747.75</v>
+        <v>326289.65</v>
       </c>
       <c r="C156" s="5" t="n">
-        <v>2239.07</v>
+        <v>4932.62</v>
       </c>
       <c r="D156" s="5" t="n">
-        <v>227508.69</v>
+        <v>321357.03</v>
       </c>
       <c r="E156" t="n">
         <v>1</v>
@@ -4978,7 +4978,7 @@
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures stop (-2,197)</t>
+          <t>US_Dollar_Index_Futures stop (-4,750)</t>
         </is>
       </c>
     </row>
@@ -4987,13 +4987,13 @@
         <v>46192</v>
       </c>
       <c r="B157" s="5" t="n">
-        <v>229747.75</v>
+        <v>326289.65</v>
       </c>
       <c r="C157" s="5" t="n">
-        <v>4514.16</v>
+        <v>9987.57</v>
       </c>
       <c r="D157" s="5" t="n">
-        <v>225233.6</v>
+        <v>316302.09</v>
       </c>
       <c r="E157" t="n">
         <v>2</v>
@@ -5005,7 +5005,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures short (risk 2,275)</t>
+          <t>US_Dollar_Index_Futures short (risk 5,055)</t>
         </is>
       </c>
       <c r="H157" t="inlineStr"/>
@@ -5015,13 +5015,13 @@
         <v>46195</v>
       </c>
       <c r="B158" s="5" t="n">
-        <v>229747.75</v>
+        <v>326289.65</v>
       </c>
       <c r="C158" s="5" t="n">
-        <v>4514.16</v>
+        <v>9987.57</v>
       </c>
       <c r="D158" s="5" t="n">
-        <v>225233.6</v>
+        <v>316302.09</v>
       </c>
       <c r="E158" t="n">
         <v>2</v>
@@ -5039,13 +5039,13 @@
         <v>46196</v>
       </c>
       <c r="B159" s="5" t="n">
-        <v>227441.29</v>
+        <v>321164.98</v>
       </c>
       <c r="C159" s="5" t="n">
-        <v>4491.4</v>
+        <v>9908.049999999999</v>
       </c>
       <c r="D159" s="5" t="n">
-        <v>222949.88</v>
+        <v>311256.93</v>
       </c>
       <c r="E159" t="n">
         <v>2</v>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures long (risk 2,252)</t>
+          <t>NY_Platinum_Futures long (risk 4,975)</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures stop (-2,306)</t>
+          <t>US_Dollar_Index_Futures stop (-5,125)</t>
         </is>
       </c>
     </row>
@@ -5071,13 +5071,13 @@
         <v>46197</v>
       </c>
       <c r="B160" s="5" t="n">
-        <v>222890.19</v>
+        <v>311125.17</v>
       </c>
       <c r="C160" s="5" t="n">
-        <v>2229.5</v>
+        <v>4896.07</v>
       </c>
       <c r="D160" s="5" t="n">
-        <v>220660.7</v>
+        <v>306229.1</v>
       </c>
       <c r="E160" t="n">
         <v>1</v>
@@ -5089,12 +5089,12 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>EURO_Futures long (risk 2,229)</t>
+          <t>EURO_Futures long (risk 4,896)</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX stop (-2,255); NY_Platinum_Futures stop (-2,296)</t>
+          <t>Gold_Futures_COMEX stop (-4,967); NY_Platinum_Futures stop (-5,073)</t>
         </is>
       </c>
     </row>
@@ -5103,13 +5103,13 @@
         <v>46198</v>
       </c>
       <c r="B161" s="5" t="n">
-        <v>222890.19</v>
+        <v>311125.17</v>
       </c>
       <c r="C161" s="5" t="n">
-        <v>10924.41</v>
+        <v>23714.13</v>
       </c>
       <c r="D161" s="5" t="n">
-        <v>211965.78</v>
+        <v>287411.04</v>
       </c>
       <c r="E161" t="n">
         <v>5</v>
@@ -5121,7 +5121,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures short (risk 2,207); NY_Palladium_Futures long (risk 2,185); NY_Platinum_Futures long (risk 2,163); US_Dollar_Index_Futures short (risk 2,141)</t>
+          <t>NY_Natural_Gas_Futures short (risk 4,817); NY_Palladium_Futures long (risk 4,741); NY_Platinum_Futures long (risk 4,667); US_Dollar_Index_Futures short (risk 4,593)</t>
         </is>
       </c>
       <c r="H161" t="inlineStr"/>
@@ -5131,13 +5131,13 @@
         <v>46199</v>
       </c>
       <c r="B162" s="5" t="n">
-        <v>220503.46</v>
+        <v>305914.97</v>
       </c>
       <c r="C162" s="5" t="n">
-        <v>8717.799999999999</v>
+        <v>18897.14</v>
       </c>
       <c r="D162" s="5" t="n">
-        <v>211785.65</v>
+        <v>287017.82</v>
       </c>
       <c r="E162" t="n">
         <v>4</v>
@@ -5150,7 +5150,7 @@
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures stop (-2,387)</t>
+          <t>NY_Natural_Gas_Futures stop (-5,210)</t>
         </is>
       </c>
     </row>
@@ -5159,13 +5159,13 @@
         <v>46202</v>
       </c>
       <c r="B163" s="5" t="n">
-        <v>220503.46</v>
+        <v>305914.97</v>
       </c>
       <c r="C163" s="5" t="n">
-        <v>8717.799999999999</v>
+        <v>18897.14</v>
       </c>
       <c r="D163" s="5" t="n">
-        <v>211785.65</v>
+        <v>287017.82</v>
       </c>
       <c r="E163" t="n">
         <v>4</v>
@@ -5183,13 +5183,13 @@
         <v>46203</v>
       </c>
       <c r="B164" s="5" t="n">
-        <v>220503.46</v>
+        <v>305914.97</v>
       </c>
       <c r="C164" s="5" t="n">
-        <v>15008.05</v>
+        <v>32229.58</v>
       </c>
       <c r="D164" s="5" t="n">
-        <v>205495.41</v>
+        <v>273685.39</v>
       </c>
       <c r="E164" t="n">
         <v>7</v>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT long (risk 2,118); German_Long_Bund short (risk 2,097); Gold_Futures_COMEX long (risk 2,076)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT long (risk 4,515); German_Long_Bund short (risk 4,444); Gold_Futures_COMEX long (risk 4,374)</t>
         </is>
       </c>
       <c r="H164" t="inlineStr"/>
@@ -5211,13 +5211,13 @@
         <v>46204</v>
       </c>
       <c r="B165" s="5" t="n">
-        <v>218315.24</v>
+        <v>301193.27</v>
       </c>
       <c r="C165" s="5" t="n">
-        <v>16934.71</v>
+        <v>36105.37</v>
       </c>
       <c r="D165" s="5" t="n">
-        <v>201380.53</v>
+        <v>265087.9</v>
       </c>
       <c r="E165" t="n">
         <v>8</v>
@@ -5229,12 +5229,12 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini short (risk 2,055); Sugar_World_CSCE_Futures short (risk 2,034)</t>
+          <t>Dow_Futures_E_mini short (risk 4,305); Sugar_World_CSCE_Futures short (risk 4,237)</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures stop (-2,188)</t>
+          <t>NY_Platinum_Futures stop (-4,722)</t>
         </is>
       </c>
     </row>
@@ -5243,13 +5243,13 @@
         <v>46205</v>
       </c>
       <c r="B166" s="5" t="n">
-        <v>233366.76</v>
+        <v>333587.76</v>
       </c>
       <c r="C166" s="5" t="n">
-        <v>12738.69</v>
+        <v>27207.07</v>
       </c>
       <c r="D166" s="5" t="n">
-        <v>220628.07</v>
+        <v>306380.69</v>
       </c>
       <c r="E166" t="n">
         <v>6</v>
@@ -5262,7 +5262,7 @@
       <c r="G166" t="inlineStr"/>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini stop (-2,077); US_Dollar_Index_Futures bearish_reversal (+17,129)</t>
+          <t>Dow_Futures_E_mini stop (-4,351); US_Dollar_Index_Futures bearish_reversal (+36,746)</t>
         </is>
       </c>
     </row>
@@ -5271,13 +5271,13 @@
         <v>46206</v>
       </c>
       <c r="B167" s="5" t="n">
-        <v>233366.76</v>
+        <v>333587.76</v>
       </c>
       <c r="C167" s="5" t="n">
-        <v>12738.69</v>
+        <v>27207.07</v>
       </c>
       <c r="D167" s="5" t="n">
-        <v>220628.07</v>
+        <v>306380.69</v>
       </c>
       <c r="E167" t="n">
         <v>6</v>
@@ -5295,13 +5295,13 @@
         <v>46210</v>
       </c>
       <c r="B168" s="5" t="n">
-        <v>231019.37</v>
+        <v>328698.51</v>
       </c>
       <c r="C168" s="5" t="n">
-        <v>10704.29</v>
+        <v>22969.72</v>
       </c>
       <c r="D168" s="5" t="n">
-        <v>220315.08</v>
+        <v>305728.79</v>
       </c>
       <c r="E168" t="n">
         <v>5</v>
@@ -5314,7 +5314,7 @@
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Sugar_World_CSCE_Futures stop (-2,347)</t>
+          <t>Sugar_World_CSCE_Futures stop (-4,889)</t>
         </is>
       </c>
     </row>
@@ -5323,13 +5323,13 @@
         <v>46211</v>
       </c>
       <c r="B169" s="5" t="n">
-        <v>265738.14</v>
+        <v>402549.1</v>
       </c>
       <c r="C169" s="5" t="n">
-        <v>10874.02</v>
+        <v>23553.74</v>
       </c>
       <c r="D169" s="5" t="n">
-        <v>254864.12</v>
+        <v>378995.37</v>
       </c>
       <c r="E169" t="n">
         <v>5</v>
@@ -5341,12 +5341,12 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Live_Cattle_Futures_CME long (risk 2,203); NY_Natural_Gas_Futures short (risk 2,181)</t>
+          <t>Live_Cattle_Futures_CME long (risk 4,809); NY_Natural_Gas_Futures short (risk 4,733)</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT bullish_reversal (+21,592); German_Long_Bund bearish_reversal (+13,127)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT bullish_reversal (+46,029); German_Long_Bund bearish_reversal (+27,822)</t>
         </is>
       </c>
     </row>
@@ -5355,13 +5355,13 @@
         <v>46212</v>
       </c>
       <c r="B170" s="5" t="n">
-        <v>273564.62</v>
+        <v>419534.13</v>
       </c>
       <c r="C170" s="5" t="n">
-        <v>8692.9</v>
+        <v>18820.27</v>
       </c>
       <c r="D170" s="5" t="n">
-        <v>264871.72</v>
+        <v>400713.86</v>
       </c>
       <c r="E170" t="n">
         <v>4</v>
@@ -5374,7 +5374,7 @@
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures bearish_reversal (+7,826)</t>
+          <t>NY_Natural_Gas_Futures bearish_reversal (+16,985)</t>
         </is>
       </c>
     </row>
@@ -5383,13 +5383,13 @@
         <v>46213</v>
       </c>
       <c r="B171" s="5" t="n">
-        <v>271256.55</v>
+        <v>414496.01</v>
       </c>
       <c r="C171" s="5" t="n">
-        <v>6489.75</v>
+        <v>14011.16</v>
       </c>
       <c r="D171" s="5" t="n">
-        <v>264766.8</v>
+        <v>400484.85</v>
       </c>
       <c r="E171" t="n">
         <v>3</v>
@@ -5402,7 +5402,7 @@
       <c r="G171" t="inlineStr"/>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Live_Cattle_Futures_CME stop (-2,308)</t>
+          <t>Live_Cattle_Futures_CME stop (-5,038)</t>
         </is>
       </c>
     </row>
@@ -5411,13 +5411,13 @@
         <v>46216</v>
       </c>
       <c r="B172" s="5" t="n">
-        <v>271256.55</v>
+        <v>414496.01</v>
       </c>
       <c r="C172" s="5" t="n">
-        <v>9137.42</v>
+        <v>20310.78</v>
       </c>
       <c r="D172" s="5" t="n">
-        <v>262119.14</v>
+        <v>394185.22</v>
       </c>
       <c r="E172" t="n">
         <v>4</v>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 2,648)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 6,300)</t>
         </is>
       </c>
       <c r="H172" t="inlineStr"/>
@@ -5439,13 +5439,13 @@
         <v>46217</v>
       </c>
       <c r="B173" s="5" t="n">
-        <v>308451.17</v>
+        <v>495221.24</v>
       </c>
       <c r="C173" s="5" t="n">
-        <v>6952.88</v>
+        <v>15569.57</v>
       </c>
       <c r="D173" s="5" t="n">
-        <v>301498.29</v>
+        <v>479651.67</v>
       </c>
       <c r="E173" t="n">
         <v>3</v>
@@ -5458,7 +5458,7 @@
       <c r="G173" t="inlineStr"/>
       <c r="H173" t="inlineStr">
         <is>
-          <t>NY_Palladium_Futures bullish_reversal (+37,195)</t>
+          <t>NY_Palladium_Futures bullish_reversal (+80,725)</t>
         </is>
       </c>
     </row>
@@ -5467,13 +5467,13 @@
         <v>46218</v>
       </c>
       <c r="B174" s="5" t="n">
-        <v>305672.75</v>
+        <v>488610.52</v>
       </c>
       <c r="C174" s="5" t="n">
-        <v>4305.21</v>
+        <v>9269.940000000001</v>
       </c>
       <c r="D174" s="5" t="n">
-        <v>301367.54</v>
+        <v>479340.58</v>
       </c>
       <c r="E174" t="n">
         <v>2</v>
@@ -5486,7 +5486,7 @@
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT stop (-2,778)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT stop (-6,611)</t>
         </is>
       </c>
     </row>
@@ -5495,13 +5495,13 @@
         <v>46219</v>
       </c>
       <c r="B175" s="5" t="n">
-        <v>305672.75</v>
+        <v>488610.52</v>
       </c>
       <c r="C175" s="5" t="n">
-        <v>4305.21</v>
+        <v>9269.940000000001</v>
       </c>
       <c r="D175" s="5" t="n">
-        <v>301367.54</v>
+        <v>479340.58</v>
       </c>
       <c r="E175" t="n">
         <v>2</v>
@@ -5519,13 +5519,13 @@
         <v>46220</v>
       </c>
       <c r="B176" s="5" t="n">
-        <v>305672.75</v>
+        <v>488610.52</v>
       </c>
       <c r="C176" s="5" t="n">
-        <v>4305.21</v>
+        <v>9269.940000000001</v>
       </c>
       <c r="D176" s="5" t="n">
-        <v>301367.54</v>
+        <v>479340.58</v>
       </c>
       <c r="E176" t="n">
         <v>2</v>
@@ -5543,13 +5543,13 @@
         <v>46223</v>
       </c>
       <c r="B177" s="5" t="n">
-        <v>305672.75</v>
+        <v>488610.52</v>
       </c>
       <c r="C177" s="5" t="n">
-        <v>4305.21</v>
+        <v>9269.940000000001</v>
       </c>
       <c r="D177" s="5" t="n">
-        <v>301367.54</v>
+        <v>479340.58</v>
       </c>
       <c r="E177" t="n">
         <v>2</v>
@@ -5567,13 +5567,13 @@
         <v>46224</v>
       </c>
       <c r="B178" s="5" t="n">
-        <v>305672.75</v>
+        <v>488610.52</v>
       </c>
       <c r="C178" s="5" t="n">
-        <v>4305.21</v>
+        <v>9269.940000000001</v>
       </c>
       <c r="D178" s="5" t="n">
-        <v>301367.54</v>
+        <v>479340.58</v>
       </c>
       <c r="E178" t="n">
         <v>2</v>
@@ -5591,13 +5591,13 @@
         <v>46225</v>
       </c>
       <c r="B179" s="5" t="n">
-        <v>305672.75</v>
+        <v>488610.52</v>
       </c>
       <c r="C179" s="5" t="n">
-        <v>4305.21</v>
+        <v>9269.940000000001</v>
       </c>
       <c r="D179" s="5" t="n">
-        <v>301367.54</v>
+        <v>479340.58</v>
       </c>
       <c r="E179" t="n">
         <v>2</v>
@@ -5615,13 +5615,13 @@
         <v>46226</v>
       </c>
       <c r="B180" s="5" t="n">
-        <v>305672.75</v>
+        <v>488610.52</v>
       </c>
       <c r="C180" s="5" t="n">
-        <v>4305.21</v>
+        <v>9269.940000000001</v>
       </c>
       <c r="D180" s="5" t="n">
-        <v>301367.54</v>
+        <v>479340.58</v>
       </c>
       <c r="E180" t="n">
         <v>2</v>
@@ -5639,13 +5639,13 @@
         <v>46227</v>
       </c>
       <c r="B181" s="5" t="n">
-        <v>305525.99</v>
+        <v>488249.74</v>
       </c>
       <c r="C181" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D181" s="5" t="n">
-        <v>305525.99</v>
+        <v>488249.74</v>
       </c>
       <c r="E181" t="n">
         <v>0</v>
@@ -5653,7 +5653,7 @@
       <c r="F181" t="inlineStr"/>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 3,014); Corn_CBOT_Futures short (risk 2,984)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 7,540); Corn_CBOT_Futures short (risk 7,421)</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -5796,13 +5796,13 @@
         <v>100000</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>1000</v>
+        <v>1573</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>11493.95</v>
+        <v>18079.99</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>111493.95</v>
+        <v>118079.99</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -5844,16 +5844,16 @@
         <v>-1.014</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>111493.95</v>
+        <v>118079.99</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>1114.94</v>
+        <v>1857.4</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>-1131.1</v>
+        <v>-1884.32</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>110362.85</v>
+        <v>116195.67</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -5895,16 +5895,16 @@
         <v>-1.008</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>110362.85</v>
+        <v>116195.67</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>1103.63</v>
+        <v>1827.76</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>-1112.35</v>
+        <v>-1842.21</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>109250.5</v>
+        <v>114353.46</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -5946,16 +5946,16 @@
         <v>-1.005</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>109259.23</v>
+        <v>114367.91</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>1092.59</v>
+        <v>1799.01</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>-1097.88</v>
+        <v>-1807.71</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>108152.62</v>
+        <v>112545.75</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -5997,16 +5997,16 @@
         <v>-1.085</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>108152.62</v>
+        <v>112545.75</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>1081.53</v>
+        <v>1770.34</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>-1173.57</v>
+        <v>-1921.01</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>106979.05</v>
+        <v>110624.74</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -6048,16 +6048,16 @@
         <v>4.314</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>106979.05</v>
+        <v>110624.74</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>1069.79</v>
+        <v>1740.13</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>4615.25</v>
+        <v>7507.18</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>111594.3</v>
+        <v>118131.92</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -6099,16 +6099,16 @@
         <v>-1.006</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>105909.26</v>
+        <v>108884.61</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>1059.09</v>
+        <v>1712.75</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>-1065.68</v>
+        <v>-1723.41</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>110528.62</v>
+        <v>116408.52</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -6150,16 +6150,16 @@
         <v>-1.222</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>110535.21</v>
+        <v>116419.17</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>1105.35</v>
+        <v>1831.27</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>-1350.99</v>
+        <v>-2238.22</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>109177.63</v>
+        <v>114170.29</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -6201,16 +6201,16 @@
         <v>-1.069</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>109423.26</v>
+        <v>114577.24</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>1094.23</v>
+        <v>1802.3</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>-1169.7</v>
+        <v>-1926.6</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>108007.93</v>
+        <v>112243.7</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -6252,16 +6252,16 @@
         <v>-1.06</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>108329.03</v>
+        <v>112774.94</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>1083.29</v>
+        <v>1773.95</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>-1147.96</v>
+        <v>-1879.86</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>106859.97</v>
+        <v>110363.84</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -6303,16 +6303,16 @@
         <v>-1.004</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>107245.74</v>
+        <v>111000.99</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>1072.46</v>
+        <v>1746.05</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>-1076.56</v>
+        <v>-1752.73</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>104733.91</v>
+        <v>106925.92</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -6354,16 +6354,16 @@
         <v>-1.026</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>105927.65</v>
+        <v>108848</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>1059.28</v>
+        <v>1712.18</v>
       </c>
       <c r="K13" s="7" t="n">
-        <v>-1087.15</v>
+        <v>-1757.24</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>102615.63</v>
+        <v>103532.18</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -6405,16 +6405,16 @@
         <v>-1.002</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>104728.24</v>
+        <v>106905.61</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>1047.28</v>
+        <v>1681.63</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>-1049.5</v>
+        <v>-1685.18</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>105810.47</v>
+        <v>108678.65</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -6456,16 +6456,16 @@
         <v>-1.001</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>103680.95</v>
+        <v>105223.99</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>1036.81</v>
+        <v>1655.17</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>-1038.19</v>
+        <v>-1657.38</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>101577.44</v>
+        <v>101874.8</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -6507,16 +6507,16 @@
         <v>-1.005</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>102637.82</v>
+        <v>103558.57</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>1026.38</v>
+        <v>1628.98</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>-1031.12</v>
+        <v>-1636.51</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>103702.78</v>
+        <v>105289.42</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -6558,16 +6558,16 @@
         <v>2.372</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>101611.44</v>
+        <v>101929.6</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>1016.11</v>
+        <v>1603.35</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>2410.65</v>
+        <v>3803.82</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>107632.38</v>
+        <v>110991.87</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -6609,16 +6609,16 @@
         <v>-1.009</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>100590.58</v>
+        <v>100318.71</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>1005.91</v>
+        <v>1578.01</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>-1014.97</v>
+        <v>-1592.23</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>100562.47</v>
+        <v>100282.57</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -6660,16 +6660,16 @@
         <v>-1.138</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>99555.42</v>
+        <v>98693.42999999999</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>995.55</v>
+        <v>1552.45</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>-1132.87</v>
+        <v>-1766.58</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>99429.60000000001</v>
+        <v>98515.99000000001</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -6711,16 +6711,16 @@
         <v>-1.001</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>98550.8</v>
+        <v>97126.77</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>985.51</v>
+        <v>1527.8</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>-986.52</v>
+        <v>-1529.38</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>97464.64999999999</v>
+        <v>95479.82000000001</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -6762,16 +6762,16 @@
         <v>-1.004</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>97427.98</v>
+        <v>95384.83</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>974.28</v>
+        <v>1500.4</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>-978.4299999999999</v>
+        <v>-1506.79</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>98451.17</v>
+        <v>97009.2</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -6813,16 +6813,16 @@
         <v>-1.286</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>96448.53</v>
+        <v>93876.47</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>964.49</v>
+        <v>1476.68</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>-1240.05</v>
+        <v>-1898.58</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>106274.5</v>
+        <v>108790.57</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -6864,16 +6864,16 @@
         <v>-1.103</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>95484.05</v>
+        <v>92399.78999999999</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>954.84</v>
+        <v>1453.45</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>-1052.77</v>
+        <v>-1602.52</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>105221.73</v>
+        <v>107188.04</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -6915,16 +6915,16 @@
         <v>10.632</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>94529.21000000001</v>
+        <v>90946.34</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>945.29</v>
+        <v>1430.59</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>10049.91</v>
+        <v>15209.33</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>107514.56</v>
+        <v>110689.15</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -6966,16 +6966,16 @@
         <v>4.243</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>104205.62</v>
+        <v>105584.69</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>1042.06</v>
+        <v>1660.85</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>4421.52</v>
+        <v>7047.09</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>109745.59</v>
+        <v>114324.5</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -7017,16 +7017,16 @@
         <v>-1.174</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>106590.32</v>
+        <v>109331.02</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>1065.9</v>
+        <v>1719.78</v>
       </c>
       <c r="K26" s="7" t="n">
-        <v>-1251.28</v>
+        <v>-2018.87</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>106381.1</v>
+        <v>108973</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -7068,16 +7068,16 @@
         <v>-1.002</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>105524.42</v>
+        <v>107611.24</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>1055.24</v>
+        <v>1692.72</v>
       </c>
       <c r="K27" s="7" t="n">
-        <v>-1057.03</v>
+        <v>-1695.59</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>105324.07</v>
+        <v>107277.41</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -7119,16 +7119,16 @@
         <v>-1.091</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>104283.8</v>
+        <v>105619.43</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>1042.84</v>
+        <v>1661.39</v>
       </c>
       <c r="K28" s="7" t="n">
-        <v>-1137.64</v>
+        <v>-1812.43</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>108607.95</v>
+        <v>112512.07</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -7170,16 +7170,16 @@
         <v>10.606</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>108607.95</v>
+        <v>112512.07</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>1086.08</v>
+        <v>1769.81</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>11519.38</v>
+        <v>18771.34</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>120127.32</v>
+        <v>131283.41</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -7221,16 +7221,16 @@
         <v>-1.031</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>107521.87</v>
+        <v>110742.26</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>1075.22</v>
+        <v>1741.98</v>
       </c>
       <c r="K30" s="7" t="n">
-        <v>-1108.05</v>
+        <v>-1795.17</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>119019.27</v>
+        <v>129488.24</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -7272,16 +7272,16 @@
         <v>7.042</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>119052.11</v>
+        <v>129541.43</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>1190.52</v>
+        <v>2037.69</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>8383.09</v>
+        <v>14348.44</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>126176.05</v>
+        <v>141762.24</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -7323,16 +7323,16 @@
         <v>14.681</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>117861.58</v>
+        <v>127503.75</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>1178.62</v>
+        <v>2005.63</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>17302.74</v>
+        <v>29443.82</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>170533.66</v>
+        <v>218002.95</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -7374,16 +7374,16 @@
         <v>-1.051</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>116650.14</v>
+        <v>125444.92</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>1166.5</v>
+        <v>1973.25</v>
       </c>
       <c r="K33" s="7" t="n">
-        <v>-1226.32</v>
+        <v>-2074.44</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>117792.95</v>
+        <v>127413.8</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -7425,16 +7425,16 @@
         <v>-1.004</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>124997.43</v>
+        <v>139756.6</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>1249.97</v>
+        <v>2198.37</v>
       </c>
       <c r="K34" s="7" t="n">
-        <v>-1254.36</v>
+        <v>-2206.08</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>124921.69</v>
+        <v>139556.15</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -7476,16 +7476,16 @@
         <v>-1.25</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>123747.46</v>
+        <v>137558.23</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>1237.47</v>
+        <v>2163.79</v>
       </c>
       <c r="K35" s="7" t="n">
-        <v>-1546.84</v>
+        <v>-2704.74</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>123374.84</v>
+        <v>136851.42</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -7527,16 +7527,16 @@
         <v>25.818</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>122509.98</v>
+        <v>135394.44</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>1225.1</v>
+        <v>2129.75</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>31629.86</v>
+        <v>54986.42</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>155004.71</v>
+        <v>191837.83</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -7578,16 +7578,16 @@
         <v>-1.008</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>121284.88</v>
+        <v>133264.69</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>1212.85</v>
+        <v>2096.25</v>
       </c>
       <c r="K37" s="7" t="n">
-        <v>-1222.09</v>
+        <v>-2112.22</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>154905.87</v>
+        <v>191655.77</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -7629,16 +7629,16 @@
         <v>0.9350000000000001</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>120072.03</v>
+        <v>131168.43</v>
       </c>
       <c r="J38" s="5" t="n">
-        <v>1200.72</v>
+        <v>2063.28</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>1123.25</v>
+        <v>1930.16</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>156127.96</v>
+        <v>193768</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -7680,16 +7680,16 @@
         <v>-1.066</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>153736.5</v>
+        <v>189666.11</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>1537.36</v>
+        <v>2983.45</v>
       </c>
       <c r="K39" s="7" t="n">
-        <v>-1638.18</v>
+        <v>-3179.08</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>153267.7</v>
+        <v>188476.69</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
@@ -7731,16 +7731,16 @@
         <v>-1.008</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>152189.89</v>
+        <v>186666.69</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>1521.9</v>
+        <v>2936.27</v>
       </c>
       <c r="K40" s="7" t="n">
-        <v>-1534.42</v>
+        <v>-2960.43</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>148435.4</v>
+        <v>179229.94</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
@@ -7782,16 +7782,16 @@
         <v>-1.002</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>150667.99</v>
+        <v>183730.42</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>1506.68</v>
+        <v>2890.08</v>
       </c>
       <c r="K41" s="7" t="n">
-        <v>-1510.29</v>
+        <v>-2897</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>151757.41</v>
+        <v>185579.69</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -7833,16 +7833,16 @@
         <v>6.225</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>149161.31</v>
+        <v>180840.34</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>1491.61</v>
+        <v>2844.62</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>9284.889999999999</v>
+        <v>17706.98</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>156304.94</v>
+        <v>194319.63</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -7884,16 +7884,16 @@
         <v>-1.211</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>147669.7</v>
+        <v>177995.72</v>
       </c>
       <c r="J43" s="5" t="n">
-        <v>1476.7</v>
+        <v>2799.87</v>
       </c>
       <c r="K43" s="7" t="n">
-        <v>-1787.58</v>
+        <v>-3389.32</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>149969.83</v>
+        <v>182190.37</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -7935,16 +7935,16 @@
         <v>-1.108</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>146088.58</v>
+        <v>174993.3</v>
       </c>
       <c r="J44" s="5" t="n">
-        <v>1460.89</v>
+        <v>2752.64</v>
       </c>
       <c r="K44" s="7" t="n">
-        <v>-1618.82</v>
+        <v>-3050.23</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>154686.12</v>
+        <v>191269.4</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
@@ -7986,16 +7986,16 @@
         <v>6.688</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>144627.7</v>
+        <v>172240.65</v>
       </c>
       <c r="J45" s="5" t="n">
-        <v>1446.28</v>
+        <v>2709.35</v>
       </c>
       <c r="K45" s="6" t="n">
-        <v>9672.700000000001</v>
+        <v>18120.1</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>178690.26</v>
+        <v>233239.44</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
@@ -8037,16 +8037,16 @@
         <v>-1.016</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>143181.42</v>
+        <v>169531.31</v>
       </c>
       <c r="J46" s="5" t="n">
-        <v>1431.81</v>
+        <v>2666.73</v>
       </c>
       <c r="K46" s="7" t="n">
-        <v>-1455.19</v>
+        <v>-2710.27</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>153230.93</v>
+        <v>188559.13</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
@@ -8088,16 +8088,16 @@
         <v>-1.001</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>141438.72</v>
+        <v>166275.13</v>
       </c>
       <c r="J47" s="5" t="n">
-        <v>1414.39</v>
+        <v>2615.51</v>
       </c>
       <c r="K47" s="7" t="n">
-        <v>-1415.35</v>
+        <v>-2617.29</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>147020.05</v>
+        <v>176612.65</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
@@ -8139,16 +8139,16 @@
         <v>22</v>
       </c>
       <c r="I48" s="5" t="n">
-        <v>140011.81</v>
+        <v>163635.46</v>
       </c>
       <c r="J48" s="5" t="n">
-        <v>1400.12</v>
+        <v>2573.99</v>
       </c>
       <c r="K48" s="6" t="n">
-        <v>30802.57</v>
+        <v>56627.64</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>204592.35</v>
+        <v>280240.38</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
@@ -8190,16 +8190,16 @@
         <v>11.171</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>138610.73</v>
+        <v>161059.69</v>
       </c>
       <c r="J49" s="5" t="n">
-        <v>1386.11</v>
+        <v>2533.47</v>
       </c>
       <c r="K49" s="6" t="n">
-        <v>15484.48</v>
+        <v>28301.88</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>220076.83</v>
+        <v>308542.26</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
@@ -8241,16 +8241,16 @@
         <v>-1.026</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>147819.81</v>
+        <v>178736.7</v>
       </c>
       <c r="J50" s="5" t="n">
-        <v>1478.2</v>
+        <v>2811.53</v>
       </c>
       <c r="K50" s="7" t="n">
-        <v>-1516.1</v>
+        <v>-2883.62</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>169017.56</v>
+        <v>215119.33</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
@@ -8292,16 +8292,16 @@
         <v>-1.014</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>146341.61</v>
+        <v>175925.17</v>
       </c>
       <c r="J51" s="5" t="n">
-        <v>1463.42</v>
+        <v>2767.3</v>
       </c>
       <c r="K51" s="7" t="n">
-        <v>-1483.53</v>
+        <v>-2805.34</v>
       </c>
       <c r="L51" s="5" t="n">
-        <v>177206.73</v>
+        <v>230434.09</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -8343,16 +8343,16 @@
         <v>-1.032</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>163321.65</v>
+        <v>204535.23</v>
       </c>
       <c r="J52" s="5" t="n">
-        <v>1633.22</v>
+        <v>3217.34</v>
       </c>
       <c r="K52" s="7" t="n">
-        <v>-1685.48</v>
+        <v>-3320.29</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>175521.25</v>
+        <v>227113.8</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
@@ -8394,16 +8394,16 @@
         <v>-1.002</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>172787.29</v>
+        <v>222109.3</v>
       </c>
       <c r="J53" s="5" t="n">
-        <v>1727.87</v>
+        <v>3493.78</v>
       </c>
       <c r="K53" s="7" t="n">
-        <v>-1731.47</v>
+        <v>-3501.06</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>173789.78</v>
+        <v>223612.74</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
@@ -8445,16 +8445,16 @@
         <v>10.11</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>171003.56</v>
+        <v>218505.29</v>
       </c>
       <c r="J54" s="5" t="n">
-        <v>1710.04</v>
+        <v>3437.09</v>
       </c>
       <c r="K54" s="6" t="n">
-        <v>17287.78</v>
+        <v>34747.6</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>237364.61</v>
+        <v>343289.86</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
@@ -8496,16 +8496,16 @@
         <v>-1.021</v>
       </c>
       <c r="I55" s="5" t="n">
-        <v>218366.79</v>
+        <v>305105.17</v>
       </c>
       <c r="J55" s="5" t="n">
-        <v>2183.67</v>
+        <v>4799.3</v>
       </c>
       <c r="K55" s="7" t="n">
-        <v>-2228.46</v>
+        <v>-4897.75</v>
       </c>
       <c r="L55" s="5" t="n">
-        <v>230778.6</v>
+        <v>328897.56</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
@@ -8547,16 +8547,16 @@
         <v>-1.024</v>
       </c>
       <c r="I56" s="5" t="n">
-        <v>216183.13</v>
+        <v>300305.87</v>
       </c>
       <c r="J56" s="5" t="n">
-        <v>2161.83</v>
+        <v>4723.81</v>
       </c>
       <c r="K56" s="7" t="n">
-        <v>-2212.7</v>
+        <v>-4834.96</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>235151.91</v>
+        <v>338454.9</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
@@ -8598,16 +8598,16 @@
         <v>-1.002</v>
       </c>
       <c r="I57" s="5" t="n">
-        <v>214021.3</v>
+        <v>295582.06</v>
       </c>
       <c r="J57" s="5" t="n">
-        <v>2140.21</v>
+        <v>4649.51</v>
       </c>
       <c r="K57" s="7" t="n">
-        <v>-2144.85</v>
+        <v>-4659.59</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>233007.06</v>
+        <v>333795.31</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
@@ -8649,16 +8649,16 @@
         <v>-1.038</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>230828.03</v>
+        <v>329006.09</v>
       </c>
       <c r="J58" s="5" t="n">
-        <v>2308.28</v>
+        <v>5175.27</v>
       </c>
       <c r="K58" s="7" t="n">
-        <v>-2395.39</v>
+        <v>-5370.56</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>221208.44</v>
+        <v>307665.03</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
@@ -8700,16 +8700,16 @@
         <v>-1.007</v>
       </c>
       <c r="I59" s="5" t="n">
-        <v>228470.32</v>
+        <v>323722.29</v>
       </c>
       <c r="J59" s="5" t="n">
-        <v>2284.7</v>
+        <v>5092.15</v>
       </c>
       <c r="K59" s="7" t="n">
-        <v>-2301.6</v>
+        <v>-5129.8</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>228477</v>
+        <v>323767.76</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
@@ -8751,16 +8751,16 @@
         <v>-1.03</v>
       </c>
       <c r="I60" s="5" t="n">
-        <v>226185.61</v>
+        <v>318630.14</v>
       </c>
       <c r="J60" s="5" t="n">
-        <v>2261.86</v>
+        <v>5012.05</v>
       </c>
       <c r="K60" s="7" t="n">
-        <v>-2328.87</v>
+        <v>-5160.56</v>
       </c>
       <c r="L60" s="5" t="n">
-        <v>226148.13</v>
+        <v>318607.2</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
@@ -8802,16 +8802,16 @@
         <v>-1.007</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>223906.87</v>
+        <v>313580.44</v>
       </c>
       <c r="J61" s="5" t="n">
-        <v>2239.07</v>
+        <v>4932.62</v>
       </c>
       <c r="K61" s="7" t="n">
-        <v>-2254.81</v>
+        <v>-4967.3</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>225186.48</v>
+        <v>316197.69</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
@@ -8853,16 +8853,16 @@
         <v>-1.148</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>221600.78</v>
+        <v>308499.31</v>
       </c>
       <c r="J62" s="5" t="n">
-        <v>2216.01</v>
+        <v>4852.69</v>
       </c>
       <c r="K62" s="7" t="n">
-        <v>-2544.31</v>
+        <v>-5571.61</v>
       </c>
       <c r="L62" s="5" t="n">
-        <v>223603.82</v>
+        <v>313035.59</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
@@ -8904,16 +8904,16 @@
         <v>4.894</v>
       </c>
       <c r="I63" s="5" t="n">
-        <v>219384.77</v>
+        <v>303646.62</v>
       </c>
       <c r="J63" s="5" t="n">
-        <v>2193.85</v>
+        <v>4776.36</v>
       </c>
       <c r="K63" s="6" t="n">
-        <v>10736.46</v>
+        <v>23375.02</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>231944.9</v>
+        <v>331040.05</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
@@ -8955,16 +8955,16 @@
         <v>-1.014</v>
       </c>
       <c r="I64" s="5" t="n">
-        <v>216775.52</v>
+        <v>297956.05</v>
       </c>
       <c r="J64" s="5" t="n">
-        <v>2167.76</v>
+        <v>4686.85</v>
       </c>
       <c r="K64" s="7" t="n">
-        <v>-2197.15</v>
+        <v>-4750.4</v>
       </c>
       <c r="L64" s="5" t="n">
-        <v>229747.75</v>
+        <v>326289.65</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
@@ -9006,16 +9006,16 @@
         <v>-1.014</v>
       </c>
       <c r="I65" s="5" t="n">
-        <v>227508.69</v>
+        <v>321357.03</v>
       </c>
       <c r="J65" s="5" t="n">
-        <v>2275.09</v>
+        <v>5054.95</v>
       </c>
       <c r="K65" s="7" t="n">
-        <v>-2306.47</v>
+        <v>-5124.67</v>
       </c>
       <c r="L65" s="5" t="n">
-        <v>227441.29</v>
+        <v>321164.98</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
@@ -9057,16 +9057,16 @@
         <v>-1.02</v>
       </c>
       <c r="I66" s="5" t="n">
-        <v>225233.6</v>
+        <v>316302.09</v>
       </c>
       <c r="J66" s="5" t="n">
-        <v>2252.34</v>
+        <v>4975.43</v>
       </c>
       <c r="K66" s="7" t="n">
-        <v>-2296.28</v>
+        <v>-5072.51</v>
       </c>
       <c r="L66" s="5" t="n">
-        <v>222890.19</v>
+        <v>311125.17</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
@@ -9100,16 +9100,16 @@
         <v>-0.004</v>
       </c>
       <c r="I67" s="5" t="n">
-        <v>222949.88</v>
+        <v>311256.93</v>
       </c>
       <c r="J67" s="5" t="n">
-        <v>2229.5</v>
+        <v>4896.07</v>
       </c>
       <c r="K67" s="7" t="n">
-        <v>-8.08</v>
+        <v>-17.74</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>305533.22</v>
+        <v>488264.98</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
@@ -9151,16 +9151,16 @@
         <v>-1.082</v>
       </c>
       <c r="I68" s="5" t="n">
-        <v>220660.7</v>
+        <v>306229.1</v>
       </c>
       <c r="J68" s="5" t="n">
-        <v>2206.61</v>
+        <v>4816.98</v>
       </c>
       <c r="K68" s="7" t="n">
-        <v>-2386.74</v>
+        <v>-5210.21</v>
       </c>
       <c r="L68" s="5" t="n">
-        <v>220503.46</v>
+        <v>305914.97</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
@@ -9202,16 +9202,16 @@
         <v>17.026</v>
       </c>
       <c r="I69" s="5" t="n">
-        <v>218454.09</v>
+        <v>301412.12</v>
       </c>
       <c r="J69" s="5" t="n">
-        <v>2184.54</v>
+        <v>4741.21</v>
       </c>
       <c r="K69" s="6" t="n">
-        <v>37194.61</v>
+        <v>80725.23</v>
       </c>
       <c r="L69" s="5" t="n">
-        <v>308451.17</v>
+        <v>495221.24</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
@@ -9253,16 +9253,16 @@
         <v>-1.012</v>
       </c>
       <c r="I70" s="5" t="n">
-        <v>216269.55</v>
+        <v>296670.9</v>
       </c>
       <c r="J70" s="5" t="n">
-        <v>2162.7</v>
+        <v>4666.63</v>
       </c>
       <c r="K70" s="7" t="n">
-        <v>-2188.21</v>
+        <v>-4721.7</v>
       </c>
       <c r="L70" s="5" t="n">
-        <v>218315.24</v>
+        <v>301193.27</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
@@ -9304,16 +9304,16 @@
         <v>8</v>
       </c>
       <c r="I71" s="5" t="n">
-        <v>214106.85</v>
+        <v>292004.27</v>
       </c>
       <c r="J71" s="5" t="n">
-        <v>2141.07</v>
+        <v>4593.23</v>
       </c>
       <c r="K71" s="6" t="n">
-        <v>17128.57</v>
+        <v>36745.86</v>
       </c>
       <c r="L71" s="5" t="n">
-        <v>233366.76</v>
+        <v>333587.76</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
@@ -9355,16 +9355,16 @@
         <v>10.195</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>211785.65</v>
+        <v>287017.82</v>
       </c>
       <c r="J72" s="5" t="n">
-        <v>2117.86</v>
+        <v>4514.79</v>
       </c>
       <c r="K72" s="6" t="n">
-        <v>21591.8</v>
+        <v>46028.83</v>
       </c>
       <c r="L72" s="5" t="n">
-        <v>252611.17</v>
+        <v>374727.34</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
@@ -9406,16 +9406,16 @@
         <v>6.261</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>209667.8</v>
+        <v>282503.03</v>
       </c>
       <c r="J73" s="5" t="n">
-        <v>2096.68</v>
+        <v>4443.77</v>
       </c>
       <c r="K73" s="6" t="n">
-        <v>13126.97</v>
+        <v>27821.77</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>265738.14</v>
+        <v>402549.1</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
@@ -9449,16 +9449,16 @@
         <v>-0.003</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>207571.12</v>
+        <v>278059.26</v>
       </c>
       <c r="J74" s="5" t="n">
-        <v>2075.71</v>
+        <v>4373.87</v>
       </c>
       <c r="K74" s="7" t="n">
-        <v>-7.23</v>
+        <v>-15.24</v>
       </c>
       <c r="L74" s="5" t="n">
-        <v>305525.99</v>
+        <v>488249.74</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
@@ -9500,16 +9500,16 @@
         <v>-1.011</v>
       </c>
       <c r="I75" s="5" t="n">
-        <v>205495.41</v>
+        <v>273685.39</v>
       </c>
       <c r="J75" s="5" t="n">
-        <v>2054.95</v>
+        <v>4305.07</v>
       </c>
       <c r="K75" s="7" t="n">
-        <v>-2077.05</v>
+        <v>-4351.36</v>
       </c>
       <c r="L75" s="5" t="n">
-        <v>216238.19</v>
+        <v>296841.91</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
@@ -9551,16 +9551,16 @@
         <v>-1.154</v>
       </c>
       <c r="I76" s="5" t="n">
-        <v>203440.45</v>
+        <v>269380.31</v>
       </c>
       <c r="J76" s="5" t="n">
-        <v>2034.4</v>
+        <v>4237.35</v>
       </c>
       <c r="K76" s="7" t="n">
-        <v>-2347.39</v>
+        <v>-4889.25</v>
       </c>
       <c r="L76" s="5" t="n">
-        <v>231019.37</v>
+        <v>328698.51</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
@@ -9602,16 +9602,16 @@
         <v>-1.048</v>
       </c>
       <c r="I77" s="5" t="n">
-        <v>220315.08</v>
+        <v>305728.79</v>
       </c>
       <c r="J77" s="5" t="n">
-        <v>2203.15</v>
+        <v>4809.11</v>
       </c>
       <c r="K77" s="7" t="n">
-        <v>-2308.06</v>
+        <v>-5038.12</v>
       </c>
       <c r="L77" s="5" t="n">
-        <v>271256.55</v>
+        <v>414496.01</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
@@ -9653,16 +9653,16 @@
         <v>3.588</v>
       </c>
       <c r="I78" s="5" t="n">
-        <v>218111.93</v>
+        <v>300919.68</v>
       </c>
       <c r="J78" s="5" t="n">
-        <v>2181.12</v>
+        <v>4733.47</v>
       </c>
       <c r="K78" s="6" t="n">
-        <v>7826.48</v>
+        <v>16985.02</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>273564.62</v>
+        <v>419534.13</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
@@ -9704,16 +9704,16 @@
         <v>-1.049</v>
       </c>
       <c r="I79" s="5" t="n">
-        <v>264766.8</v>
+        <v>400484.85</v>
       </c>
       <c r="J79" s="5" t="n">
-        <v>2647.67</v>
+        <v>6299.63</v>
       </c>
       <c r="K79" s="7" t="n">
-        <v>-2778.42</v>
+        <v>-6610.72</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>305672.75</v>
+        <v>488610.52</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
@@ -9747,16 +9747,16 @@
         <v>-0.019</v>
       </c>
       <c r="I80" s="5" t="n">
-        <v>301367.54</v>
+        <v>479340.58</v>
       </c>
       <c r="J80" s="5" t="n">
-        <v>3013.68</v>
+        <v>7540.03</v>
       </c>
       <c r="K80" s="7" t="n">
-        <v>-56.86</v>
+        <v>-142.26</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>305615.89</v>
+        <v>488468.26</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
@@ -9790,16 +9790,16 @@
         <v>-0.025</v>
       </c>
       <c r="I81" s="5" t="n">
-        <v>298353.87</v>
+        <v>471800.55</v>
       </c>
       <c r="J81" s="5" t="n">
-        <v>2983.54</v>
+        <v>7421.42</v>
       </c>
       <c r="K81" s="7" t="n">
-        <v>-74.59</v>
+        <v>-185.54</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>305541.3</v>
+        <v>488282.72</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>

--- a/output/slowfix_portfolio_daily.xlsx
+++ b/output/slowfix_portfolio_daily.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>488,249.74</t>
+          <t>158,195.32</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+388.25%</t>
+          <t>+58.20%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>511,213  (+411.21%)</t>
+          <t>160,319  (+60.32%)</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10,198  (23.0 pts of return)</t>
+          <t>1,630  (2.1 pts of return)</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>19.18%</t>
+          <t>6.00%</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>20.2x</t>
+          <t>9.7x</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>+9.44R  (best +25.82R)</t>
+          <t>+9.51R  (best +25.82R)</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>26,586  (+14.85%)</t>
+          <t>4,279  (+3.77%)</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-3,086  (-1.65%)</t>
+          <t>-575  (-0.51%)</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>12.0% of live balance</t>
+          <t>3.1% of live balance</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.573% of liquid capital</t>
+          <t>0.396% of liquid capital (solved for a 6% max drawdown)</t>
         </is>
       </c>
     </row>
@@ -954,10 +954,10 @@
         <v>100000</v>
       </c>
       <c r="C2" s="5" t="n">
-        <v>1573</v>
+        <v>396</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>98427</v>
+        <v>99604</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX short (risk 1,573)</t>
+          <t>Gold_Futures_COMEX short (risk 396)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -979,13 +979,13 @@
         <v>46010</v>
       </c>
       <c r="B3" s="5" t="n">
-        <v>118079.99</v>
+        <v>104551.6</v>
       </c>
       <c r="C3" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>118079.99</v>
+        <v>104551.6</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -994,7 +994,7 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX bearish_reversal (+18,080)</t>
+          <t>Gold_Futures_COMEX bearish_reversal (+4,552)</t>
         </is>
       </c>
     </row>
@@ -1003,13 +1003,13 @@
         <v>46011</v>
       </c>
       <c r="B4" s="5" t="n">
-        <v>118079.99</v>
+        <v>104551.6</v>
       </c>
       <c r="C4" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>118079.99</v>
+        <v>104551.6</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -1023,13 +1023,13 @@
         <v>46021</v>
       </c>
       <c r="B5" s="5" t="n">
-        <v>118079.99</v>
+        <v>104551.6</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1857.4</v>
+        <v>414.02</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>116222.59</v>
+        <v>104137.58</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX short (risk 1,857)</t>
+          <t>Gold_Futures_COMEX short (risk 414)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -1051,13 +1051,13 @@
         <v>46023</v>
       </c>
       <c r="B6" s="5" t="n">
-        <v>118079.99</v>
+        <v>104551.6</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>1857.4</v>
+        <v>414.02</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>116222.59</v>
+        <v>104137.58</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -1075,13 +1075,13 @@
         <v>46024</v>
       </c>
       <c r="B7" s="5" t="n">
-        <v>118079.99</v>
+        <v>104551.6</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1857.4</v>
+        <v>414.02</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>116222.59</v>
+        <v>104137.58</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -1099,13 +1099,13 @@
         <v>46025</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>118079.99</v>
+        <v>104551.6</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>1857.4</v>
+        <v>414.02</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>116222.59</v>
+        <v>104137.58</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
@@ -1123,13 +1123,13 @@
         <v>46026</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>118079.99</v>
+        <v>104551.6</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1857.4</v>
+        <v>414.02</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>116222.59</v>
+        <v>104137.58</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -1147,13 +1147,13 @@
         <v>46027</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>116195.67</v>
+        <v>104131.58</v>
       </c>
       <c r="C10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>116195.67</v>
+        <v>104131.58</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -1162,7 +1162,7 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX stop (-1,884)</t>
+          <t>Gold_Futures_COMEX stop (-420)</t>
         </is>
       </c>
     </row>
@@ -1171,13 +1171,13 @@
         <v>46028</v>
       </c>
       <c r="B11" s="5" t="n">
-        <v>116195.67</v>
+        <v>104131.58</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>116195.67</v>
+        <v>104131.58</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -1191,13 +1191,13 @@
         <v>46029</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>116195.67</v>
+        <v>104131.58</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>3626.77</v>
+        <v>823.09</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>112568.9</v>
+        <v>103308.49</v>
       </c>
       <c r="E12" t="n">
         <v>2</v>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Coffee_NYCSCE_Futures short (risk 1,828); S_P_500_Index short (risk 1,799)</t>
+          <t>Coffee_NYCSCE_Futures short (risk 412); S_P_500_Index short (risk 411)</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -1219,13 +1219,13 @@
         <v>46030</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>114353.46</v>
+        <v>103715.96</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1799.01</v>
+        <v>410.73</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>112554.46</v>
+        <v>103305.23</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -1238,7 +1238,7 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Coffee_NYCSCE_Futures stop (-1,842)</t>
+          <t>Coffee_NYCSCE_Futures stop (-416)</t>
         </is>
       </c>
     </row>
@@ -1247,13 +1247,13 @@
         <v>46031</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>112545.75</v>
+        <v>103303.24</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>112545.75</v>
+        <v>103303.24</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -1262,7 +1262,7 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>S_P_500_Index stop (-1,808)</t>
+          <t>S_P_500_Index stop (-413)</t>
         </is>
       </c>
     </row>
@@ -1271,13 +1271,13 @@
         <v>46032</v>
       </c>
       <c r="B15" s="5" t="n">
-        <v>112545.75</v>
+        <v>103303.24</v>
       </c>
       <c r="C15" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>112545.75</v>
+        <v>103303.24</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -1291,13 +1291,13 @@
         <v>46033</v>
       </c>
       <c r="B16" s="5" t="n">
-        <v>112545.75</v>
+        <v>103303.24</v>
       </c>
       <c r="C16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>112545.75</v>
+        <v>103303.24</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -1311,13 +1311,13 @@
         <v>46034</v>
       </c>
       <c r="B17" s="5" t="n">
-        <v>112545.75</v>
+        <v>103303.24</v>
       </c>
       <c r="C17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>112545.75</v>
+        <v>103303.24</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -1331,13 +1331,13 @@
         <v>46035</v>
       </c>
       <c r="B18" s="5" t="n">
-        <v>112545.75</v>
+        <v>103303.24</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>1770.34</v>
+        <v>409.08</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>110775.41</v>
+        <v>102894.16</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cocoa_NYCSCE_Futures long (risk 1,770)</t>
+          <t>Cocoa_NYCSCE_Futures long (risk 409)</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -1359,13 +1359,13 @@
         <v>46036</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>110624.74</v>
+        <v>102859.35</v>
       </c>
       <c r="C19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>110624.74</v>
+        <v>102859.35</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -1374,7 +1374,7 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Cocoa_NYCSCE_Futures stop (-1,921)</t>
+          <t>Cocoa_NYCSCE_Futures stop (-444)</t>
         </is>
       </c>
     </row>
@@ -1383,13 +1383,13 @@
         <v>46037</v>
       </c>
       <c r="B20" s="5" t="n">
-        <v>110624.74</v>
+        <v>102859.35</v>
       </c>
       <c r="C20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>110624.74</v>
+        <v>102859.35</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -1403,13 +1403,13 @@
         <v>46038</v>
       </c>
       <c r="B21" s="5" t="n">
-        <v>110624.74</v>
+        <v>102859.35</v>
       </c>
       <c r="C21" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>110624.74</v>
+        <v>102859.35</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>46039</v>
       </c>
       <c r="B22" s="5" t="n">
-        <v>110624.74</v>
+        <v>102859.35</v>
       </c>
       <c r="C22" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>110624.74</v>
+        <v>102859.35</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -1443,13 +1443,13 @@
         <v>46040</v>
       </c>
       <c r="B23" s="5" t="n">
-        <v>110624.74</v>
+        <v>102859.35</v>
       </c>
       <c r="C23" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>110624.74</v>
+        <v>102859.35</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -1463,13 +1463,13 @@
         <v>46041</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>110624.74</v>
+        <v>102859.35</v>
       </c>
       <c r="C24" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>110624.74</v>
+        <v>102859.35</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -1483,13 +1483,13 @@
         <v>46042</v>
       </c>
       <c r="B25" s="5" t="n">
-        <v>110624.74</v>
+        <v>102859.35</v>
       </c>
       <c r="C25" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>110624.74</v>
+        <v>102859.35</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -1503,13 +1503,13 @@
         <v>46043</v>
       </c>
       <c r="B26" s="5" t="n">
-        <v>110624.74</v>
+        <v>102859.35</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>1740.13</v>
+        <v>407.32</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>108884.61</v>
+        <v>102452.03</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Coffee_NYCSCE_Futures long (risk 1,740)</t>
+          <t>Coffee_NYCSCE_Futures long (risk 407)</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
@@ -1531,13 +1531,13 @@
         <v>46044</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>110624.74</v>
+        <v>102859.35</v>
       </c>
       <c r="C27" s="5" t="n">
-        <v>1740.13</v>
+        <v>407.32</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>108884.61</v>
+        <v>102452.03</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -1555,13 +1555,13 @@
         <v>46045</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>110624.74</v>
+        <v>102859.35</v>
       </c>
       <c r="C28" s="5" t="n">
-        <v>1740.13</v>
+        <v>407.32</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>108884.61</v>
+        <v>102452.03</v>
       </c>
       <c r="E28" t="n">
         <v>1</v>
@@ -1579,13 +1579,13 @@
         <v>46046</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>110624.74</v>
+        <v>102859.35</v>
       </c>
       <c r="C29" s="5" t="n">
-        <v>1740.13</v>
+        <v>407.32</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>108884.61</v>
+        <v>102452.03</v>
       </c>
       <c r="E29" t="n">
         <v>1</v>
@@ -1603,13 +1603,13 @@
         <v>46047</v>
       </c>
       <c r="B30" s="5" t="n">
-        <v>110624.74</v>
+        <v>102859.35</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>1740.13</v>
+        <v>407.32</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>108884.61</v>
+        <v>102452.03</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
@@ -1627,13 +1627,13 @@
         <v>46048</v>
       </c>
       <c r="B31" s="5" t="n">
-        <v>110624.74</v>
+        <v>102859.35</v>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1740.13</v>
+        <v>407.32</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>108884.61</v>
+        <v>102452.03</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
@@ -1651,13 +1651,13 @@
         <v>46049</v>
       </c>
       <c r="B32" s="5" t="n">
-        <v>118131.92</v>
+        <v>104616.6</v>
       </c>
       <c r="C32" s="5" t="n">
-        <v>1712.75</v>
+        <v>405.71</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>116419.17</v>
+        <v>104210.89</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
@@ -1669,12 +1669,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>S_P_500_Index short (risk 1,713)</t>
+          <t>S_P_500_Index short (risk 406)</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Coffee_NYCSCE_Futures bullish_reversal (+7,507)</t>
+          <t>Coffee_NYCSCE_Futures bullish_reversal (+1,757)</t>
         </is>
       </c>
     </row>
@@ -1683,13 +1683,13 @@
         <v>46050</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>116408.52</v>
+        <v>103377.4</v>
       </c>
       <c r="C33" s="5" t="n">
-        <v>1831.27</v>
+        <v>412.68</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>114577.24</v>
+        <v>102964.72</v>
       </c>
       <c r="E33" t="n">
         <v>1</v>
@@ -1701,12 +1701,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Teucrium_Wheat_Fund short (risk 1,831)</t>
+          <t>Teucrium_Wheat_Fund short (risk 413)</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>S_P_500_Index stop (-1,723)</t>
+          <t>S_P_500_Index stop (-1,239)</t>
         </is>
       </c>
     </row>
@@ -1715,13 +1715,13 @@
         <v>46051</v>
       </c>
       <c r="B34" s="5" t="n">
-        <v>114170.29</v>
+        <v>102850.07</v>
       </c>
       <c r="C34" s="5" t="n">
-        <v>5322.3</v>
+        <v>1218.38</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>108848</v>
+        <v>101631.69</v>
       </c>
       <c r="E34" t="n">
         <v>3</v>
@@ -1733,12 +1733,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ethereum_Per_USD_Binance long (risk 1,802); Live_Cattle_Futures_CME short (risk 1,774); S_P_500_Index short (risk 1,746)</t>
+          <t>Ethereum_Per_USD_Binance long (risk 408); Live_Cattle_Futures_CME short (risk 406); S_P_500_Index short (risk 405)</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Teucrium_Wheat_Fund stop (-2,238)</t>
+          <t>Teucrium_Wheat_Fund stop (-527)</t>
         </is>
       </c>
     </row>
@@ -1747,13 +1747,13 @@
         <v>46052</v>
       </c>
       <c r="B35" s="5" t="n">
-        <v>110363.84</v>
+        <v>101983.84</v>
       </c>
       <c r="C35" s="5" t="n">
-        <v>3458.22</v>
+        <v>806.98</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>106905.61</v>
+        <v>101176.86</v>
       </c>
       <c r="E35" t="n">
         <v>2</v>
@@ -1765,12 +1765,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cocoa_NYCSCE_Futures long (risk 1,712)</t>
+          <t>Cocoa_NYCSCE_Futures long (risk 402)</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Ethereum_Per_USD_Binance stop (-1,927); Live_Cattle_Futures_CME stop (-1,880)</t>
+          <t>Ethereum_Per_USD_Binance stop (-436); Live_Cattle_Futures_CME stop (-430)</t>
         </is>
       </c>
     </row>
@@ -1779,13 +1779,13 @@
         <v>46053</v>
       </c>
       <c r="B36" s="5" t="n">
-        <v>110363.84</v>
+        <v>101983.84</v>
       </c>
       <c r="C36" s="5" t="n">
-        <v>3458.22</v>
+        <v>806.98</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>106905.61</v>
+        <v>101176.86</v>
       </c>
       <c r="E36" t="n">
         <v>2</v>
@@ -1803,13 +1803,13 @@
         <v>46054</v>
       </c>
       <c r="B37" s="5" t="n">
-        <v>110363.84</v>
+        <v>101983.84</v>
       </c>
       <c r="C37" s="5" t="n">
-        <v>3458.22</v>
+        <v>806.98</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>106905.61</v>
+        <v>101176.86</v>
       </c>
       <c r="E37" t="n">
         <v>2</v>
@@ -1827,13 +1827,13 @@
         <v>46055</v>
       </c>
       <c r="B38" s="5" t="n">
-        <v>110363.84</v>
+        <v>101983.84</v>
       </c>
       <c r="C38" s="5" t="n">
-        <v>5139.85</v>
+        <v>1207.64</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>105223.99</v>
+        <v>100776.2</v>
       </c>
       <c r="E38" t="n">
         <v>3</v>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance long (risk 1,682)</t>
+          <t>Bitcoin_Per_USD_Binance long (risk 401)</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
@@ -1855,13 +1855,13 @@
         <v>46056</v>
       </c>
       <c r="B39" s="5" t="n">
-        <v>106925.92</v>
+        <v>101176.26</v>
       </c>
       <c r="C39" s="5" t="n">
-        <v>3367.35</v>
+        <v>801.54</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>103558.57</v>
+        <v>100374.73</v>
       </c>
       <c r="E39" t="n">
         <v>2</v>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>EURO_STOXX_50_Index short (risk 1,655)</t>
+          <t>EURO_STOXX_50_Index short (risk 399)</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance stop (-1,685); S_P_500_Index stop (-1,753)</t>
+          <t>Bitcoin_Per_USD_Binance stop (-402); S_P_500_Index stop (-406)</t>
         </is>
       </c>
     </row>
@@ -1887,13 +1887,13 @@
         <v>46057</v>
       </c>
       <c r="B40" s="5" t="n">
-        <v>106925.92</v>
+        <v>101176.26</v>
       </c>
       <c r="C40" s="5" t="n">
-        <v>3367.35</v>
+        <v>801.54</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>103558.57</v>
+        <v>100374.73</v>
       </c>
       <c r="E40" t="n">
         <v>2</v>
@@ -1911,13 +1911,13 @@
         <v>46058</v>
       </c>
       <c r="B41" s="5" t="n">
-        <v>106925.92</v>
+        <v>101176.26</v>
       </c>
       <c r="C41" s="5" t="n">
-        <v>4996.33</v>
+        <v>1199.02</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>101929.6</v>
+        <v>99977.24000000001</v>
       </c>
       <c r="E41" t="n">
         <v>3</v>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures long (risk 1,629)</t>
+          <t>NY_Copper_Futures long (risk 397)</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
@@ -1939,13 +1939,13 @@
         <v>46059</v>
       </c>
       <c r="B42" s="5" t="n">
-        <v>105289.42</v>
+        <v>100776.94</v>
       </c>
       <c r="C42" s="5" t="n">
-        <v>4970.7</v>
+        <v>1197.45</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>100318.71</v>
+        <v>99579.5</v>
       </c>
       <c r="E42" t="n">
         <v>3</v>
@@ -1957,12 +1957,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance long (risk 1,603)</t>
+          <t>Bitcoin_Per_USD_Binance long (risk 396)</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures stop (-1,637)</t>
+          <t>NY_Copper_Futures stop (-399)</t>
         </is>
       </c>
     </row>
@@ -1971,13 +1971,13 @@
         <v>46060</v>
       </c>
       <c r="B43" s="5" t="n">
-        <v>105289.42</v>
+        <v>100776.94</v>
       </c>
       <c r="C43" s="5" t="n">
-        <v>4970.7</v>
+        <v>1197.45</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>100318.71</v>
+        <v>99579.5</v>
       </c>
       <c r="E43" t="n">
         <v>3</v>
@@ -1995,13 +1995,13 @@
         <v>46061</v>
       </c>
       <c r="B44" s="5" t="n">
-        <v>105289.42</v>
+        <v>100776.94</v>
       </c>
       <c r="C44" s="5" t="n">
-        <v>4970.7</v>
+        <v>1197.45</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>100318.71</v>
+        <v>99579.5</v>
       </c>
       <c r="E44" t="n">
         <v>3</v>
@@ -2019,13 +2019,13 @@
         <v>46062</v>
       </c>
       <c r="B45" s="5" t="n">
-        <v>105289.42</v>
+        <v>100776.94</v>
       </c>
       <c r="C45" s="5" t="n">
-        <v>4970.7</v>
+        <v>1197.45</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>100318.71</v>
+        <v>99579.5</v>
       </c>
       <c r="E45" t="n">
         <v>3</v>
@@ -2043,13 +2043,13 @@
         <v>46063</v>
       </c>
       <c r="B46" s="5" t="n">
-        <v>101874.8</v>
+        <v>99964.28</v>
       </c>
       <c r="C46" s="5" t="n">
-        <v>3181.37</v>
+        <v>790.24</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>98693.42999999999</v>
+        <v>99174.03999999999</v>
       </c>
       <c r="E46" t="n">
         <v>2</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>S_P_500_Index short (risk 1,578)</t>
+          <t>S_P_500_Index short (risk 394)</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Cocoa_NYCSCE_Futures stop (-1,757); EURO_STOXX_50_Index stop (-1,657)</t>
+          <t>Cocoa_NYCSCE_Futures stop (-413); EURO_STOXX_50_Index stop (-400)</t>
         </is>
       </c>
     </row>
@@ -2075,13 +2075,13 @@
         <v>46064</v>
       </c>
       <c r="B47" s="5" t="n">
-        <v>100282.57</v>
+        <v>99566.39</v>
       </c>
       <c r="C47" s="5" t="n">
-        <v>3155.8</v>
+        <v>788.64</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>97126.77</v>
+        <v>98777.75999999999</v>
       </c>
       <c r="E47" t="n">
         <v>2</v>
@@ -2093,12 +2093,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT short (risk 1,552)</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT short (risk 393)</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>S_P_500_Index stop (-1,592)</t>
+          <t>S_P_500_Index stop (-398)</t>
         </is>
       </c>
     </row>
@@ -2107,13 +2107,13 @@
         <v>46065</v>
       </c>
       <c r="B48" s="5" t="n">
-        <v>98515.99000000001</v>
+        <v>99119.5</v>
       </c>
       <c r="C48" s="5" t="n">
-        <v>3131.16</v>
+        <v>787.0700000000001</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>95384.83</v>
+        <v>98332.42999999999</v>
       </c>
       <c r="E48" t="n">
         <v>2</v>
@@ -2125,12 +2125,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>EURO_STOXX_50_Index short (risk 1,528)</t>
+          <t>EURO_STOXX_50_Index short (risk 391)</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT stop (-1,767)</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT stop (-447)</t>
         </is>
       </c>
     </row>
@@ -2139,13 +2139,13 @@
         <v>46066</v>
       </c>
       <c r="B49" s="5" t="n">
-        <v>98515.99000000001</v>
+        <v>99119.5</v>
       </c>
       <c r="C49" s="5" t="n">
-        <v>4631.56</v>
+        <v>1176.47</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>93884.42999999999</v>
+        <v>97943.03</v>
       </c>
       <c r="E49" t="n">
         <v>3</v>
@@ -2157,7 +2157,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures long (risk 1,500)</t>
+          <t>NY_Copper_Futures long (risk 389)</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
@@ -2167,13 +2167,13 @@
         <v>46067</v>
       </c>
       <c r="B50" s="5" t="n">
-        <v>98515.99000000001</v>
+        <v>99119.5</v>
       </c>
       <c r="C50" s="5" t="n">
-        <v>4631.56</v>
+        <v>1176.47</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>93884.42999999999</v>
+        <v>97943.03</v>
       </c>
       <c r="E50" t="n">
         <v>3</v>
@@ -2191,13 +2191,13 @@
         <v>46068</v>
       </c>
       <c r="B51" s="5" t="n">
-        <v>98515.99000000001</v>
+        <v>99119.5</v>
       </c>
       <c r="C51" s="5" t="n">
-        <v>4631.56</v>
+        <v>1176.47</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>93884.42999999999</v>
+        <v>97943.03</v>
       </c>
       <c r="E51" t="n">
         <v>3</v>
@@ -2215,13 +2215,13 @@
         <v>46069</v>
       </c>
       <c r="B52" s="5" t="n">
-        <v>98515.99000000001</v>
+        <v>99119.5</v>
       </c>
       <c r="C52" s="5" t="n">
-        <v>4631.56</v>
+        <v>1176.47</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>93884.42999999999</v>
+        <v>97943.03</v>
       </c>
       <c r="E52" t="n">
         <v>3</v>
@@ -2239,13 +2239,13 @@
         <v>46070</v>
       </c>
       <c r="B53" s="5" t="n">
-        <v>97009.2</v>
+        <v>98728.44</v>
       </c>
       <c r="C53" s="5" t="n">
-        <v>3131.16</v>
+        <v>787.0700000000001</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>93878.03999999999</v>
+        <v>97941.37</v>
       </c>
       <c r="E53" t="n">
         <v>2</v>
@@ -2258,7 +2258,7 @@
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures stop (-1,507)</t>
+          <t>NY_Copper_Futures stop (-391)</t>
         </is>
       </c>
     </row>
@@ -2267,13 +2267,13 @@
         <v>46071</v>
       </c>
       <c r="B54" s="5" t="n">
-        <v>95479.82000000001</v>
+        <v>98336.88</v>
       </c>
       <c r="C54" s="5" t="n">
-        <v>1603.35</v>
+        <v>395.91</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>93876.47</v>
+        <v>97940.97</v>
       </c>
       <c r="E54" t="n">
         <v>1</v>
@@ -2286,7 +2286,7 @@
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>EURO_STOXX_50_Index stop (-1,529)</t>
+          <t>EURO_STOXX_50_Index stop (-392)</t>
         </is>
       </c>
     </row>
@@ -2295,13 +2295,13 @@
         <v>46072</v>
       </c>
       <c r="B55" s="5" t="n">
-        <v>95479.82000000001</v>
+        <v>98336.88</v>
       </c>
       <c r="C55" s="5" t="n">
-        <v>1603.35</v>
+        <v>395.91</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>93876.47</v>
+        <v>97940.97</v>
       </c>
       <c r="E55" t="n">
         <v>1</v>
@@ -2319,13 +2319,13 @@
         <v>46073</v>
       </c>
       <c r="B56" s="5" t="n">
-        <v>95479.82000000001</v>
+        <v>98336.88</v>
       </c>
       <c r="C56" s="5" t="n">
-        <v>1603.35</v>
+        <v>395.91</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>93876.47</v>
+        <v>97940.97</v>
       </c>
       <c r="E56" t="n">
         <v>1</v>
@@ -2343,13 +2343,13 @@
         <v>46074</v>
       </c>
       <c r="B57" s="5" t="n">
-        <v>95479.82000000001</v>
+        <v>98336.88</v>
       </c>
       <c r="C57" s="5" t="n">
-        <v>1603.35</v>
+        <v>395.91</v>
       </c>
       <c r="D57" s="5" t="n">
-        <v>93876.47</v>
+        <v>97940.97</v>
       </c>
       <c r="E57" t="n">
         <v>1</v>
@@ -2367,13 +2367,13 @@
         <v>46075</v>
       </c>
       <c r="B58" s="5" t="n">
-        <v>95479.82000000001</v>
+        <v>98336.88</v>
       </c>
       <c r="C58" s="5" t="n">
-        <v>1603.35</v>
+        <v>395.91</v>
       </c>
       <c r="D58" s="5" t="n">
-        <v>93876.47</v>
+        <v>97940.97</v>
       </c>
       <c r="E58" t="n">
         <v>1</v>
@@ -2391,13 +2391,13 @@
         <v>46076</v>
       </c>
       <c r="B59" s="5" t="n">
-        <v>95479.82000000001</v>
+        <v>98336.88</v>
       </c>
       <c r="C59" s="5" t="n">
-        <v>3080.03</v>
+        <v>783.76</v>
       </c>
       <c r="D59" s="5" t="n">
-        <v>92399.78999999999</v>
+        <v>97553.12</v>
       </c>
       <c r="E59" t="n">
         <v>2</v>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT short (risk 1,477)</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT short (risk 388)</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
@@ -2419,13 +2419,13 @@
         <v>46077</v>
       </c>
       <c r="B60" s="5" t="n">
-        <v>95479.82000000001</v>
+        <v>98336.88</v>
       </c>
       <c r="C60" s="5" t="n">
-        <v>5964.06</v>
+        <v>1554.85</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>89515.75999999999</v>
+        <v>96782.03</v>
       </c>
       <c r="E60" t="n">
         <v>4</v>
@@ -2437,7 +2437,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cocoa_NYCSCE_Futures long (risk 1,453); Ethereum_Per_USD_Binance long (risk 1,431)</t>
+          <t>Cocoa_NYCSCE_Futures long (risk 386); Ethereum_Per_USD_Binance long (risk 385)</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
@@ -2447,13 +2447,13 @@
         <v>46078</v>
       </c>
       <c r="B61" s="5" t="n">
-        <v>110689.15</v>
+        <v>102427.69</v>
       </c>
       <c r="C61" s="5" t="n">
-        <v>4533.48</v>
+        <v>1170.07</v>
       </c>
       <c r="D61" s="5" t="n">
-        <v>106155.67</v>
+        <v>101257.62</v>
       </c>
       <c r="E61" t="n">
         <v>3</v>
@@ -2466,7 +2466,7 @@
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Ethereum_Per_USD_Binance bullish_reversal (+15,209)</t>
+          <t>Ethereum_Per_USD_Binance bullish_reversal (+4,091)</t>
         </is>
       </c>
     </row>
@@ -2475,13 +2475,13 @@
         <v>46079</v>
       </c>
       <c r="B62" s="5" t="n">
-        <v>108790.57</v>
+        <v>101929.03</v>
       </c>
       <c r="C62" s="5" t="n">
-        <v>3056.8</v>
+        <v>782.22</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>105733.76</v>
+        <v>101146.81</v>
       </c>
       <c r="E62" t="n">
         <v>2</v>
@@ -2494,7 +2494,7 @@
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT stop (-1,899)</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT stop (-499)</t>
         </is>
       </c>
     </row>
@@ -2503,13 +2503,13 @@
         <v>46080</v>
       </c>
       <c r="B63" s="5" t="n">
-        <v>107188.04</v>
+        <v>101503.1</v>
       </c>
       <c r="C63" s="5" t="n">
-        <v>1603.35</v>
+        <v>395.91</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>105584.69</v>
+        <v>101107.19</v>
       </c>
       <c r="E63" t="n">
         <v>1</v>
@@ -2522,7 +2522,7 @@
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Cocoa_NYCSCE_Futures stop (-1,603)</t>
+          <t>Cocoa_NYCSCE_Futures stop (-426)</t>
         </is>
       </c>
     </row>
@@ -2531,13 +2531,13 @@
         <v>46081</v>
       </c>
       <c r="B64" s="5" t="n">
-        <v>107188.04</v>
+        <v>101503.1</v>
       </c>
       <c r="C64" s="5" t="n">
-        <v>1603.35</v>
+        <v>395.91</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>105584.69</v>
+        <v>101107.19</v>
       </c>
       <c r="E64" t="n">
         <v>1</v>
@@ -2555,13 +2555,13 @@
         <v>46082</v>
       </c>
       <c r="B65" s="5" t="n">
-        <v>107188.04</v>
+        <v>101503.1</v>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1603.35</v>
+        <v>395.91</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>105584.69</v>
+        <v>101107.19</v>
       </c>
       <c r="E65" t="n">
         <v>1</v>
@@ -2579,13 +2579,13 @@
         <v>46083</v>
       </c>
       <c r="B66" s="5" t="n">
-        <v>110991.87</v>
+        <v>102442.36</v>
       </c>
       <c r="C66" s="5" t="n">
-        <v>1660.85</v>
+        <v>400.38</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>109331.02</v>
+        <v>102041.98</v>
       </c>
       <c r="E66" t="n">
         <v>1</v>
@@ -2597,12 +2597,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX short (risk 1,661)</t>
+          <t>Gold_Futures_COMEX short (risk 400)</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance bullish_reversal (+3,804)</t>
+          <t>Bitcoin_Per_USD_Binance bullish_reversal (+939)</t>
         </is>
       </c>
     </row>
@@ -2611,13 +2611,13 @@
         <v>46084</v>
       </c>
       <c r="B67" s="5" t="n">
-        <v>110991.87</v>
+        <v>102442.36</v>
       </c>
       <c r="C67" s="5" t="n">
-        <v>1660.85</v>
+        <v>400.38</v>
       </c>
       <c r="D67" s="5" t="n">
-        <v>109331.02</v>
+        <v>102041.98</v>
       </c>
       <c r="E67" t="n">
         <v>1</v>
@@ -2635,13 +2635,13 @@
         <v>46085</v>
       </c>
       <c r="B68" s="5" t="n">
-        <v>110991.87</v>
+        <v>102442.36</v>
       </c>
       <c r="C68" s="5" t="n">
-        <v>3380.62</v>
+        <v>804.47</v>
       </c>
       <c r="D68" s="5" t="n">
-        <v>107611.24</v>
+        <v>101637.89</v>
       </c>
       <c r="E68" t="n">
         <v>2</v>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate short (risk 1,720)</t>
+          <t>USD_EUR_Cross_Rate short (risk 404)</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
@@ -2663,13 +2663,13 @@
         <v>46086</v>
       </c>
       <c r="B69" s="5" t="n">
-        <v>108973</v>
+        <v>101968</v>
       </c>
       <c r="C69" s="5" t="n">
-        <v>3353.57</v>
+        <v>802.87</v>
       </c>
       <c r="D69" s="5" t="n">
-        <v>105619.43</v>
+        <v>101165.13</v>
       </c>
       <c r="E69" t="n">
         <v>2</v>
@@ -2681,12 +2681,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>S_P_500_Index long (risk 1,693)</t>
+          <t>S_P_500_Index long (risk 402)</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate stop (-2,019)</t>
+          <t>USD_EUR_Cross_Rate stop (-474)</t>
         </is>
       </c>
     </row>
@@ -2695,13 +2695,13 @@
         <v>46087</v>
       </c>
       <c r="B70" s="5" t="n">
-        <v>107277.41</v>
+        <v>101535.21</v>
       </c>
       <c r="C70" s="5" t="n">
-        <v>3322.24</v>
+        <v>801</v>
       </c>
       <c r="D70" s="5" t="n">
-        <v>103955.17</v>
+        <v>100734.21</v>
       </c>
       <c r="E70" t="n">
         <v>2</v>
@@ -2713,12 +2713,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate short (risk 1,661)</t>
+          <t>USD_EUR_Cross_Rate short (risk 401)</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>S_P_500_Index stop (-1,696)</t>
+          <t>S_P_500_Index stop (-433)</t>
         </is>
       </c>
     </row>
@@ -2727,13 +2727,13 @@
         <v>46088</v>
       </c>
       <c r="B71" s="5" t="n">
-        <v>107277.41</v>
+        <v>101535.21</v>
       </c>
       <c r="C71" s="5" t="n">
-        <v>3322.24</v>
+        <v>801</v>
       </c>
       <c r="D71" s="5" t="n">
-        <v>103955.17</v>
+        <v>100734.21</v>
       </c>
       <c r="E71" t="n">
         <v>2</v>
@@ -2751,13 +2751,13 @@
         <v>46089</v>
       </c>
       <c r="B72" s="5" t="n">
-        <v>107277.41</v>
+        <v>101535.21</v>
       </c>
       <c r="C72" s="5" t="n">
-        <v>3322.24</v>
+        <v>801</v>
       </c>
       <c r="D72" s="5" t="n">
-        <v>103955.17</v>
+        <v>100734.21</v>
       </c>
       <c r="E72" t="n">
         <v>2</v>
@@ -2775,13 +2775,13 @@
         <v>46090</v>
       </c>
       <c r="B73" s="5" t="n">
-        <v>112512.07</v>
+        <v>102797.04</v>
       </c>
       <c r="C73" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D73" s="5" t="n">
-        <v>112512.07</v>
+        <v>102797.04</v>
       </c>
       <c r="E73" t="n">
         <v>0</v>
@@ -2790,7 +2790,7 @@
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX bearish_reversal (+7,047); USD_EUR_Cross_Rate stop (-1,812)</t>
+          <t>Gold_Futures_COMEX bearish_reversal (+1,699); USD_EUR_Cross_Rate stop (-437)</t>
         </is>
       </c>
     </row>
@@ -2799,13 +2799,13 @@
         <v>46091</v>
       </c>
       <c r="B74" s="5" t="n">
-        <v>112512.07</v>
+        <v>102797.04</v>
       </c>
       <c r="C74" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>112512.07</v>
+        <v>102797.04</v>
       </c>
       <c r="E74" t="n">
         <v>0</v>
@@ -2819,13 +2819,13 @@
         <v>46092</v>
       </c>
       <c r="B75" s="5" t="n">
-        <v>112512.07</v>
+        <v>102797.04</v>
       </c>
       <c r="C75" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>112512.07</v>
+        <v>102797.04</v>
       </c>
       <c r="E75" t="n">
         <v>0</v>
@@ -2839,13 +2839,13 @@
         <v>46093</v>
       </c>
       <c r="B76" s="5" t="n">
-        <v>112512.07</v>
+        <v>102797.04</v>
       </c>
       <c r="C76" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>112512.07</v>
+        <v>102797.04</v>
       </c>
       <c r="E76" t="n">
         <v>0</v>
@@ -2859,13 +2859,13 @@
         <v>46094</v>
       </c>
       <c r="B77" s="5" t="n">
-        <v>112512.07</v>
+        <v>102797.04</v>
       </c>
       <c r="C77" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D77" s="5" t="n">
-        <v>112512.07</v>
+        <v>102797.04</v>
       </c>
       <c r="E77" t="n">
         <v>0</v>
@@ -2879,13 +2879,13 @@
         <v>46095</v>
       </c>
       <c r="B78" s="5" t="n">
-        <v>112512.07</v>
+        <v>102797.04</v>
       </c>
       <c r="C78" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D78" s="5" t="n">
-        <v>112512.07</v>
+        <v>102797.04</v>
       </c>
       <c r="E78" t="n">
         <v>0</v>
@@ -2899,13 +2899,13 @@
         <v>46096</v>
       </c>
       <c r="B79" s="5" t="n">
-        <v>112512.07</v>
+        <v>102797.04</v>
       </c>
       <c r="C79" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D79" s="5" t="n">
-        <v>112512.07</v>
+        <v>102797.04</v>
       </c>
       <c r="E79" t="n">
         <v>0</v>
@@ -2919,13 +2919,13 @@
         <v>46097</v>
       </c>
       <c r="B80" s="5" t="n">
-        <v>112512.07</v>
+        <v>102797.04</v>
       </c>
       <c r="C80" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D80" s="5" t="n">
-        <v>112512.07</v>
+        <v>102797.04</v>
       </c>
       <c r="E80" t="n">
         <v>0</v>
@@ -2939,13 +2939,13 @@
         <v>46098</v>
       </c>
       <c r="B81" s="5" t="n">
-        <v>112512.07</v>
+        <v>102797.04</v>
       </c>
       <c r="C81" s="5" t="n">
-        <v>1769.81</v>
+        <v>407.08</v>
       </c>
       <c r="D81" s="5" t="n">
-        <v>110742.26</v>
+        <v>102389.96</v>
       </c>
       <c r="E81" t="n">
         <v>1</v>
@@ -2957,7 +2957,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance short (risk 1,770)</t>
+          <t>Bitcoin_Per_USD_Binance short (risk 407)</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
@@ -2967,13 +2967,13 @@
         <v>46099</v>
       </c>
       <c r="B82" s="5" t="n">
-        <v>112512.07</v>
+        <v>102797.04</v>
       </c>
       <c r="C82" s="5" t="n">
-        <v>1769.81</v>
+        <v>407.08</v>
       </c>
       <c r="D82" s="5" t="n">
-        <v>110742.26</v>
+        <v>102389.96</v>
       </c>
       <c r="E82" t="n">
         <v>1</v>
@@ -2991,13 +2991,13 @@
         <v>46100</v>
       </c>
       <c r="B83" s="5" t="n">
-        <v>112512.07</v>
+        <v>102797.04</v>
       </c>
       <c r="C83" s="5" t="n">
-        <v>1769.81</v>
+        <v>407.08</v>
       </c>
       <c r="D83" s="5" t="n">
-        <v>110742.26</v>
+        <v>102389.96</v>
       </c>
       <c r="E83" t="n">
         <v>1</v>
@@ -3015,13 +3015,13 @@
         <v>46101</v>
       </c>
       <c r="B84" s="5" t="n">
-        <v>112512.07</v>
+        <v>102797.04</v>
       </c>
       <c r="C84" s="5" t="n">
-        <v>3511.79</v>
+        <v>812.54</v>
       </c>
       <c r="D84" s="5" t="n">
-        <v>109000.28</v>
+        <v>101984.49</v>
       </c>
       <c r="E84" t="n">
         <v>2</v>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP short (risk 1,742)</t>
+          <t>United_States_Oil_Fund_LP short (risk 405)</t>
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
@@ -3043,13 +3043,13 @@
         <v>46102</v>
       </c>
       <c r="B85" s="5" t="n">
-        <v>112512.07</v>
+        <v>102797.04</v>
       </c>
       <c r="C85" s="5" t="n">
-        <v>3511.79</v>
+        <v>812.54</v>
       </c>
       <c r="D85" s="5" t="n">
-        <v>109000.28</v>
+        <v>101984.49</v>
       </c>
       <c r="E85" t="n">
         <v>2</v>
@@ -3067,13 +3067,13 @@
         <v>46103</v>
       </c>
       <c r="B86" s="5" t="n">
-        <v>131283.41</v>
+        <v>107114.64</v>
       </c>
       <c r="C86" s="5" t="n">
-        <v>1741.98</v>
+        <v>405.46</v>
       </c>
       <c r="D86" s="5" t="n">
-        <v>129541.43</v>
+        <v>106709.18</v>
       </c>
       <c r="E86" t="n">
         <v>1</v>
@@ -3086,7 +3086,7 @@
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance bearish_reversal (+18,771)</t>
+          <t>Bitcoin_Per_USD_Binance bearish_reversal (+4,318)</t>
         </is>
       </c>
     </row>
@@ -3095,13 +3095,13 @@
         <v>46104</v>
       </c>
       <c r="B87" s="5" t="n">
-        <v>131283.41</v>
+        <v>107114.64</v>
       </c>
       <c r="C87" s="5" t="n">
-        <v>3779.66</v>
+        <v>828.03</v>
       </c>
       <c r="D87" s="5" t="n">
-        <v>127503.75</v>
+        <v>106286.61</v>
       </c>
       <c r="E87" t="n">
         <v>2</v>
@@ -3113,7 +3113,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures long (risk 2,038)</t>
+          <t>NY_Copper_Futures long (risk 423)</t>
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
@@ -3123,13 +3123,13 @@
         <v>46105</v>
       </c>
       <c r="B88" s="5" t="n">
-        <v>131283.41</v>
+        <v>107114.64</v>
       </c>
       <c r="C88" s="5" t="n">
-        <v>5785.3</v>
+        <v>1248.93</v>
       </c>
       <c r="D88" s="5" t="n">
-        <v>125498.11</v>
+        <v>105865.71</v>
       </c>
       <c r="E88" t="n">
         <v>3</v>
@@ -3141,7 +3141,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX long (risk 2,006)</t>
+          <t>Gold_Futures_COMEX long (risk 421)</t>
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
@@ -3151,13 +3151,13 @@
         <v>46106</v>
       </c>
       <c r="B89" s="5" t="n">
-        <v>131283.41</v>
+        <v>107114.64</v>
       </c>
       <c r="C89" s="5" t="n">
-        <v>5785.3</v>
+        <v>1248.93</v>
       </c>
       <c r="D89" s="5" t="n">
-        <v>125498.11</v>
+        <v>105865.71</v>
       </c>
       <c r="E89" t="n">
         <v>3</v>
@@ -3175,13 +3175,13 @@
         <v>46107</v>
       </c>
       <c r="B90" s="5" t="n">
-        <v>131283.41</v>
+        <v>107114.64</v>
       </c>
       <c r="C90" s="5" t="n">
-        <v>5785.3</v>
+        <v>1248.93</v>
       </c>
       <c r="D90" s="5" t="n">
-        <v>125498.11</v>
+        <v>105865.71</v>
       </c>
       <c r="E90" t="n">
         <v>3</v>
@@ -3199,13 +3199,13 @@
         <v>46108</v>
       </c>
       <c r="B91" s="5" t="n">
-        <v>129488.24</v>
+        <v>106696.8</v>
       </c>
       <c r="C91" s="5" t="n">
-        <v>4043.32</v>
+        <v>843.46</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>125444.92</v>
+        <v>105853.33</v>
       </c>
       <c r="E91" t="n">
         <v>2</v>
@@ -3218,7 +3218,7 @@
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP stop (-1,795)</t>
+          <t>United_States_Oil_Fund_LP stop (-418)</t>
         </is>
       </c>
     </row>
@@ -3227,13 +3227,13 @@
         <v>46109</v>
       </c>
       <c r="B92" s="5" t="n">
-        <v>129488.24</v>
+        <v>106696.8</v>
       </c>
       <c r="C92" s="5" t="n">
-        <v>4043.32</v>
+        <v>843.46</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>125444.92</v>
+        <v>105853.33</v>
       </c>
       <c r="E92" t="n">
         <v>2</v>
@@ -3251,13 +3251,13 @@
         <v>46110</v>
       </c>
       <c r="B93" s="5" t="n">
-        <v>129488.24</v>
+        <v>106696.8</v>
       </c>
       <c r="C93" s="5" t="n">
-        <v>4043.32</v>
+        <v>843.46</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>125444.92</v>
+        <v>105853.33</v>
       </c>
       <c r="E93" t="n">
         <v>2</v>
@@ -3275,13 +3275,13 @@
         <v>46111</v>
       </c>
       <c r="B94" s="5" t="n">
-        <v>129488.24</v>
+        <v>106696.8</v>
       </c>
       <c r="C94" s="5" t="n">
-        <v>4043.32</v>
+        <v>843.46</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>125444.92</v>
+        <v>105853.33</v>
       </c>
       <c r="E94" t="n">
         <v>2</v>
@@ -3299,13 +3299,13 @@
         <v>46112</v>
       </c>
       <c r="B95" s="5" t="n">
-        <v>129488.24</v>
+        <v>106696.8</v>
       </c>
       <c r="C95" s="5" t="n">
-        <v>6016.57</v>
+        <v>1262.64</v>
       </c>
       <c r="D95" s="5" t="n">
-        <v>123471.67</v>
+        <v>105434.15</v>
       </c>
       <c r="E95" t="n">
         <v>3</v>
@@ -3317,7 +3317,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP short (risk 1,973)</t>
+          <t>United_States_Oil_Fund_LP short (risk 419)</t>
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
@@ -3327,13 +3327,13 @@
         <v>46113</v>
       </c>
       <c r="B96" s="5" t="n">
-        <v>129488.24</v>
+        <v>106696.8</v>
       </c>
       <c r="C96" s="5" t="n">
-        <v>6016.57</v>
+        <v>1262.64</v>
       </c>
       <c r="D96" s="5" t="n">
-        <v>123471.67</v>
+        <v>105434.15</v>
       </c>
       <c r="E96" t="n">
         <v>3</v>
@@ -3351,13 +3351,13 @@
         <v>46114</v>
       </c>
       <c r="B97" s="5" t="n">
-        <v>127413.8</v>
+        <v>101779.5</v>
       </c>
       <c r="C97" s="5" t="n">
-        <v>4043.32</v>
+        <v>843.46</v>
       </c>
       <c r="D97" s="5" t="n">
-        <v>123370.48</v>
+        <v>100936.03</v>
       </c>
       <c r="E97" t="n">
         <v>2</v>
@@ -3370,7 +3370,7 @@
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP stop (-2,074)</t>
+          <t>United_States_Oil_Fund_LP stop (-4,917)</t>
         </is>
       </c>
     </row>
@@ -3379,13 +3379,13 @@
         <v>46115</v>
       </c>
       <c r="B98" s="5" t="n">
-        <v>127413.8</v>
+        <v>101779.5</v>
       </c>
       <c r="C98" s="5" t="n">
-        <v>4043.32</v>
+        <v>843.46</v>
       </c>
       <c r="D98" s="5" t="n">
-        <v>123370.48</v>
+        <v>100936.03</v>
       </c>
       <c r="E98" t="n">
         <v>2</v>
@@ -3403,13 +3403,13 @@
         <v>46116</v>
       </c>
       <c r="B99" s="5" t="n">
-        <v>127413.8</v>
+        <v>101779.5</v>
       </c>
       <c r="C99" s="5" t="n">
-        <v>4043.32</v>
+        <v>843.46</v>
       </c>
       <c r="D99" s="5" t="n">
-        <v>123370.48</v>
+        <v>100936.03</v>
       </c>
       <c r="E99" t="n">
         <v>2</v>
@@ -3427,13 +3427,13 @@
         <v>46117</v>
       </c>
       <c r="B100" s="5" t="n">
-        <v>127413.8</v>
+        <v>101779.5</v>
       </c>
       <c r="C100" s="5" t="n">
-        <v>4043.32</v>
+        <v>843.46</v>
       </c>
       <c r="D100" s="5" t="n">
-        <v>123370.48</v>
+        <v>100936.03</v>
       </c>
       <c r="E100" t="n">
         <v>2</v>
@@ -3451,13 +3451,13 @@
         <v>46118</v>
       </c>
       <c r="B101" s="5" t="n">
-        <v>127413.8</v>
+        <v>101779.5</v>
       </c>
       <c r="C101" s="5" t="n">
-        <v>4043.32</v>
+        <v>843.46</v>
       </c>
       <c r="D101" s="5" t="n">
-        <v>123370.48</v>
+        <v>100936.03</v>
       </c>
       <c r="E101" t="n">
         <v>2</v>
@@ -3475,13 +3475,13 @@
         <v>46119</v>
       </c>
       <c r="B102" s="5" t="n">
-        <v>127413.8</v>
+        <v>101779.5</v>
       </c>
       <c r="C102" s="5" t="n">
-        <v>4043.32</v>
+        <v>843.46</v>
       </c>
       <c r="D102" s="5" t="n">
-        <v>123370.48</v>
+        <v>100936.03</v>
       </c>
       <c r="E102" t="n">
         <v>2</v>
@@ -3499,13 +3499,13 @@
         <v>46120</v>
       </c>
       <c r="B103" s="5" t="n">
-        <v>127413.8</v>
+        <v>101779.5</v>
       </c>
       <c r="C103" s="5" t="n">
-        <v>4043.32</v>
+        <v>843.46</v>
       </c>
       <c r="D103" s="5" t="n">
-        <v>123370.48</v>
+        <v>100936.03</v>
       </c>
       <c r="E103" t="n">
         <v>2</v>
@@ -3523,13 +3523,13 @@
         <v>46121</v>
       </c>
       <c r="B104" s="5" t="n">
-        <v>127413.8</v>
+        <v>101779.5</v>
       </c>
       <c r="C104" s="5" t="n">
-        <v>4043.32</v>
+        <v>843.46</v>
       </c>
       <c r="D104" s="5" t="n">
-        <v>123370.48</v>
+        <v>100936.03</v>
       </c>
       <c r="E104" t="n">
         <v>2</v>
@@ -3547,13 +3547,13 @@
         <v>46122</v>
       </c>
       <c r="B105" s="5" t="n">
-        <v>141762.24</v>
+        <v>104755.03</v>
       </c>
       <c r="C105" s="5" t="n">
-        <v>2005.63</v>
+        <v>420.89</v>
       </c>
       <c r="D105" s="5" t="n">
-        <v>139756.6</v>
+        <v>104334.13</v>
       </c>
       <c r="E105" t="n">
         <v>1</v>
@@ -3566,7 +3566,7 @@
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures bullish_reversal (+14,348)</t>
+          <t>NY_Copper_Futures bullish_reversal (+2,976)</t>
         </is>
       </c>
     </row>
@@ -3575,13 +3575,13 @@
         <v>46123</v>
       </c>
       <c r="B106" s="5" t="n">
-        <v>141762.24</v>
+        <v>104755.03</v>
       </c>
       <c r="C106" s="5" t="n">
-        <v>2005.63</v>
+        <v>420.89</v>
       </c>
       <c r="D106" s="5" t="n">
-        <v>139756.6</v>
+        <v>104334.13</v>
       </c>
       <c r="E106" t="n">
         <v>1</v>
@@ -3599,13 +3599,13 @@
         <v>46124</v>
       </c>
       <c r="B107" s="5" t="n">
-        <v>141762.24</v>
+        <v>104755.03</v>
       </c>
       <c r="C107" s="5" t="n">
-        <v>2005.63</v>
+        <v>420.89</v>
       </c>
       <c r="D107" s="5" t="n">
-        <v>139756.6</v>
+        <v>104334.13</v>
       </c>
       <c r="E107" t="n">
         <v>1</v>
@@ -3623,13 +3623,13 @@
         <v>46125</v>
       </c>
       <c r="B108" s="5" t="n">
-        <v>141762.24</v>
+        <v>104755.03</v>
       </c>
       <c r="C108" s="5" t="n">
-        <v>2005.63</v>
+        <v>420.89</v>
       </c>
       <c r="D108" s="5" t="n">
-        <v>139756.6</v>
+        <v>104334.13</v>
       </c>
       <c r="E108" t="n">
         <v>1</v>
@@ -3647,13 +3647,13 @@
         <v>46126</v>
       </c>
       <c r="B109" s="5" t="n">
-        <v>141762.24</v>
+        <v>104755.03</v>
       </c>
       <c r="C109" s="5" t="n">
-        <v>4204.01</v>
+        <v>834.0599999999999</v>
       </c>
       <c r="D109" s="5" t="n">
-        <v>137558.23</v>
+        <v>103920.97</v>
       </c>
       <c r="E109" t="n">
         <v>2</v>
@@ -3665,7 +3665,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance short (risk 2,198)</t>
+          <t>Bitcoin_Per_USD_Binance short (risk 413)</t>
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
@@ -3675,13 +3675,13 @@
         <v>46127</v>
       </c>
       <c r="B110" s="5" t="n">
-        <v>141762.24</v>
+        <v>104755.03</v>
       </c>
       <c r="C110" s="5" t="n">
-        <v>10593.8</v>
+        <v>2063.76</v>
       </c>
       <c r="D110" s="5" t="n">
-        <v>131168.43</v>
+        <v>102691.27</v>
       </c>
       <c r="E110" t="n">
         <v>5</v>
@@ -3693,7 +3693,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Ethereum_Per_USD_Binance short (risk 2,164); Live_Cattle_Futures_CME short (risk 2,130); NY_Copper_Futures short (risk 2,096)</t>
+          <t>Ethereum_Per_USD_Binance short (risk 412); Live_Cattle_Futures_CME short (risk 410); NY_Copper_Futures short (risk 408)</t>
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
@@ -3703,13 +3703,13 @@
         <v>46128</v>
       </c>
       <c r="B111" s="5" t="n">
-        <v>141762.24</v>
+        <v>104755.03</v>
       </c>
       <c r="C111" s="5" t="n">
-        <v>10593.8</v>
+        <v>2063.76</v>
       </c>
       <c r="D111" s="5" t="n">
-        <v>131168.43</v>
+        <v>102691.27</v>
       </c>
       <c r="E111" t="n">
         <v>5</v>
@@ -3727,13 +3727,13 @@
         <v>46129</v>
       </c>
       <c r="B112" s="5" t="n">
-        <v>193768</v>
+        <v>114789.24</v>
       </c>
       <c r="C112" s="5" t="n">
-        <v>4101.89</v>
+        <v>829.17</v>
       </c>
       <c r="D112" s="5" t="n">
-        <v>189666.11</v>
+        <v>113960.07</v>
       </c>
       <c r="E112" t="n">
         <v>2</v>
@@ -3745,12 +3745,12 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate long (risk 2,063)</t>
+          <t>USD_EUR_Cross_Rate long (risk 407)</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance stop (-2,206); Ethereum_Per_USD_Binance stop (-2,705); Live_Cattle_Futures_CME bearish_reversal (+54,986); USD_EUR_Cross_Rate data_end (+1,930)</t>
+          <t>Bitcoin_Per_USD_Binance stop (-415); Ethereum_Per_USD_Binance stop (-514); Live_Cattle_Futures_CME bearish_reversal (+10,583); USD_EUR_Cross_Rate data_end (+380)</t>
         </is>
       </c>
     </row>
@@ -3759,13 +3759,13 @@
         <v>46130</v>
       </c>
       <c r="B113" s="5" t="n">
-        <v>193768</v>
+        <v>114789.24</v>
       </c>
       <c r="C113" s="5" t="n">
-        <v>4101.89</v>
+        <v>829.17</v>
       </c>
       <c r="D113" s="5" t="n">
-        <v>189666.11</v>
+        <v>113960.07</v>
       </c>
       <c r="E113" t="n">
         <v>2</v>
@@ -3783,13 +3783,13 @@
         <v>46132</v>
       </c>
       <c r="B114" s="5" t="n">
-        <v>193768</v>
+        <v>114789.24</v>
       </c>
       <c r="C114" s="5" t="n">
-        <v>4101.89</v>
+        <v>829.17</v>
       </c>
       <c r="D114" s="5" t="n">
-        <v>189666.11</v>
+        <v>113960.07</v>
       </c>
       <c r="E114" t="n">
         <v>2</v>
@@ -3807,13 +3807,13 @@
         <v>46133</v>
       </c>
       <c r="B115" s="5" t="n">
-        <v>193768</v>
+        <v>114789.24</v>
       </c>
       <c r="C115" s="5" t="n">
-        <v>4101.89</v>
+        <v>829.17</v>
       </c>
       <c r="D115" s="5" t="n">
-        <v>189666.11</v>
+        <v>113960.07</v>
       </c>
       <c r="E115" t="n">
         <v>2</v>
@@ -3831,13 +3831,13 @@
         <v>46134</v>
       </c>
       <c r="B116" s="5" t="n">
-        <v>191655.77</v>
+        <v>114377.85</v>
       </c>
       <c r="C116" s="5" t="n">
-        <v>4989.08</v>
+        <v>872.1799999999999</v>
       </c>
       <c r="D116" s="5" t="n">
-        <v>186666.69</v>
+        <v>113505.67</v>
       </c>
       <c r="E116" t="n">
         <v>2</v>
@@ -3849,12 +3849,12 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini short (risk 2,983)</t>
+          <t>Dow_Futures_E_mini short (risk 451)</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures stop (-2,112)</t>
+          <t>NY_Copper_Futures stop (-411)</t>
         </is>
       </c>
     </row>
@@ -3863,13 +3863,13 @@
         <v>46135</v>
       </c>
       <c r="B117" s="5" t="n">
-        <v>191655.77</v>
+        <v>114377.85</v>
       </c>
       <c r="C117" s="5" t="n">
-        <v>4989.08</v>
+        <v>872.1799999999999</v>
       </c>
       <c r="D117" s="5" t="n">
-        <v>186666.69</v>
+        <v>113505.67</v>
       </c>
       <c r="E117" t="n">
         <v>2</v>
@@ -3887,13 +3887,13 @@
         <v>46136</v>
       </c>
       <c r="B118" s="5" t="n">
-        <v>191655.77</v>
+        <v>114377.85</v>
       </c>
       <c r="C118" s="5" t="n">
-        <v>4989.08</v>
+        <v>872.1799999999999</v>
       </c>
       <c r="D118" s="5" t="n">
-        <v>186666.69</v>
+        <v>113505.67</v>
       </c>
       <c r="E118" t="n">
         <v>2</v>
@@ -3911,13 +3911,13 @@
         <v>46139</v>
       </c>
       <c r="B119" s="5" t="n">
-        <v>191655.77</v>
+        <v>114377.85</v>
       </c>
       <c r="C119" s="5" t="n">
-        <v>7925.35</v>
+        <v>1321.66</v>
       </c>
       <c r="D119" s="5" t="n">
-        <v>183730.42</v>
+        <v>113056.19</v>
       </c>
       <c r="E119" t="n">
         <v>3</v>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_CME short (risk 2,936)</t>
+          <t>Bitcoin_Per_USD_CME short (risk 449)</t>
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
@@ -3939,13 +3939,13 @@
         <v>46140</v>
       </c>
       <c r="B120" s="5" t="n">
-        <v>191655.77</v>
+        <v>114377.85</v>
       </c>
       <c r="C120" s="5" t="n">
-        <v>10815.43</v>
+        <v>1769.36</v>
       </c>
       <c r="D120" s="5" t="n">
-        <v>180840.34</v>
+        <v>112608.49</v>
       </c>
       <c r="E120" t="n">
         <v>4</v>
@@ -3957,7 +3957,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>S_P_500_E_mini short (risk 2,890)</t>
+          <t>S_P_500_E_mini short (risk 448)</t>
         </is>
       </c>
       <c r="H120" t="inlineStr"/>
@@ -3967,13 +3967,13 @@
         <v>46141</v>
       </c>
       <c r="B121" s="5" t="n">
-        <v>191655.77</v>
+        <v>114377.85</v>
       </c>
       <c r="C121" s="5" t="n">
-        <v>13660.05</v>
+        <v>2215.29</v>
       </c>
       <c r="D121" s="5" t="n">
-        <v>177995.72</v>
+        <v>112162.56</v>
       </c>
       <c r="E121" t="n">
         <v>5</v>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 2,845)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 446)</t>
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
@@ -3995,13 +3995,13 @@
         <v>46142</v>
       </c>
       <c r="B122" s="5" t="n">
-        <v>185579.69</v>
+        <v>113448.2</v>
       </c>
       <c r="C122" s="5" t="n">
-        <v>10586.39</v>
+        <v>1760.47</v>
       </c>
       <c r="D122" s="5" t="n">
-        <v>174993.3</v>
+        <v>111687.73</v>
       </c>
       <c r="E122" t="n">
         <v>4</v>
@@ -4013,12 +4013,12 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures short (risk 2,800)</t>
+          <t>Corn_CBOT_Futures short (risk 444)</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini stop (-3,179); S_P_500_E_mini stop (-2,897)</t>
+          <t>Dow_Futures_E_mini stop (-481); S_P_500_E_mini stop (-449)</t>
         </is>
       </c>
     </row>
@@ -4027,13 +4027,13 @@
         <v>46143</v>
       </c>
       <c r="B123" s="5" t="n">
-        <v>182190.37</v>
+        <v>112910.53</v>
       </c>
       <c r="C123" s="5" t="n">
-        <v>15915.24</v>
+        <v>2637.91</v>
       </c>
       <c r="D123" s="5" t="n">
-        <v>166275.13</v>
+        <v>110272.62</v>
       </c>
       <c r="E123" t="n">
         <v>6</v>
@@ -4045,12 +4045,12 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Japanese_Yen_Futures short (risk 2,753); Live_Cattle_Futures_CME short (risk 2,709); US_Dollar_Index_Futures long (risk 2,667)</t>
+          <t>Japanese_Yen_Futures short (risk 442); Live_Cattle_Futures_CME short (risk 441); US_Dollar_Index_Futures long (risk 439)</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures stop (-3,389)</t>
+          <t>Corn_CBOT_Futures stop (-538)</t>
         </is>
       </c>
     </row>
@@ -4059,13 +4059,13 @@
         <v>46146</v>
       </c>
       <c r="B124" s="5" t="n">
-        <v>179229.94</v>
+        <v>112457.35</v>
       </c>
       <c r="C124" s="5" t="n">
-        <v>15594.48</v>
+        <v>2625.11</v>
       </c>
       <c r="D124" s="5" t="n">
-        <v>163635.46</v>
+        <v>109832.24</v>
       </c>
       <c r="E124" t="n">
         <v>6</v>
@@ -4077,12 +4077,12 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Nasdaq_100_E_mini short (risk 2,616)</t>
+          <t>Nasdaq_100_E_mini short (risk 437)</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_CME stop (-2,960)</t>
+          <t>Bitcoin_Per_USD_CME stop (-453)</t>
         </is>
       </c>
     </row>
@@ -4091,13 +4091,13 @@
         <v>46147</v>
       </c>
       <c r="B125" s="5" t="n">
-        <v>176612.65</v>
+        <v>112020.37</v>
       </c>
       <c r="C125" s="5" t="n">
-        <v>15552.96</v>
+        <v>2623.36</v>
       </c>
       <c r="D125" s="5" t="n">
-        <v>161059.69</v>
+        <v>109397.01</v>
       </c>
       <c r="E125" t="n">
         <v>6</v>
@@ -4109,12 +4109,12 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures short (risk 2,574)</t>
+          <t>Corn_CBOT_Futures short (risk 435)</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Nasdaq_100_E_mini stop (-2,617)</t>
+          <t>Nasdaq_100_E_mini stop (-437)</t>
         </is>
       </c>
     </row>
@@ -4123,13 +4123,13 @@
         <v>46148</v>
       </c>
       <c r="B126" s="5" t="n">
-        <v>188559.13</v>
+        <v>113860.11</v>
       </c>
       <c r="C126" s="5" t="n">
-        <v>9822.43</v>
+        <v>1729.57</v>
       </c>
       <c r="D126" s="5" t="n">
-        <v>178736.7</v>
+        <v>112130.54</v>
       </c>
       <c r="E126" t="n">
         <v>4</v>
@@ -4141,12 +4141,12 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_CME short (risk 2,533)</t>
+          <t>Bitcoin_Per_USD_CME short (risk 433)</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT bearish_reversal (+17,707); Japanese_Yen_Futures stop (-3,050); US_Dollar_Index_Futures stop (-2,710)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT bearish_reversal (+2,776); Japanese_Yen_Futures stop (-490); US_Dollar_Index_Futures stop (-446)</t>
         </is>
       </c>
     </row>
@@ -4155,13 +4155,13 @@
         <v>46149</v>
       </c>
       <c r="B127" s="5" t="n">
-        <v>218002.95</v>
+        <v>120039.09</v>
       </c>
       <c r="C127" s="5" t="n">
-        <v>13395.63</v>
+        <v>2195</v>
       </c>
       <c r="D127" s="5" t="n">
-        <v>204607.32</v>
+        <v>117844.09</v>
       </c>
       <c r="E127" t="n">
         <v>5</v>
@@ -4173,12 +4173,12 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>EURO_Futures short (risk 2,812); NY_Platinum_Futures short (risk 2,767)</t>
+          <t>EURO_Futures short (risk 444); NY_Platinum_Futures short (risk 442)</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX bullish_reversal (+29,444)</t>
+          <t>Gold_Futures_COMEX bullish_reversal (+6,179)</t>
         </is>
       </c>
     </row>
@@ -4187,13 +4187,13 @@
         <v>46150</v>
       </c>
       <c r="B128" s="5" t="n">
-        <v>215119.33</v>
+        <v>119583.66</v>
       </c>
       <c r="C128" s="5" t="n">
-        <v>10584.1</v>
+        <v>1750.96</v>
       </c>
       <c r="D128" s="5" t="n">
-        <v>204535.23</v>
+        <v>117832.7</v>
       </c>
       <c r="E128" t="n">
         <v>4</v>
@@ -4206,7 +4206,7 @@
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr">
         <is>
-          <t>EURO_Futures stop (-2,884)</t>
+          <t>EURO_Futures stop (-455)</t>
         </is>
       </c>
     </row>
@@ -4215,13 +4215,13 @@
         <v>46153</v>
       </c>
       <c r="B129" s="5" t="n">
-        <v>230434.09</v>
+        <v>122081.58</v>
       </c>
       <c r="C129" s="5" t="n">
-        <v>8324.790000000001</v>
+        <v>1334.77</v>
       </c>
       <c r="D129" s="5" t="n">
-        <v>222109.3</v>
+        <v>120746.82</v>
       </c>
       <c r="E129" t="n">
         <v>3</v>
@@ -4233,12 +4233,12 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX short (risk 3,217)</t>
+          <t>Gold_Futures_COMEX short (risk 467)</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Live_Cattle_Futures_CME bearish_reversal (+18,120); NY_Platinum_Futures stop (-2,805)</t>
+          <t>Live_Cattle_Futures_CME bearish_reversal (+2,946); NY_Platinum_Futures stop (-448)</t>
         </is>
       </c>
     </row>
@@ -4247,13 +4247,13 @@
         <v>46154</v>
       </c>
       <c r="B130" s="5" t="n">
-        <v>227113.8</v>
+        <v>121600.03</v>
       </c>
       <c r="C130" s="5" t="n">
-        <v>8601.23</v>
+        <v>1346.31</v>
       </c>
       <c r="D130" s="5" t="n">
-        <v>218512.57</v>
+        <v>120253.73</v>
       </c>
       <c r="E130" t="n">
         <v>3</v>
@@ -4265,12 +4265,12 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX short (risk 3,494)</t>
+          <t>Silver_Futures_COMEX short (risk 478)</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX stop (-3,320)</t>
+          <t>Gold_Futures_COMEX stop (-482)</t>
         </is>
       </c>
     </row>
@@ -4279,13 +4279,13 @@
         <v>46155</v>
       </c>
       <c r="B131" s="5" t="n">
-        <v>223612.74</v>
+        <v>121120.88</v>
       </c>
       <c r="C131" s="5" t="n">
-        <v>5107.45</v>
+        <v>868.15</v>
       </c>
       <c r="D131" s="5" t="n">
-        <v>218505.29</v>
+        <v>120252.73</v>
       </c>
       <c r="E131" t="n">
         <v>2</v>
@@ -4298,7 +4298,7 @@
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX stop (-3,501)</t>
+          <t>Silver_Futures_COMEX stop (-479)</t>
         </is>
       </c>
     </row>
@@ -4307,13 +4307,13 @@
         <v>46156</v>
       </c>
       <c r="B132" s="5" t="n">
-        <v>223612.74</v>
+        <v>121120.88</v>
       </c>
       <c r="C132" s="5" t="n">
-        <v>8544.540000000001</v>
+        <v>1344.35</v>
       </c>
       <c r="D132" s="5" t="n">
-        <v>215068.2</v>
+        <v>119776.53</v>
       </c>
       <c r="E132" t="n">
         <v>3</v>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 3,437)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 476)</t>
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
@@ -4335,13 +4335,13 @@
         <v>46157</v>
       </c>
       <c r="B133" s="5" t="n">
-        <v>280240.38</v>
+        <v>130689.46</v>
       </c>
       <c r="C133" s="5" t="n">
-        <v>5970.56</v>
+        <v>909.41</v>
       </c>
       <c r="D133" s="5" t="n">
-        <v>274269.83</v>
+        <v>129780.04</v>
       </c>
       <c r="E133" t="n">
         <v>2</v>
@@ -4354,7 +4354,7 @@
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures bearish_reversal (+56,628)</t>
+          <t>Corn_CBOT_Futures bearish_reversal (+9,569)</t>
         </is>
       </c>
     </row>
@@ -4363,13 +4363,13 @@
         <v>46160</v>
       </c>
       <c r="B134" s="5" t="n">
-        <v>308542.26</v>
+        <v>135528.96</v>
       </c>
       <c r="C134" s="5" t="n">
-        <v>3437.09</v>
+        <v>476.2</v>
       </c>
       <c r="D134" s="5" t="n">
-        <v>305105.17</v>
+        <v>135052.75</v>
       </c>
       <c r="E134" t="n">
         <v>1</v>
@@ -4382,7 +4382,7 @@
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_CME bearish_reversal (+28,302)</t>
+          <t>Bitcoin_Per_USD_CME bearish_reversal (+4,839)</t>
         </is>
       </c>
     </row>
@@ -4391,13 +4391,13 @@
         <v>46161</v>
       </c>
       <c r="B135" s="5" t="n">
-        <v>308542.26</v>
+        <v>135528.96</v>
       </c>
       <c r="C135" s="5" t="n">
-        <v>3437.09</v>
+        <v>476.2</v>
       </c>
       <c r="D135" s="5" t="n">
-        <v>305105.17</v>
+        <v>135052.75</v>
       </c>
       <c r="E135" t="n">
         <v>1</v>
@@ -4415,13 +4415,13 @@
         <v>46162</v>
       </c>
       <c r="B136" s="5" t="n">
-        <v>308542.26</v>
+        <v>135528.96</v>
       </c>
       <c r="C136" s="5" t="n">
-        <v>8236.389999999999</v>
+        <v>1011.01</v>
       </c>
       <c r="D136" s="5" t="n">
-        <v>300305.87</v>
+        <v>134517.95</v>
       </c>
       <c r="E136" t="n">
         <v>2</v>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures short (risk 4,799)</t>
+          <t>US_Dollar_Index_Futures short (risk 535)</t>
         </is>
       </c>
       <c r="H136" t="inlineStr"/>
@@ -4443,13 +4443,13 @@
         <v>46163</v>
       </c>
       <c r="B137" s="5" t="n">
-        <v>308542.26</v>
+        <v>135528.96</v>
       </c>
       <c r="C137" s="5" t="n">
-        <v>12960.2</v>
+        <v>1543.7</v>
       </c>
       <c r="D137" s="5" t="n">
-        <v>295582.06</v>
+        <v>133985.25</v>
       </c>
       <c r="E137" t="n">
         <v>3</v>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>NY_Palladium_Futures long (risk 4,724)</t>
+          <t>NY_Palladium_Futures long (risk 533)</t>
         </is>
       </c>
       <c r="H137" t="inlineStr"/>
@@ -4471,13 +4471,13 @@
         <v>46164</v>
       </c>
       <c r="B138" s="5" t="n">
-        <v>308542.26</v>
+        <v>135528.96</v>
       </c>
       <c r="C138" s="5" t="n">
-        <v>12960.2</v>
+        <v>1543.7</v>
       </c>
       <c r="D138" s="5" t="n">
-        <v>295582.06</v>
+        <v>133985.25</v>
       </c>
       <c r="E138" t="n">
         <v>3</v>
@@ -4495,13 +4495,13 @@
         <v>46167</v>
       </c>
       <c r="B139" s="5" t="n">
-        <v>308542.26</v>
+        <v>135528.96</v>
       </c>
       <c r="C139" s="5" t="n">
-        <v>12960.2</v>
+        <v>1543.7</v>
       </c>
       <c r="D139" s="5" t="n">
-        <v>295582.06</v>
+        <v>133985.25</v>
       </c>
       <c r="E139" t="n">
         <v>3</v>
@@ -4519,13 +4519,13 @@
         <v>46168</v>
       </c>
       <c r="B140" s="5" t="n">
-        <v>308542.26</v>
+        <v>135528.96</v>
       </c>
       <c r="C140" s="5" t="n">
-        <v>12960.2</v>
+        <v>1543.7</v>
       </c>
       <c r="D140" s="5" t="n">
-        <v>295582.06</v>
+        <v>133985.25</v>
       </c>
       <c r="E140" t="n">
         <v>3</v>
@@ -4543,13 +4543,13 @@
         <v>46169</v>
       </c>
       <c r="B141" s="5" t="n">
-        <v>308542.26</v>
+        <v>135528.96</v>
       </c>
       <c r="C141" s="5" t="n">
-        <v>12960.2</v>
+        <v>1543.7</v>
       </c>
       <c r="D141" s="5" t="n">
-        <v>295582.06</v>
+        <v>133985.25</v>
       </c>
       <c r="E141" t="n">
         <v>3</v>
@@ -4567,13 +4567,13 @@
         <v>46170</v>
       </c>
       <c r="B142" s="5" t="n">
-        <v>308542.26</v>
+        <v>135528.96</v>
       </c>
       <c r="C142" s="5" t="n">
-        <v>17609.71</v>
+        <v>2074.28</v>
       </c>
       <c r="D142" s="5" t="n">
-        <v>290932.55</v>
+        <v>133454.67</v>
       </c>
       <c r="E142" t="n">
         <v>4</v>
@@ -4585,7 +4585,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX long (risk 4,650)</t>
+          <t>Silver_Futures_COMEX long (risk 531)</t>
         </is>
       </c>
       <c r="H142" t="inlineStr"/>
@@ -4595,13 +4595,13 @@
         <v>46174</v>
       </c>
       <c r="B143" s="5" t="n">
-        <v>343289.86</v>
+        <v>140343.16</v>
       </c>
       <c r="C143" s="5" t="n">
-        <v>14172.62</v>
+        <v>1598.08</v>
       </c>
       <c r="D143" s="5" t="n">
-        <v>329117.24</v>
+        <v>138745.07</v>
       </c>
       <c r="E143" t="n">
         <v>3</v>
@@ -4614,7 +4614,7 @@
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT bearish_reversal (+34,748)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT bearish_reversal (+4,814)</t>
         </is>
       </c>
     </row>
@@ -4623,13 +4623,13 @@
         <v>46175</v>
       </c>
       <c r="B144" s="5" t="n">
-        <v>343289.86</v>
+        <v>140343.16</v>
       </c>
       <c r="C144" s="5" t="n">
-        <v>14172.62</v>
+        <v>1598.08</v>
       </c>
       <c r="D144" s="5" t="n">
-        <v>329117.24</v>
+        <v>138745.07</v>
       </c>
       <c r="E144" t="n">
         <v>3</v>
@@ -4647,13 +4647,13 @@
         <v>46176</v>
       </c>
       <c r="B145" s="5" t="n">
-        <v>338454.9</v>
+        <v>139797.93</v>
       </c>
       <c r="C145" s="5" t="n">
-        <v>9448.809999999999</v>
+        <v>1065.39</v>
       </c>
       <c r="D145" s="5" t="n">
-        <v>329006.09</v>
+        <v>138732.54</v>
       </c>
       <c r="E145" t="n">
         <v>2</v>
@@ -4666,7 +4666,7 @@
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr">
         <is>
-          <t>NY_Palladium_Futures stop (-4,835)</t>
+          <t>NY_Palladium_Futures stop (-545)</t>
         </is>
       </c>
     </row>
@@ -4675,13 +4675,13 @@
         <v>46177</v>
       </c>
       <c r="B146" s="5" t="n">
-        <v>338454.9</v>
+        <v>139797.93</v>
       </c>
       <c r="C146" s="5" t="n">
-        <v>9448.809999999999</v>
+        <v>1065.39</v>
       </c>
       <c r="D146" s="5" t="n">
-        <v>329006.09</v>
+        <v>138732.54</v>
       </c>
       <c r="E146" t="n">
         <v>2</v>
@@ -4699,13 +4699,13 @@
         <v>46178</v>
       </c>
       <c r="B147" s="5" t="n">
-        <v>328897.56</v>
+        <v>138720.42</v>
       </c>
       <c r="C147" s="5" t="n">
-        <v>5175.27</v>
+        <v>549.38</v>
       </c>
       <c r="D147" s="5" t="n">
-        <v>323722.29</v>
+        <v>138171.04</v>
       </c>
       <c r="E147" t="n">
         <v>1</v>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini short (risk 5,175)</t>
+          <t>Dow_Futures_E_mini short (risk 549)</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX stop (-4,660); US_Dollar_Index_Futures stop (-4,898)</t>
+          <t>Silver_Futures_COMEX stop (-532); US_Dollar_Index_Futures stop (-546)</t>
         </is>
       </c>
     </row>
@@ -4731,13 +4731,13 @@
         <v>46181</v>
       </c>
       <c r="B148" s="5" t="n">
-        <v>328897.56</v>
+        <v>138720.42</v>
       </c>
       <c r="C148" s="5" t="n">
-        <v>15279.47</v>
+        <v>1641.53</v>
       </c>
       <c r="D148" s="5" t="n">
-        <v>313618.09</v>
+        <v>137078.89</v>
       </c>
       <c r="E148" t="n">
         <v>3</v>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX long (risk 5,092); US_Dollar_Index_Futures short (risk 5,012)</t>
+          <t>Gold_Futures_COMEX long (risk 547); US_Dollar_Index_Futures short (risk 545)</t>
         </is>
       </c>
       <c r="H148" t="inlineStr"/>
@@ -4759,13 +4759,13 @@
         <v>46182</v>
       </c>
       <c r="B149" s="5" t="n">
-        <v>323767.76</v>
+        <v>138169.22</v>
       </c>
       <c r="C149" s="5" t="n">
-        <v>10187.32</v>
+        <v>1094.37</v>
       </c>
       <c r="D149" s="5" t="n">
-        <v>313580.44</v>
+        <v>137074.85</v>
       </c>
       <c r="E149" t="n">
         <v>2</v>
@@ -4778,7 +4778,7 @@
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX stop (-5,130)</t>
+          <t>Gold_Futures_COMEX stop (-551)</t>
         </is>
       </c>
     </row>
@@ -4787,13 +4787,13 @@
         <v>46183</v>
       </c>
       <c r="B150" s="5" t="n">
-        <v>323767.76</v>
+        <v>138169.22</v>
       </c>
       <c r="C150" s="5" t="n">
-        <v>10187.32</v>
+        <v>1094.37</v>
       </c>
       <c r="D150" s="5" t="n">
-        <v>313580.44</v>
+        <v>137074.85</v>
       </c>
       <c r="E150" t="n">
         <v>2</v>
@@ -4811,13 +4811,13 @@
         <v>46184</v>
       </c>
       <c r="B151" s="5" t="n">
-        <v>318607.2</v>
+        <v>137608.08</v>
       </c>
       <c r="C151" s="5" t="n">
-        <v>10107.89</v>
+        <v>1092.2</v>
       </c>
       <c r="D151" s="5" t="n">
-        <v>308499.31</v>
+        <v>136515.88</v>
       </c>
       <c r="E151" t="n">
         <v>2</v>
@@ -4829,12 +4829,12 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX long (risk 4,933)</t>
+          <t>Gold_Futures_COMEX long (risk 543)</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures stop (-5,161)</t>
+          <t>US_Dollar_Index_Futures stop (-561)</t>
         </is>
       </c>
     </row>
@@ -4843,13 +4843,13 @@
         <v>46185</v>
       </c>
       <c r="B152" s="5" t="n">
-        <v>318607.2</v>
+        <v>137608.08</v>
       </c>
       <c r="C152" s="5" t="n">
-        <v>14960.58</v>
+        <v>1632.8</v>
       </c>
       <c r="D152" s="5" t="n">
-        <v>303646.62</v>
+        <v>135975.28</v>
       </c>
       <c r="E152" t="n">
         <v>3</v>
@@ -4861,7 +4861,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures long (risk 4,853)</t>
+          <t>Corn_CBOT_Futures long (risk 541)</t>
         </is>
       </c>
       <c r="H152" t="inlineStr"/>
@@ -4871,13 +4871,13 @@
         <v>46188</v>
       </c>
       <c r="B153" s="5" t="n">
-        <v>307665.03</v>
+        <v>136417.27</v>
       </c>
       <c r="C153" s="5" t="n">
-        <v>9708.98</v>
+        <v>1081.28</v>
       </c>
       <c r="D153" s="5" t="n">
-        <v>297956.05</v>
+        <v>135336</v>
       </c>
       <c r="E153" t="n">
         <v>2</v>
@@ -4889,12 +4889,12 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT long (risk 4,776)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT long (risk 538)</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures stop (-5,572); Dow_Futures_E_mini stop (-5,371)</t>
+          <t>Corn_CBOT_Futures stop (-621); Dow_Futures_E_mini stop (-570)</t>
         </is>
       </c>
     </row>
@@ -4903,13 +4903,13 @@
         <v>46189</v>
       </c>
       <c r="B154" s="5" t="n">
-        <v>307665.03</v>
+        <v>136417.27</v>
       </c>
       <c r="C154" s="5" t="n">
-        <v>9708.98</v>
+        <v>1081.28</v>
       </c>
       <c r="D154" s="5" t="n">
-        <v>297956.05</v>
+        <v>135336</v>
       </c>
       <c r="E154" t="n">
         <v>2</v>
@@ -4927,13 +4927,13 @@
         <v>46190</v>
       </c>
       <c r="B155" s="5" t="n">
-        <v>331040.05</v>
+        <v>139052.45</v>
       </c>
       <c r="C155" s="5" t="n">
-        <v>9619.469999999999</v>
+        <v>1078.75</v>
       </c>
       <c r="D155" s="5" t="n">
-        <v>321420.58</v>
+        <v>137973.71</v>
       </c>
       <c r="E155" t="n">
         <v>2</v>
@@ -4945,12 +4945,12 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures short (risk 4,687)</t>
+          <t>US_Dollar_Index_Futures short (risk 536)</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT bullish_reversal (+23,375)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT bullish_reversal (+2,635)</t>
         </is>
       </c>
     </row>
@@ -4959,13 +4959,13 @@
         <v>46191</v>
       </c>
       <c r="B156" s="5" t="n">
-        <v>326289.65</v>
+        <v>138509.26</v>
       </c>
       <c r="C156" s="5" t="n">
-        <v>4932.62</v>
+        <v>542.8200000000001</v>
       </c>
       <c r="D156" s="5" t="n">
-        <v>321357.03</v>
+        <v>137966.44</v>
       </c>
       <c r="E156" t="n">
         <v>1</v>
@@ -4978,7 +4978,7 @@
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures stop (-4,750)</t>
+          <t>US_Dollar_Index_Futures stop (-543)</t>
         </is>
       </c>
     </row>
@@ -4987,13 +4987,13 @@
         <v>46192</v>
       </c>
       <c r="B157" s="5" t="n">
-        <v>326289.65</v>
+        <v>138509.26</v>
       </c>
       <c r="C157" s="5" t="n">
-        <v>9987.57</v>
+        <v>1089.16</v>
       </c>
       <c r="D157" s="5" t="n">
-        <v>316302.09</v>
+        <v>137420.09</v>
       </c>
       <c r="E157" t="n">
         <v>2</v>
@@ -5005,7 +5005,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures short (risk 5,055)</t>
+          <t>US_Dollar_Index_Futures short (risk 546)</t>
         </is>
       </c>
       <c r="H157" t="inlineStr"/>
@@ -5015,13 +5015,13 @@
         <v>46195</v>
       </c>
       <c r="B158" s="5" t="n">
-        <v>326289.65</v>
+        <v>138509.26</v>
       </c>
       <c r="C158" s="5" t="n">
-        <v>9987.57</v>
+        <v>1089.16</v>
       </c>
       <c r="D158" s="5" t="n">
-        <v>316302.09</v>
+        <v>137420.09</v>
       </c>
       <c r="E158" t="n">
         <v>2</v>
@@ -5039,13 +5039,13 @@
         <v>46196</v>
       </c>
       <c r="B159" s="5" t="n">
-        <v>321164.98</v>
+        <v>137955.37</v>
       </c>
       <c r="C159" s="5" t="n">
-        <v>9908.049999999999</v>
+        <v>1087</v>
       </c>
       <c r="D159" s="5" t="n">
-        <v>311256.93</v>
+        <v>136868.37</v>
       </c>
       <c r="E159" t="n">
         <v>2</v>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures long (risk 4,975)</t>
+          <t>NY_Platinum_Futures long (risk 544)</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures stop (-5,125)</t>
+          <t>US_Dollar_Index_Futures stop (-554)</t>
         </is>
       </c>
     </row>
@@ -5071,13 +5071,13 @@
         <v>46197</v>
       </c>
       <c r="B160" s="5" t="n">
-        <v>311125.17</v>
+        <v>136853.94</v>
       </c>
       <c r="C160" s="5" t="n">
-        <v>4896.07</v>
+        <v>542</v>
       </c>
       <c r="D160" s="5" t="n">
-        <v>306229.1</v>
+        <v>136311.94</v>
       </c>
       <c r="E160" t="n">
         <v>1</v>
@@ -5089,12 +5089,12 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>EURO_Futures long (risk 4,896)</t>
+          <t>EURO_Futures long (risk 542)</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX stop (-4,967); NY_Platinum_Futures stop (-5,073)</t>
+          <t>Gold_Futures_COMEX stop (-547); NY_Platinum_Futures stop (-555)</t>
         </is>
       </c>
     </row>
@@ -5103,13 +5103,13 @@
         <v>46198</v>
       </c>
       <c r="B161" s="5" t="n">
-        <v>311125.17</v>
+        <v>136853.94</v>
       </c>
       <c r="C161" s="5" t="n">
-        <v>23714.13</v>
+        <v>2688.39</v>
       </c>
       <c r="D161" s="5" t="n">
-        <v>287411.04</v>
+        <v>134165.55</v>
       </c>
       <c r="E161" t="n">
         <v>5</v>
@@ -5121,7 +5121,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures short (risk 4,817); NY_Palladium_Futures long (risk 4,741); NY_Platinum_Futures long (risk 4,667); US_Dollar_Index_Futures short (risk 4,593)</t>
+          <t>NY_Natural_Gas_Futures short (risk 540); NY_Palladium_Futures long (risk 538); NY_Platinum_Futures long (risk 536); US_Dollar_Index_Futures short (risk 533)</t>
         </is>
       </c>
       <c r="H161" t="inlineStr"/>
@@ -5131,13 +5131,13 @@
         <v>46199</v>
       </c>
       <c r="B162" s="5" t="n">
-        <v>305914.97</v>
+        <v>136270.08</v>
       </c>
       <c r="C162" s="5" t="n">
-        <v>18897.14</v>
+        <v>2148.59</v>
       </c>
       <c r="D162" s="5" t="n">
-        <v>287017.82</v>
+        <v>134121.49</v>
       </c>
       <c r="E162" t="n">
         <v>4</v>
@@ -5150,7 +5150,7 @@
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures stop (-5,210)</t>
+          <t>NY_Natural_Gas_Futures stop (-584)</t>
         </is>
       </c>
     </row>
@@ -5159,13 +5159,13 @@
         <v>46202</v>
       </c>
       <c r="B163" s="5" t="n">
-        <v>305914.97</v>
+        <v>136270.08</v>
       </c>
       <c r="C163" s="5" t="n">
-        <v>18897.14</v>
+        <v>2148.59</v>
       </c>
       <c r="D163" s="5" t="n">
-        <v>287017.82</v>
+        <v>134121.49</v>
       </c>
       <c r="E163" t="n">
         <v>4</v>
@@ -5183,13 +5183,13 @@
         <v>46203</v>
       </c>
       <c r="B164" s="5" t="n">
-        <v>305914.97</v>
+        <v>136270.08</v>
       </c>
       <c r="C164" s="5" t="n">
-        <v>32229.58</v>
+        <v>3735.65</v>
       </c>
       <c r="D164" s="5" t="n">
-        <v>273685.39</v>
+        <v>132534.42</v>
       </c>
       <c r="E164" t="n">
         <v>7</v>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT long (risk 4,515); German_Long_Bund short (risk 4,444); Gold_Futures_COMEX long (risk 4,374)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT long (risk 531); German_Long_Bund short (risk 529); Gold_Futures_COMEX long (risk 527)</t>
         </is>
       </c>
       <c r="H164" t="inlineStr"/>
@@ -5211,13 +5211,13 @@
         <v>46204</v>
       </c>
       <c r="B165" s="5" t="n">
-        <v>301193.27</v>
+        <v>135728.23</v>
       </c>
       <c r="C165" s="5" t="n">
-        <v>36105.37</v>
+        <v>4247.72</v>
       </c>
       <c r="D165" s="5" t="n">
-        <v>265087.9</v>
+        <v>131480.51</v>
       </c>
       <c r="E165" t="n">
         <v>8</v>
@@ -5229,12 +5229,12 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini short (risk 4,305); Sugar_World_CSCE_Futures short (risk 4,237)</t>
+          <t>Dow_Futures_E_mini short (risk 525); Sugar_World_CSCE_Futures short (risk 523)</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures stop (-4,722)</t>
+          <t>NY_Platinum_Futures stop (-542)</t>
         </is>
       </c>
     </row>
@@ -5243,13 +5243,13 @@
         <v>46205</v>
       </c>
       <c r="B166" s="5" t="n">
-        <v>333587.76</v>
+        <v>139465.02</v>
       </c>
       <c r="C166" s="5" t="n">
-        <v>27207.07</v>
+        <v>3189.48</v>
       </c>
       <c r="D166" s="5" t="n">
-        <v>306380.69</v>
+        <v>136275.54</v>
       </c>
       <c r="E166" t="n">
         <v>6</v>
@@ -5262,7 +5262,7 @@
       <c r="G166" t="inlineStr"/>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini stop (-4,351); US_Dollar_Index_Futures bearish_reversal (+36,746)</t>
+          <t>Dow_Futures_E_mini stop (-530); US_Dollar_Index_Futures bearish_reversal (+4,267)</t>
         </is>
       </c>
     </row>
@@ -5271,13 +5271,13 @@
         <v>46206</v>
       </c>
       <c r="B167" s="5" t="n">
-        <v>333587.76</v>
+        <v>139465.02</v>
       </c>
       <c r="C167" s="5" t="n">
-        <v>27207.07</v>
+        <v>3189.48</v>
       </c>
       <c r="D167" s="5" t="n">
-        <v>306380.69</v>
+        <v>136275.54</v>
       </c>
       <c r="E167" t="n">
         <v>6</v>
@@ -5295,13 +5295,13 @@
         <v>46210</v>
       </c>
       <c r="B168" s="5" t="n">
-        <v>328698.51</v>
+        <v>138861.84</v>
       </c>
       <c r="C168" s="5" t="n">
-        <v>22969.72</v>
+        <v>2666.72</v>
       </c>
       <c r="D168" s="5" t="n">
-        <v>305728.79</v>
+        <v>136195.12</v>
       </c>
       <c r="E168" t="n">
         <v>5</v>
@@ -5314,7 +5314,7 @@
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Sugar_World_CSCE_Futures stop (-4,889)</t>
+          <t>Sugar_World_CSCE_Futures stop (-603)</t>
         </is>
       </c>
     </row>
@@ -5323,13 +5323,13 @@
         <v>46211</v>
       </c>
       <c r="B169" s="5" t="n">
-        <v>402549.1</v>
+        <v>148324.8</v>
       </c>
       <c r="C169" s="5" t="n">
-        <v>23553.74</v>
+        <v>2683.11</v>
       </c>
       <c r="D169" s="5" t="n">
-        <v>378995.37</v>
+        <v>145641.69</v>
       </c>
       <c r="E169" t="n">
         <v>5</v>
@@ -5341,12 +5341,12 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Live_Cattle_Futures_CME long (risk 4,809); NY_Natural_Gas_Futures short (risk 4,733)</t>
+          <t>Live_Cattle_Futures_CME long (risk 539); NY_Natural_Gas_Futures short (risk 537)</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT bullish_reversal (+46,029); German_Long_Bund bearish_reversal (+27,822)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT bullish_reversal (+5,415); German_Long_Bund bearish_reversal (+4,048)</t>
         </is>
       </c>
     </row>
@@ -5355,13 +5355,13 @@
         <v>46212</v>
       </c>
       <c r="B170" s="5" t="n">
-        <v>419534.13</v>
+        <v>150252.41</v>
       </c>
       <c r="C170" s="5" t="n">
-        <v>18820.27</v>
+        <v>2145.91</v>
       </c>
       <c r="D170" s="5" t="n">
-        <v>400713.86</v>
+        <v>148106.5</v>
       </c>
       <c r="E170" t="n">
         <v>4</v>
@@ -5374,7 +5374,7 @@
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures bearish_reversal (+16,985)</t>
+          <t>NY_Natural_Gas_Futures bearish_reversal (+1,928)</t>
         </is>
       </c>
     </row>
@@ -5383,13 +5383,13 @@
         <v>46213</v>
       </c>
       <c r="B171" s="5" t="n">
-        <v>414496.01</v>
+        <v>149687.4</v>
       </c>
       <c r="C171" s="5" t="n">
-        <v>14011.16</v>
+        <v>1606.58</v>
       </c>
       <c r="D171" s="5" t="n">
-        <v>400484.85</v>
+        <v>148080.82</v>
       </c>
       <c r="E171" t="n">
         <v>3</v>
@@ -5402,7 +5402,7 @@
       <c r="G171" t="inlineStr"/>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Live_Cattle_Futures_CME stop (-5,038)</t>
+          <t>Live_Cattle_Futures_CME stop (-565)</t>
         </is>
       </c>
     </row>
@@ -5411,13 +5411,13 @@
         <v>46216</v>
       </c>
       <c r="B172" s="5" t="n">
-        <v>414496.01</v>
+        <v>149687.4</v>
       </c>
       <c r="C172" s="5" t="n">
-        <v>20310.78</v>
+        <v>2192.98</v>
       </c>
       <c r="D172" s="5" t="n">
-        <v>394185.22</v>
+        <v>147494.42</v>
       </c>
       <c r="E172" t="n">
         <v>4</v>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 6,300)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 586)</t>
         </is>
       </c>
       <c r="H172" t="inlineStr"/>
@@ -5439,13 +5439,13 @@
         <v>46217</v>
       </c>
       <c r="B173" s="5" t="n">
-        <v>495221.24</v>
+        <v>158841.71</v>
       </c>
       <c r="C173" s="5" t="n">
-        <v>15569.57</v>
+        <v>1655.32</v>
       </c>
       <c r="D173" s="5" t="n">
-        <v>479651.67</v>
+        <v>157186.39</v>
       </c>
       <c r="E173" t="n">
         <v>3</v>
@@ -5458,7 +5458,7 @@
       <c r="G173" t="inlineStr"/>
       <c r="H173" t="inlineStr">
         <is>
-          <t>NY_Palladium_Futures bullish_reversal (+80,725)</t>
+          <t>NY_Palladium_Futures bullish_reversal (+9,154)</t>
         </is>
       </c>
     </row>
@@ -5467,13 +5467,13 @@
         <v>46218</v>
       </c>
       <c r="B174" s="5" t="n">
-        <v>488610.52</v>
+        <v>158226.35</v>
       </c>
       <c r="C174" s="5" t="n">
-        <v>9269.940000000001</v>
+        <v>1068.92</v>
       </c>
       <c r="D174" s="5" t="n">
-        <v>479340.58</v>
+        <v>157157.43</v>
       </c>
       <c r="E174" t="n">
         <v>2</v>
@@ -5486,7 +5486,7 @@
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT stop (-6,611)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT stop (-615)</t>
         </is>
       </c>
     </row>
@@ -5495,13 +5495,13 @@
         <v>46219</v>
       </c>
       <c r="B175" s="5" t="n">
-        <v>488610.52</v>
+        <v>158226.35</v>
       </c>
       <c r="C175" s="5" t="n">
-        <v>9269.940000000001</v>
+        <v>1068.92</v>
       </c>
       <c r="D175" s="5" t="n">
-        <v>479340.58</v>
+        <v>157157.43</v>
       </c>
       <c r="E175" t="n">
         <v>2</v>
@@ -5519,13 +5519,13 @@
         <v>46220</v>
       </c>
       <c r="B176" s="5" t="n">
-        <v>488610.52</v>
+        <v>158226.35</v>
       </c>
       <c r="C176" s="5" t="n">
-        <v>9269.940000000001</v>
+        <v>1068.92</v>
       </c>
       <c r="D176" s="5" t="n">
-        <v>479340.58</v>
+        <v>157157.43</v>
       </c>
       <c r="E176" t="n">
         <v>2</v>
@@ -5543,13 +5543,13 @@
         <v>46223</v>
       </c>
       <c r="B177" s="5" t="n">
-        <v>488610.52</v>
+        <v>158226.35</v>
       </c>
       <c r="C177" s="5" t="n">
-        <v>9269.940000000001</v>
+        <v>1068.92</v>
       </c>
       <c r="D177" s="5" t="n">
-        <v>479340.58</v>
+        <v>157157.43</v>
       </c>
       <c r="E177" t="n">
         <v>2</v>
@@ -5567,13 +5567,13 @@
         <v>46224</v>
       </c>
       <c r="B178" s="5" t="n">
-        <v>488610.52</v>
+        <v>158226.35</v>
       </c>
       <c r="C178" s="5" t="n">
-        <v>9269.940000000001</v>
+        <v>1068.92</v>
       </c>
       <c r="D178" s="5" t="n">
-        <v>479340.58</v>
+        <v>157157.43</v>
       </c>
       <c r="E178" t="n">
         <v>2</v>
@@ -5591,13 +5591,13 @@
         <v>46225</v>
       </c>
       <c r="B179" s="5" t="n">
-        <v>488610.52</v>
+        <v>158226.35</v>
       </c>
       <c r="C179" s="5" t="n">
-        <v>9269.940000000001</v>
+        <v>1068.92</v>
       </c>
       <c r="D179" s="5" t="n">
-        <v>479340.58</v>
+        <v>157157.43</v>
       </c>
       <c r="E179" t="n">
         <v>2</v>
@@ -5615,13 +5615,13 @@
         <v>46226</v>
       </c>
       <c r="B180" s="5" t="n">
-        <v>488610.52</v>
+        <v>158226.35</v>
       </c>
       <c r="C180" s="5" t="n">
-        <v>9269.940000000001</v>
+        <v>1068.92</v>
       </c>
       <c r="D180" s="5" t="n">
-        <v>479340.58</v>
+        <v>157157.43</v>
       </c>
       <c r="E180" t="n">
         <v>2</v>
@@ -5639,13 +5639,13 @@
         <v>46227</v>
       </c>
       <c r="B181" s="5" t="n">
-        <v>488249.74</v>
+        <v>158195.32</v>
       </c>
       <c r="C181" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D181" s="5" t="n">
-        <v>488249.74</v>
+        <v>158195.32</v>
       </c>
       <c r="E181" t="n">
         <v>0</v>
@@ -5653,7 +5653,7 @@
       <c r="F181" t="inlineStr"/>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 7,540); Corn_CBOT_Futures short (risk 7,421)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 622); Corn_CBOT_Futures short (risk 620)</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -5684,10 +5684,10 @@
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
     <col width="9" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="18" customWidth="1" min="13" max="13"/>
   </cols>
@@ -5796,13 +5796,13 @@
         <v>100000</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>1573</v>
+        <v>1175</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>18079.99</v>
+        <v>13505.39</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>118079.99</v>
+        <v>113505.39</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -5844,16 +5844,16 @@
         <v>-1.014</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>118079.99</v>
+        <v>113505.39</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>1857.4</v>
+        <v>1333.69</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>-1884.32</v>
+        <v>-1353.02</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>116195.67</v>
+        <v>112152.38</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -5895,16 +5895,16 @@
         <v>-1.008</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>116195.67</v>
+        <v>112152.38</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>1827.76</v>
+        <v>1317.79</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>-1842.21</v>
+        <v>-1328.21</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>114353.46</v>
+        <v>110824.17</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -5946,16 +5946,16 @@
         <v>-1.005</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>114367.91</v>
+        <v>110834.59</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>1799.01</v>
+        <v>1302.31</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>-1807.71</v>
+        <v>-1308.61</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>112545.75</v>
+        <v>109515.56</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -5997,16 +5997,16 @@
         <v>-1.085</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>112545.75</v>
+        <v>109515.56</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>1770.34</v>
+        <v>1286.81</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>-1921.01</v>
+        <v>-1396.32</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>110624.74</v>
+        <v>108119.24</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -6048,16 +6048,16 @@
         <v>4.314</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>110624.74</v>
+        <v>108119.24</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>1740.13</v>
+        <v>1270.4</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>7507.18</v>
+        <v>5480.71</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>118131.92</v>
+        <v>113599.95</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -6090,25 +6090,25 @@
         <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>-1</v>
+        <v>-3.048</v>
       </c>
       <c r="G8" t="n">
         <v>0.006</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.006</v>
+        <v>-3.054</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>108884.61</v>
+        <v>106848.84</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>1712.75</v>
+        <v>1255.47</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>-1723.41</v>
+        <v>-3834.75</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>116408.52</v>
+        <v>109765.2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -6141,25 +6141,25 @@
         <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>-1</v>
+        <v>-1.056</v>
       </c>
       <c r="G9" t="n">
         <v>0.222</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.222</v>
+        <v>-1.278</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>116419.17</v>
+        <v>112344.48</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>1831.27</v>
+        <v>1320.05</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>-2238.22</v>
+        <v>-1686.79</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>114170.29</v>
+        <v>108078.42</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -6201,16 +6201,16 @@
         <v>-1.069</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>114577.24</v>
+        <v>108445.16</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>1802.3</v>
+        <v>1274.23</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>-1926.6</v>
+        <v>-1362.11</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>112243.7</v>
+        <v>106716.31</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -6252,16 +6252,16 @@
         <v>-1.06</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>112774.94</v>
+        <v>107170.93</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>1773.95</v>
+        <v>1259.26</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>-1879.86</v>
+        <v>-1334.44</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>110363.84</v>
+        <v>105381.87</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -6303,16 +6303,16 @@
         <v>-1.004</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>111000.99</v>
+        <v>105911.67</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>1746.05</v>
+        <v>1244.46</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>-1752.73</v>
+        <v>-1249.23</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>106925.92</v>
+        <v>102920.87</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -6354,16 +6354,16 @@
         <v>-1.026</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>108848</v>
+        <v>104300.47</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>1712.18</v>
+        <v>1225.53</v>
       </c>
       <c r="K13" s="7" t="n">
-        <v>-1757.24</v>
+        <v>-1257.78</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>103532.18</v>
+        <v>100476.75</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -6405,16 +6405,16 @@
         <v>-1.002</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>106905.61</v>
+        <v>102911.88</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>1681.63</v>
+        <v>1209.21</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>-1685.18</v>
+        <v>-1211.77</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>108678.65</v>
+        <v>104170.1</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -6456,16 +6456,16 @@
         <v>-1.001</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>105223.99</v>
+        <v>101702.66</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>1655.17</v>
+        <v>1195.01</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>-1657.38</v>
+        <v>-1196.6</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>101874.8</v>
+        <v>99280.14999999999</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -6507,16 +6507,16 @@
         <v>-1.005</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>103558.57</v>
+        <v>100500.34</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>1628.98</v>
+        <v>1180.88</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>-1636.51</v>
+        <v>-1186.34</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>105289.42</v>
+        <v>101734.53</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -6558,16 +6558,16 @@
         <v>2.372</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>101929.6</v>
+        <v>99319.46000000001</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>1603.35</v>
+        <v>1167</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>3803.82</v>
+        <v>2768.62</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>110991.87</v>
+        <v>106135.6</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -6609,16 +6609,16 @@
         <v>-1.009</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>100318.71</v>
+        <v>98146.99000000001</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>1578.01</v>
+        <v>1153.23</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>-1592.23</v>
+        <v>-1163.62</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>100282.57</v>
+        <v>98116.53</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -6660,16 +6660,16 @@
         <v>-1.138</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>98693.42999999999</v>
+        <v>96959.92</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>1552.45</v>
+        <v>1139.28</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>-1766.58</v>
+        <v>-1296.42</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>98515.99000000001</v>
+        <v>96820.11</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -6711,16 +6711,16 @@
         <v>-1.001</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>97126.77</v>
+        <v>95810.25</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>1527.8</v>
+        <v>1125.77</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>-1529.38</v>
+        <v>-1126.93</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>95479.82000000001</v>
+        <v>94577.75999999999</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -6762,16 +6762,16 @@
         <v>-1.004</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>95384.83</v>
+        <v>94527.34</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>1500.4</v>
+        <v>1110.7</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>-1506.79</v>
+        <v>-1115.42</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>97009.2</v>
+        <v>95704.69</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -6813,16 +6813,16 @@
         <v>-1.286</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>93876.47</v>
+        <v>93410.75999999999</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>1476.68</v>
+        <v>1097.58</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>-1898.58</v>
+        <v>-1411.17</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>108790.57</v>
+        <v>104562.91</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -6864,16 +6864,16 @@
         <v>-1.103</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>92399.78999999999</v>
+        <v>92313.17999999999</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>1453.45</v>
+        <v>1084.68</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>-1602.52</v>
+        <v>-1195.93</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>107188.04</v>
+        <v>103366.98</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -6915,16 +6915,16 @@
         <v>10.632</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>90946.34</v>
+        <v>91228.5</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>1430.59</v>
+        <v>1071.93</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>15209.33</v>
+        <v>11396.32</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>110689.15</v>
+        <v>105974.07</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -6966,16 +6966,16 @@
         <v>4.243</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>105584.69</v>
+        <v>102199.97</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>1660.85</v>
+        <v>1200.85</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>7047.09</v>
+        <v>5095.29</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>114324.5</v>
+        <v>108473.23</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -7017,16 +7017,16 @@
         <v>-1.174</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>109331.02</v>
+        <v>104934.75</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>1719.78</v>
+        <v>1232.98</v>
       </c>
       <c r="K26" s="7" t="n">
-        <v>-2018.87</v>
+        <v>-1447.42</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>108973</v>
+        <v>104688.18</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -7059,25 +7059,25 @@
         <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>-1</v>
+        <v>-1.074</v>
       </c>
       <c r="G27" t="n">
         <v>0.002</v>
       </c>
       <c r="H27" t="n">
-        <v>-1.002</v>
+        <v>-1.075</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>107611.24</v>
+        <v>103701.76</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>1692.72</v>
+        <v>1218.5</v>
       </c>
       <c r="K27" s="7" t="n">
-        <v>-1695.59</v>
+        <v>-1310.24</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>107277.41</v>
+        <v>103377.94</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -7119,16 +7119,16 @@
         <v>-1.091</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>105619.43</v>
+        <v>102268.84</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>1661.39</v>
+        <v>1201.66</v>
       </c>
       <c r="K28" s="7" t="n">
-        <v>-1812.43</v>
+        <v>-1310.9</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>112512.07</v>
+        <v>107162.33</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -7170,16 +7170,16 @@
         <v>10.606</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>112512.07</v>
+        <v>107162.33</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>1769.81</v>
+        <v>1259.16</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>18771.34</v>
+        <v>13355.11</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>131283.41</v>
+        <v>120517.44</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -7221,16 +7221,16 @@
         <v>-1.031</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>110742.26</v>
+        <v>105903.17</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>1741.98</v>
+        <v>1244.36</v>
       </c>
       <c r="K30" s="7" t="n">
-        <v>-1795.17</v>
+        <v>-1282.36</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>129488.24</v>
+        <v>119235.08</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -7272,16 +7272,16 @@
         <v>7.042</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>129541.43</v>
+        <v>119273.08</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>2037.69</v>
+        <v>1401.46</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>14348.44</v>
+        <v>9868.42</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>141762.24</v>
+        <v>113052.6</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -7323,16 +7323,16 @@
         <v>14.681</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>127503.75</v>
+        <v>117871.62</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>2005.63</v>
+        <v>1384.99</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>29443.82</v>
+        <v>20332.44</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>218002.95</v>
+        <v>161639.29</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -7365,25 +7365,25 @@
         <v>2</v>
       </c>
       <c r="F33" t="n">
-        <v>-1</v>
+        <v>-11.68</v>
       </c>
       <c r="G33" t="n">
         <v>0.051</v>
       </c>
       <c r="H33" t="n">
-        <v>-1.051</v>
+        <v>-11.731</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>125444.92</v>
+        <v>116448.63</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>1973.25</v>
+        <v>1368.27</v>
       </c>
       <c r="K33" s="7" t="n">
-        <v>-2074.44</v>
+        <v>-16050.89</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>127413.8</v>
+        <v>103184.19</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -7425,16 +7425,16 @@
         <v>-1.004</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>139756.6</v>
+        <v>111667.61</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>2198.37</v>
+        <v>1312.09</v>
       </c>
       <c r="K34" s="7" t="n">
-        <v>-2206.08</v>
+        <v>-1316.7</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>139556.15</v>
+        <v>111735.91</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -7476,16 +7476,16 @@
         <v>-1.25</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>137558.23</v>
+        <v>110355.52</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>2163.79</v>
+        <v>1296.68</v>
       </c>
       <c r="K35" s="7" t="n">
-        <v>-2704.74</v>
+        <v>-1620.85</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>136851.42</v>
+        <v>110115.06</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -7527,16 +7527,16 @@
         <v>25.818</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>135394.44</v>
+        <v>109058.84</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>2129.75</v>
+        <v>1281.44</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>54986.42</v>
+        <v>33084.5</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>191837.83</v>
+        <v>143199.56</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -7578,16 +7578,16 @@
         <v>-1.008</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>133264.69</v>
+        <v>107777.4</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>2096.25</v>
+        <v>1266.38</v>
       </c>
       <c r="K37" s="7" t="n">
-        <v>-2112.22</v>
+        <v>-1276.03</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>191655.77</v>
+        <v>143094.29</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -7629,16 +7629,16 @@
         <v>0.9350000000000001</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>131168.43</v>
+        <v>106511.01</v>
       </c>
       <c r="J38" s="5" t="n">
-        <v>2063.28</v>
+        <v>1251.5</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>1930.16</v>
+        <v>1170.76</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>193768</v>
+        <v>144370.32</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -7680,16 +7680,16 @@
         <v>-1.066</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>189666.11</v>
+        <v>141718.95</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>2983.45</v>
+        <v>1665.2</v>
       </c>
       <c r="K39" s="7" t="n">
-        <v>-3179.08</v>
+        <v>-1774.39</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>188476.69</v>
+        <v>141319.9</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
@@ -7731,16 +7731,16 @@
         <v>-1.008</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>186666.69</v>
+        <v>140044.1</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>2936.27</v>
+        <v>1645.52</v>
       </c>
       <c r="K40" s="7" t="n">
-        <v>-2960.43</v>
+        <v>-1659.06</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>179229.94</v>
+        <v>136108.21</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
@@ -7782,16 +7782,16 @@
         <v>-1.002</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>183730.42</v>
+        <v>138398.58</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>2890.08</v>
+        <v>1626.18</v>
       </c>
       <c r="K41" s="7" t="n">
-        <v>-2897</v>
+        <v>-1630.08</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>185579.69</v>
+        <v>139689.82</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -7833,16 +7833,16 @@
         <v>6.225</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>180840.34</v>
+        <v>136772.4</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>2844.62</v>
+        <v>1607.08</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>17706.98</v>
+        <v>10003.61</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>194319.63</v>
+        <v>144601.15</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -7884,16 +7884,16 @@
         <v>-1.211</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>177995.72</v>
+        <v>135165.32</v>
       </c>
       <c r="J43" s="5" t="n">
-        <v>2799.87</v>
+        <v>1588.19</v>
       </c>
       <c r="K43" s="7" t="n">
-        <v>-3389.32</v>
+        <v>-1922.55</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>182190.37</v>
+        <v>137767.27</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -7935,16 +7935,16 @@
         <v>-1.108</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>174993.3</v>
+        <v>133464.04</v>
       </c>
       <c r="J44" s="5" t="n">
-        <v>2752.64</v>
+        <v>1568.2</v>
       </c>
       <c r="K44" s="7" t="n">
-        <v>-3050.23</v>
+        <v>-1737.74</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>191269.4</v>
+        <v>142863.41</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
@@ -7986,16 +7986,16 @@
         <v>6.688</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>172240.65</v>
+        <v>131895.84</v>
       </c>
       <c r="J45" s="5" t="n">
-        <v>2709.35</v>
+        <v>1549.78</v>
       </c>
       <c r="K45" s="6" t="n">
-        <v>18120.1</v>
+        <v>10364.9</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>233239.44</v>
+        <v>170372.37</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
@@ -8037,16 +8037,16 @@
         <v>-1.016</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>169531.31</v>
+        <v>130346.07</v>
       </c>
       <c r="J46" s="5" t="n">
-        <v>2666.73</v>
+        <v>1531.57</v>
       </c>
       <c r="K46" s="7" t="n">
-        <v>-2710.27</v>
+        <v>-1556.57</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>188559.13</v>
+        <v>141306.84</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
@@ -8088,16 +8088,16 @@
         <v>-1.001</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>166275.13</v>
+        <v>128480.14</v>
       </c>
       <c r="J47" s="5" t="n">
-        <v>2615.51</v>
+        <v>1509.64</v>
       </c>
       <c r="K47" s="7" t="n">
-        <v>-2617.29</v>
+        <v>-1510.67</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>176612.65</v>
+        <v>134597.54</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
@@ -8139,16 +8139,16 @@
         <v>22</v>
       </c>
       <c r="I48" s="5" t="n">
-        <v>163635.46</v>
+        <v>126956.96</v>
       </c>
       <c r="J48" s="5" t="n">
-        <v>2573.99</v>
+        <v>1491.74</v>
       </c>
       <c r="K48" s="6" t="n">
-        <v>56627.64</v>
+        <v>32818.35</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>280240.38</v>
+        <v>197799.29</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
@@ -8190,16 +8190,16 @@
         <v>11.171</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>161059.69</v>
+        <v>125464.19</v>
       </c>
       <c r="J49" s="5" t="n">
-        <v>2533.47</v>
+        <v>1474.2</v>
       </c>
       <c r="K49" s="6" t="n">
-        <v>28301.88</v>
+        <v>16468.62</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>308542.26</v>
+        <v>214267.92</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
@@ -8241,16 +8241,16 @@
         <v>-1.026</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>178736.7</v>
+        <v>135406.13</v>
       </c>
       <c r="J50" s="5" t="n">
-        <v>2811.53</v>
+        <v>1591.02</v>
       </c>
       <c r="K50" s="7" t="n">
-        <v>-2883.62</v>
+        <v>-1631.82</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>215119.33</v>
+        <v>160007.47</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
@@ -8292,16 +8292,16 @@
         <v>-1.014</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>175925.17</v>
+        <v>133815.1</v>
       </c>
       <c r="J51" s="5" t="n">
-        <v>2767.3</v>
+        <v>1572.33</v>
       </c>
       <c r="K51" s="7" t="n">
-        <v>-2805.34</v>
+        <v>-1593.94</v>
       </c>
       <c r="L51" s="5" t="n">
-        <v>230434.09</v>
+        <v>168778.43</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -8343,16 +8343,16 @@
         <v>-1.032</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>204535.23</v>
+        <v>153919.42</v>
       </c>
       <c r="J52" s="5" t="n">
-        <v>3217.34</v>
+        <v>1808.55</v>
       </c>
       <c r="K52" s="7" t="n">
-        <v>-3320.29</v>
+        <v>-1866.43</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>227113.8</v>
+        <v>166912.01</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
@@ -8394,16 +8394,16 @@
         <v>-1.002</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>222109.3</v>
+        <v>164003.93</v>
       </c>
       <c r="J53" s="5" t="n">
-        <v>3493.78</v>
+        <v>1927.05</v>
       </c>
       <c r="K53" s="7" t="n">
-        <v>-3501.06</v>
+        <v>-1931.06</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>223612.74</v>
+        <v>164980.94</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
@@ -8445,16 +8445,16 @@
         <v>10.11</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>218505.29</v>
+        <v>162015</v>
       </c>
       <c r="J54" s="5" t="n">
-        <v>3437.09</v>
+        <v>1903.68</v>
       </c>
       <c r="K54" s="6" t="n">
-        <v>34747.6</v>
+        <v>19245.41</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>343289.86</v>
+        <v>233513.33</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
@@ -8496,16 +8496,16 @@
         <v>-1.021</v>
       </c>
       <c r="I55" s="5" t="n">
-        <v>305105.17</v>
+        <v>212364.24</v>
       </c>
       <c r="J55" s="5" t="n">
-        <v>4799.3</v>
+        <v>2495.28</v>
       </c>
       <c r="K55" s="7" t="n">
-        <v>-4897.75</v>
+        <v>-2546.47</v>
       </c>
       <c r="L55" s="5" t="n">
-        <v>328897.56</v>
+        <v>226000.61</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
@@ -8547,16 +8547,16 @@
         <v>-1.024</v>
       </c>
       <c r="I56" s="5" t="n">
-        <v>300305.87</v>
+        <v>209868.96</v>
       </c>
       <c r="J56" s="5" t="n">
-        <v>4723.81</v>
+        <v>2465.96</v>
       </c>
       <c r="K56" s="7" t="n">
-        <v>-4834.96</v>
+        <v>-2523.98</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>338454.9</v>
+        <v>230989.34</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
@@ -8598,16 +8598,16 @@
         <v>-1.002</v>
       </c>
       <c r="I57" s="5" t="n">
-        <v>295582.06</v>
+        <v>207403</v>
       </c>
       <c r="J57" s="5" t="n">
-        <v>4649.51</v>
+        <v>2436.99</v>
       </c>
       <c r="K57" s="7" t="n">
-        <v>-4659.59</v>
+        <v>-2442.27</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>333795.31</v>
+        <v>228547.07</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
@@ -8649,16 +8649,16 @@
         <v>-1.038</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>329006.09</v>
+        <v>226057.08</v>
       </c>
       <c r="J58" s="5" t="n">
-        <v>5175.27</v>
+        <v>2656.17</v>
       </c>
       <c r="K58" s="7" t="n">
-        <v>-5370.56</v>
+        <v>-2756.4</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>307665.03</v>
+        <v>215023.38</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
@@ -8700,16 +8700,16 @@
         <v>-1.007</v>
       </c>
       <c r="I59" s="5" t="n">
-        <v>323722.29</v>
+        <v>223344.44</v>
       </c>
       <c r="J59" s="5" t="n">
-        <v>5092.15</v>
+        <v>2624.3</v>
       </c>
       <c r="K59" s="7" t="n">
-        <v>-5129.8</v>
+        <v>-2643.7</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>323767.76</v>
+        <v>223356.91</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
@@ -8751,16 +8751,16 @@
         <v>-1.03</v>
       </c>
       <c r="I60" s="5" t="n">
-        <v>318630.14</v>
+        <v>220720.14</v>
       </c>
       <c r="J60" s="5" t="n">
-        <v>5012.05</v>
+        <v>2593.46</v>
       </c>
       <c r="K60" s="7" t="n">
-        <v>-5160.56</v>
+        <v>-2670.3</v>
       </c>
       <c r="L60" s="5" t="n">
-        <v>318607.2</v>
+        <v>220686.6</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
@@ -8802,16 +8802,16 @@
         <v>-1.007</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>313580.44</v>
+        <v>218107.28</v>
       </c>
       <c r="J61" s="5" t="n">
-        <v>4932.62</v>
+        <v>2562.76</v>
       </c>
       <c r="K61" s="7" t="n">
-        <v>-4967.3</v>
+        <v>-2580.78</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>316197.69</v>
+        <v>219539.74</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
@@ -8853,16 +8853,16 @@
         <v>-1.148</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>308499.31</v>
+        <v>215467.67</v>
       </c>
       <c r="J62" s="5" t="n">
-        <v>4852.69</v>
+        <v>2531.75</v>
       </c>
       <c r="K62" s="7" t="n">
-        <v>-5571.61</v>
+        <v>-2906.82</v>
       </c>
       <c r="L62" s="5" t="n">
-        <v>313035.59</v>
+        <v>217779.79</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
@@ -8904,16 +8904,16 @@
         <v>4.894</v>
       </c>
       <c r="I63" s="5" t="n">
-        <v>303646.62</v>
+        <v>212935.93</v>
       </c>
       <c r="J63" s="5" t="n">
-        <v>4776.36</v>
+        <v>2502</v>
       </c>
       <c r="K63" s="6" t="n">
-        <v>23375.02</v>
+        <v>12244.52</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>331040.05</v>
+        <v>227267.9</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
@@ -8955,16 +8955,16 @@
         <v>-1.014</v>
       </c>
       <c r="I64" s="5" t="n">
-        <v>297956.05</v>
+        <v>209958.62</v>
       </c>
       <c r="J64" s="5" t="n">
-        <v>4686.85</v>
+        <v>2467.01</v>
       </c>
       <c r="K64" s="7" t="n">
-        <v>-4750.4</v>
+        <v>-2500.46</v>
       </c>
       <c r="L64" s="5" t="n">
-        <v>326289.65</v>
+        <v>224767.43</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
@@ -9006,16 +9006,16 @@
         <v>-1.014</v>
       </c>
       <c r="I65" s="5" t="n">
-        <v>321357.03</v>
+        <v>222204.67</v>
       </c>
       <c r="J65" s="5" t="n">
-        <v>5054.95</v>
+        <v>2610.9</v>
       </c>
       <c r="K65" s="7" t="n">
-        <v>-5124.67</v>
+        <v>-2646.92</v>
       </c>
       <c r="L65" s="5" t="n">
-        <v>321164.98</v>
+        <v>222120.52</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
@@ -9057,16 +9057,16 @@
         <v>-1.02</v>
       </c>
       <c r="I66" s="5" t="n">
-        <v>316302.09</v>
+        <v>219593.77</v>
       </c>
       <c r="J66" s="5" t="n">
-        <v>4975.43</v>
+        <v>2580.23</v>
       </c>
       <c r="K66" s="7" t="n">
-        <v>-5072.51</v>
+        <v>-2630.57</v>
       </c>
       <c r="L66" s="5" t="n">
-        <v>311125.17</v>
+        <v>216909.17</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
@@ -9100,16 +9100,16 @@
         <v>-0.004</v>
       </c>
       <c r="I67" s="5" t="n">
-        <v>311256.93</v>
+        <v>216977.53</v>
       </c>
       <c r="J67" s="5" t="n">
-        <v>4896.07</v>
+        <v>2549.49</v>
       </c>
       <c r="K67" s="7" t="n">
-        <v>-17.74</v>
+        <v>-9.24</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>488264.98</v>
+        <v>313974</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
@@ -9151,16 +9151,16 @@
         <v>-1.082</v>
       </c>
       <c r="I68" s="5" t="n">
-        <v>306229.1</v>
+        <v>214359.68</v>
       </c>
       <c r="J68" s="5" t="n">
-        <v>4816.98</v>
+        <v>2518.73</v>
       </c>
       <c r="K68" s="7" t="n">
-        <v>-5210.21</v>
+        <v>-2724.34</v>
       </c>
       <c r="L68" s="5" t="n">
-        <v>305914.97</v>
+        <v>214184.83</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
@@ -9202,16 +9202,16 @@
         <v>17.026</v>
       </c>
       <c r="I69" s="5" t="n">
-        <v>301412.12</v>
+        <v>211840.95</v>
       </c>
       <c r="J69" s="5" t="n">
-        <v>4741.21</v>
+        <v>2489.13</v>
       </c>
       <c r="K69" s="6" t="n">
-        <v>80725.23</v>
+        <v>42380.66</v>
       </c>
       <c r="L69" s="5" t="n">
-        <v>495221.24</v>
+        <v>317442.12</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
@@ -9253,16 +9253,16 @@
         <v>-1.012</v>
       </c>
       <c r="I70" s="5" t="n">
-        <v>296670.9</v>
+        <v>209351.82</v>
       </c>
       <c r="J70" s="5" t="n">
-        <v>4666.63</v>
+        <v>2459.88</v>
       </c>
       <c r="K70" s="7" t="n">
-        <v>-4721.7</v>
+        <v>-2488.91</v>
       </c>
       <c r="L70" s="5" t="n">
-        <v>301193.27</v>
+        <v>211695.92</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
@@ -9304,16 +9304,16 @@
         <v>8</v>
       </c>
       <c r="I71" s="5" t="n">
-        <v>292004.27</v>
+        <v>206891.94</v>
       </c>
       <c r="J71" s="5" t="n">
-        <v>4593.23</v>
+        <v>2430.98</v>
       </c>
       <c r="K71" s="6" t="n">
-        <v>36745.86</v>
+        <v>19447.86</v>
       </c>
       <c r="L71" s="5" t="n">
-        <v>333587.76</v>
+        <v>228802.49</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
@@ -9355,16 +9355,16 @@
         <v>10.195</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>287017.82</v>
+        <v>204255.35</v>
       </c>
       <c r="J72" s="5" t="n">
-        <v>4514.79</v>
+        <v>2400</v>
       </c>
       <c r="K72" s="6" t="n">
-        <v>46028.83</v>
+        <v>24468.29</v>
       </c>
       <c r="L72" s="5" t="n">
-        <v>374727.34</v>
+        <v>250629.42</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
@@ -9397,25 +9397,25 @@
         <v>5</v>
       </c>
       <c r="F73" t="n">
-        <v>6.348</v>
+        <v>7.739</v>
       </c>
       <c r="G73" t="n">
         <v>0.08699999999999999</v>
       </c>
       <c r="H73" t="n">
-        <v>6.261</v>
+        <v>7.652</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>282503.03</v>
+        <v>201855.35</v>
       </c>
       <c r="J73" s="5" t="n">
-        <v>4443.77</v>
+        <v>2371.8</v>
       </c>
       <c r="K73" s="6" t="n">
-        <v>27821.77</v>
+        <v>18149.36</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>402549.1</v>
+        <v>268778.78</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
@@ -9449,16 +9449,16 @@
         <v>-0.003</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>278059.26</v>
+        <v>199483.55</v>
       </c>
       <c r="J74" s="5" t="n">
-        <v>4373.87</v>
+        <v>2343.93</v>
       </c>
       <c r="K74" s="7" t="n">
-        <v>-15.24</v>
+        <v>-8.17</v>
       </c>
       <c r="L74" s="5" t="n">
-        <v>488249.74</v>
+        <v>313965.84</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
@@ -9500,16 +9500,16 @@
         <v>-1.011</v>
       </c>
       <c r="I75" s="5" t="n">
-        <v>273685.39</v>
+        <v>197139.62</v>
       </c>
       <c r="J75" s="5" t="n">
-        <v>4305.07</v>
+        <v>2316.39</v>
       </c>
       <c r="K75" s="7" t="n">
-        <v>-4351.36</v>
+        <v>-2341.3</v>
       </c>
       <c r="L75" s="5" t="n">
-        <v>296841.91</v>
+        <v>209354.62</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
@@ -9551,16 +9551,16 @@
         <v>-1.154</v>
       </c>
       <c r="I76" s="5" t="n">
-        <v>269380.31</v>
+        <v>194823.23</v>
       </c>
       <c r="J76" s="5" t="n">
-        <v>4237.35</v>
+        <v>2289.17</v>
       </c>
       <c r="K76" s="7" t="n">
-        <v>-4889.25</v>
+        <v>-2641.35</v>
       </c>
       <c r="L76" s="5" t="n">
-        <v>328698.51</v>
+        <v>226161.13</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
@@ -9602,16 +9602,16 @@
         <v>-1.048</v>
       </c>
       <c r="I77" s="5" t="n">
-        <v>305728.79</v>
+        <v>214006.78</v>
       </c>
       <c r="J77" s="5" t="n">
-        <v>4809.11</v>
+        <v>2514.58</v>
       </c>
       <c r="K77" s="7" t="n">
-        <v>-5038.12</v>
+        <v>-2634.32</v>
       </c>
       <c r="L77" s="5" t="n">
-        <v>414496.01</v>
+        <v>275061.47</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
@@ -9653,16 +9653,16 @@
         <v>3.588</v>
       </c>
       <c r="I78" s="5" t="n">
-        <v>300919.68</v>
+        <v>211492.2</v>
       </c>
       <c r="J78" s="5" t="n">
-        <v>4733.47</v>
+        <v>2485.03</v>
       </c>
       <c r="K78" s="6" t="n">
-        <v>16985.02</v>
+        <v>8917.01</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>419534.13</v>
+        <v>277695.79</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
@@ -9704,16 +9704,16 @@
         <v>-1.049</v>
       </c>
       <c r="I79" s="5" t="n">
-        <v>400484.85</v>
+        <v>267678.92</v>
       </c>
       <c r="J79" s="5" t="n">
-        <v>6299.63</v>
+        <v>3145.23</v>
       </c>
       <c r="K79" s="7" t="n">
-        <v>-6610.72</v>
+        <v>-3300.55</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>488610.52</v>
+        <v>314141.57</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
@@ -9747,16 +9747,16 @@
         <v>-0.019</v>
       </c>
       <c r="I80" s="5" t="n">
-        <v>479340.58</v>
+        <v>309248.16</v>
       </c>
       <c r="J80" s="5" t="n">
-        <v>7540.03</v>
+        <v>3633.67</v>
       </c>
       <c r="K80" s="7" t="n">
-        <v>-142.26</v>
+        <v>-68.56</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>488468.26</v>
+        <v>314073.01</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
@@ -9790,16 +9790,16 @@
         <v>-0.025</v>
       </c>
       <c r="I81" s="5" t="n">
-        <v>471800.55</v>
+        <v>305614.49</v>
       </c>
       <c r="J81" s="5" t="n">
-        <v>7421.42</v>
+        <v>3590.97</v>
       </c>
       <c r="K81" s="7" t="n">
-        <v>-185.54</v>
+        <v>-89.77</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>488282.72</v>
+        <v>313983.24</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
